--- a/01_전문업무_및_엔지니어링/11_현장_프로젝트/01_동탄트램/08.메뉴얼 및 평면도/최종/02_메뉴얼 공종프로섹스(집행단계)/매뉴얼 BODY (집행단계)v5.xlsx
+++ b/01_전문업무_및_엔지니어링/11_현장_프로젝트/01_동탄트램/08.메뉴얼 및 평면도/최종/02_메뉴얼 공종프로섹스(집행단계)/매뉴얼 BODY (집행단계)v5.xlsx
@@ -43,7 +43,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -226,6 +226,13 @@
       <color rgb="00000000"/>
       <sz val="13"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="000000FF"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -304,7 +311,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -561,11 +568,55 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -920,6 +971,32 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7270,7 +7347,7 @@
 2) LTE-R 무선망, 8대 이종 통신시스템, 타공종 간섭 및 리스크 헷지·기회반영 설계변경 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K2" s="78" t="inlineStr">
+      <c r="K2" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -7281,7 +7358,7 @@
 2) 시공성 및 설계변경: 현장 지장물 실측 조사, 타공종 3D 간섭 조정, 공법/안전 검토 및 현장 전직원+본사 동시 검토 회의로 설계변경 수립</t>
         </is>
       </c>
-      <c r="M2" s="78" t="inlineStr">
+      <c r="M2" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -7292,7 +7369,7 @@
 2) LTE-R 무선망, 타공종 3D 간섭조정, 8대 이종 통신시스템, 관제연동 적정성 검토 및 현장전직원+본사 동시 검토 승인을 완료하였는가?</t>
         </is>
       </c>
-      <c r="O2" s="67" t="inlineStr">
+      <c r="O2" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -7372,7 +7449,7 @@
 2) 주요 통신 자재 납품 수급 계획 및 시공 적격성 평가를 반영한 발주전략 KOM 보고서 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K3" s="78" t="inlineStr">
+      <c r="K3" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -7383,7 +7460,7 @@
 2) 전략 수립 및 승인: 리스크 헷지형 계약 조건 도출 및 현장소장/공무팀 주관 발주전략 KOM 보고서 확정</t>
         </is>
       </c>
-      <c r="M3" s="78" t="inlineStr">
+      <c r="M3" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -7394,7 +7471,7 @@
 2) 주요 자재 납품 수급 계획 및 적격 시공업체 평가 기준을 마련하여 발주전략 KOM 승인을 완수하였는가?</t>
         </is>
       </c>
-      <c r="O3" s="67" t="inlineStr">
+      <c r="O3" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -7464,7 +7541,7 @@
 2) 타공종 구조체 타설 전 통신 매립 배관 위치 검증 및 인터페이스 협의록 작성 표준 적용</t>
         </is>
       </c>
-      <c r="K4" s="67" t="inlineStr">
+      <c r="K4" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -7475,7 +7552,7 @@
 2) 협의 수행 및 승인: 타공종 구조체 콘크리트 타설 전 통신 배관 매립 위치 현장 확인 및 3D 간섭 조정 협의록 확정</t>
         </is>
       </c>
-      <c r="M4" s="67" t="inlineStr">
+      <c r="M4" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -7486,7 +7563,7 @@
 2) 업체 Pool[적격 업체] 철도/트램 시공 및 영업운행 실적이 입증된 적격 업체 Pool을 검토하였는가?</t>
         </is>
       </c>
-      <c r="O4" s="78" t="inlineStr">
+      <c r="O4" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -7561,7 +7638,7 @@
 2) 타공종 간 전자기 적합성(EMC/EMI), 전력 케이블 유도장해 차폐 및 서지 보호 표준 적용</t>
         </is>
       </c>
-      <c r="K5" s="67" t="inlineStr">
+      <c r="K5" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -7572,7 +7649,7 @@
 2) 3D/BIM 간섭조정 및 승인: 이종 시스템 간 인터페이스 핀 맵, 데이터 포맷 교차 검증 및 시스템 합동 인터페이스 협의록 작성</t>
         </is>
       </c>
-      <c r="M5" s="67" t="inlineStr">
+      <c r="M5" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -7583,7 +7660,7 @@
 2) KEC 점유율[KEC 33%] 전선관 내부 단면적 점유율 33% 이하 및 ELP ø150mm×6개×2조 배관을 확인하였는가?</t>
         </is>
       </c>
-      <c r="O5" s="78" t="inlineStr">
+      <c r="O5" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -7653,7 +7730,7 @@
 2) 제작사 간 데이터 입출력 포맷 및 연동 케이블 사양서 확정 협의록 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K6" s="78" t="inlineStr">
+      <c r="K6" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -7664,7 +7741,7 @@
 2) 연동 시험 수칙 수립: 제작사 간 신호 연동 핀 배열 확정 및 상호 연동 인터페이스 사양서 감리 승인 절차 수행</t>
         </is>
       </c>
-      <c r="M6" s="78" t="inlineStr">
+      <c r="M6" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -7675,7 +7752,7 @@
 2) 전원 잭 확인[코드 잭 준비] 각 장비에 220V 코드를 꽂을지 48V 전기를 줄지 전원 잭을 사전에 확인하였는가?</t>
         </is>
       </c>
-      <c r="O6" s="78" t="inlineStr">
+      <c r="O6" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -7747,7 +7824,7 @@
 2) 관제 서버, 네트워크 스위치 및 운영사 통합 수선 체계 부합성 확인 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K7" s="67" t="inlineStr">
+      <c r="K7" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -7758,7 +7835,7 @@
 2) 관제 인터페이스 승인: 관제 서버-현장 장치 간 제어 데이터 송수신 시험 절차 수립 및 운영사 합동 검토서 확정</t>
         </is>
       </c>
-      <c r="M7" s="78" t="inlineStr">
+      <c r="M7" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -7769,7 +7846,7 @@
 2) 4K CCTV 65개[명당 자리] 교차로 4K CCTV 카메라 65개소가 사각지대 없이 보이도록 명당 자리를 배치하였는가?</t>
         </is>
       </c>
-      <c r="O7" s="78" t="inlineStr">
+      <c r="O7" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -7839,7 +7916,7 @@
 2) 품질시험계획서 수립 및 발주처 승인 품질 기준 준수서 작성 표준 적용</t>
         </is>
       </c>
-      <c r="K8" s="67" t="inlineStr">
+      <c r="K8" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -7850,7 +7927,7 @@
 2) 품질 관리 수립: 현장 품질시험계획서 수립, 불합격 자재 반출 절차 확립 및 발주처 승인 품질 수칙 이행</t>
         </is>
       </c>
-      <c r="M8" s="67" t="inlineStr">
+      <c r="M8" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -7861,7 +7938,7 @@
 2) [Hold Point] 감리원 현장 직접 입회 검측 항목(Hold Point)을 사전 분류 지정하였는가?</t>
         </is>
       </c>
-      <c r="O8" s="67" t="inlineStr">
+      <c r="O8" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -7931,7 +8008,7 @@
 2) 예정공정표 대비 인원·장비 투입 수급 타당성 및 안전 수칙 준수 검토 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K9" s="78" t="inlineStr">
+      <c r="K9" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -7942,7 +8019,7 @@
 2) 공정 수급 승인: 예정공정표 대비 적정 투입 인원 산출, 작업 안전 구역 확보 및 현장소장 투입 승인 절차 수행</t>
         </is>
       </c>
-      <c r="M9" s="67" t="inlineStr">
+      <c r="M9" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -7953,7 +8030,7 @@
 2) [인력 자격] 통신 공종별 특급/고급 기술자 자격증 및 현장 배치 계획을 확인하였는가?</t>
         </is>
       </c>
-      <c r="O9" s="78" t="inlineStr">
+      <c r="O9" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -8032,7 +8109,7 @@
 2) 간섭사항 사전 도출 및 공종 간 공정 마일스톤 협의록 작성 표준 적용</t>
         </is>
       </c>
-      <c r="K10" s="67" t="inlineStr">
+      <c r="K10" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -8043,7 +8120,7 @@
 2) 간섭 리스크 해소: 공사 착수 전 분야별 간섭 위험 요소를 발굴하여 헷지 방안 수립 및 Big Room 회의록 최종 승인</t>
         </is>
       </c>
-      <c r="M10" s="67" t="inlineStr">
+      <c r="M10" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -8054,7 +8131,7 @@
 2) [인터페이스] 노반(궤도)/전기/신호/기계/차량 5대 공종 간 관통 경로 및 간섭점을 사전 도출 검출하였는가?</t>
         </is>
       </c>
-      <c r="O10" s="67" t="inlineStr">
+      <c r="O10" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -8125,7 +8202,7 @@
 2) 감리단 및 발주처 승인을 위한 제작사양서 승인 신청서 및 공학적 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K11" s="67" t="inlineStr">
+      <c r="K11" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -8136,7 +8213,7 @@
 2) 공학적 승인 신청: 발주처 입찰시방과 제작사양서 1:1 대조 검증 및 감리단 공학적 승인 제출 절차 수행</t>
         </is>
       </c>
-      <c r="M11" s="67" t="inlineStr">
+      <c r="M11" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -8147,7 +8224,7 @@
 2) [사양서 정의] 실제 제작·설치될 통신설비의 전기적·기계적 세부 규격 및 제작도면(Shop Drawing)을 작성하였는가?</t>
         </is>
       </c>
-      <c r="O11" s="67" t="inlineStr">
+      <c r="O11" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -8220,7 +8297,7 @@
 2) 통신설비 설치 공법 타당성 및 감리단 시공계획서 승인 제출 표준 적용</t>
         </is>
       </c>
-      <c r="K12" s="67" t="inlineStr">
+      <c r="K12" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -8231,7 +8308,7 @@
 2) 감리 승인 및 이행: 시공상세도(Shop Drawing) 첨부, 현장 안전 위험성 평가 실시 및 감리단 시공계획서 승인 완료</t>
         </is>
       </c>
-      <c r="M12" s="67" t="inlineStr">
+      <c r="M12" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -8242,7 +8319,7 @@
 2) [안전 대책] 통신기계실 DC -48V 감전 방지 및 정거장 고소작업 시 안전대/2인1조 작업 대책을 수립하였는가?</t>
         </is>
       </c>
-      <c r="O12" s="67" t="inlineStr">
+      <c r="O12" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -8315,7 +8392,7 @@
 2) 성능보증이 가능한 복수 자재공급원 승인 서류 수립 및 감리 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K13" s="67" t="inlineStr">
+      <c r="K13" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -8326,7 +8403,7 @@
 2) 자재 승인 및 관리: 복수 공급원 비교 검토서 작성, 불량 자재 차단 헷지 및 감리단 자재공급원 승인 획득</t>
         </is>
       </c>
-      <c r="M13" s="67" t="inlineStr">
+      <c r="M13" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -8337,7 +8414,7 @@
 2) [사양 대조] 설계도서 수치(KCS 31 10 00)와 자재 카탈로그 규격 간 1:1 대조표를 정확히 작성하였는가?</t>
         </is>
       </c>
-      <c r="O13" s="67" t="inlineStr">
+      <c r="O13" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -8412,7 +8489,7 @@
 2) 공장 수검 검사, 품질 성능 시험성적서 확인 및 공장검사 합격증명서 발급 표준 적용</t>
         </is>
       </c>
-      <c r="K14" s="67" t="inlineStr">
+      <c r="K14" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -8423,7 +8500,7 @@
 2) 입회 검사 실시: 전원 인입, 기능 시험, 방수/내열 공인시험 실측 확인 및 FAT 공장검사 합격증명서 획득</t>
         </is>
       </c>
-      <c r="M14" s="67" t="inlineStr">
+      <c r="M14" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -8434,7 +8511,7 @@
 2) [ITP 승인] 감리 승인된 ITP 절차서와 절연저항계(Megger), OTDR의 교정 유효기간 증명서를 사전 확인하였는가?</t>
         </is>
       </c>
-      <c r="O14" s="67" t="inlineStr">
+      <c r="O14" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -8506,7 +8583,7 @@
 2) 바닥 엑세스플로어, 방화 구획 및 기초 구조체 인수인계 확인서 작성 표준 적용</t>
         </is>
       </c>
-      <c r="K15" s="67" t="inlineStr">
+      <c r="K15" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -8517,7 +8594,7 @@
 2) 인수인계 승인: 미비 사항 현장 보완 조치 요구 및 통신 시공 적격 선행 공정 인수인계 확인서 최종 승인</t>
         </is>
       </c>
-      <c r="M15" s="78" t="inlineStr">
+      <c r="M15" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -8528,7 +8605,7 @@
 2) 토목, 건축, 통신 현장 담당자 3자 공조 체계를 구성하고 현장 합동 점검표, Mandrel 도통시험기 및 레이저 레벨기를 사전 준비하였는가?</t>
         </is>
       </c>
-      <c r="O15" s="67" t="inlineStr">
+      <c r="O15" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -8600,7 +8677,7 @@
 2) 장비 반입 허가서 작성 및 안전 교육 이수 수료증 관리 표준 적용</t>
         </is>
       </c>
-      <c r="K16" s="78" t="inlineStr">
+      <c r="K16" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -8611,7 +8688,7 @@
 2) 안전 교육 이수: 통신 시공 작업자 대상 특별안전보건교육, 보호구 착용 점검 및 안전 교육 이수 수료 관리</t>
         </is>
       </c>
-      <c r="M16" s="67" t="inlineStr">
+      <c r="M16" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -8622,7 +8699,7 @@
 2) 토목/건축 등 타분야 양중 작업 간섭 여부를 사전 협의하고 양중 시간대를 분리 조율하였는가?</t>
         </is>
       </c>
-      <c r="O16" s="67" t="inlineStr">
+      <c r="O16" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -8694,7 +8771,7 @@
 2) 자재검수 요청서 작성 및 감리 입회 검수 합격 확인 표준 적용</t>
         </is>
       </c>
-      <c r="K17" s="67" t="inlineStr">
+      <c r="K17" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -8705,7 +8782,7 @@
 2) 자재검수 보고: 감리 입회 자재 검수 실시, 자재검수 요청서 결재 및 현장 통신 자재 창고 입고 관리</t>
         </is>
       </c>
-      <c r="M17" s="67" t="inlineStr">
+      <c r="M17" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -8716,7 +8793,7 @@
 2) 업체 Pool[적격 업체] 철도/트램 시공 및 영업운행 실적이 입증된 적격 업체 Pool을 검토하였는가?</t>
         </is>
       </c>
-      <c r="O17" s="78" t="inlineStr">
+      <c r="O17" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -8790,7 +8867,7 @@
 2) 케이블 성단, OTDR 접속 및 설비 고정 상태 검측 표준 적용</t>
         </is>
       </c>
-      <c r="K18" s="67" t="inlineStr">
+      <c r="K18" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -8801,7 +8878,7 @@
 2) 접속 및 검측: OTDR 접속 손실(≤0.05dB) 측정, 랙 전원 인입 배선 정리 및 설비 고정 상태 감리 검측</t>
         </is>
       </c>
-      <c r="M18" s="67" t="inlineStr">
+      <c r="M18" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -8812,7 +8889,7 @@
 2) 72-Core 광케이블 융착 접속 트레이 정돈 및 접속 손실 샘플 시공 승인을 획득하였는가?</t>
         </is>
       </c>
-      <c r="O18" s="78" t="inlineStr">
+      <c r="O18" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -8883,7 +8960,7 @@
 2) 관제 시스템 전원 인입, 배선 정리 및 관제 환경 설치 검측 표준 적용</t>
         </is>
       </c>
-      <c r="K19" s="67" t="inlineStr">
+      <c r="K19" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -8894,7 +8971,7 @@
 2) 전원 및 계통 검측: 관제 전원 분배기 전원 인입, 이중화 네트워크 케이블 성단 및 관제실 설치 상태 확인</t>
         </is>
       </c>
-      <c r="M19" s="67" t="inlineStr">
+      <c r="M19" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -8905,7 +8982,7 @@
 2) 멀티 디스플레이 패널 간 베젤 이격 단차(≤0.5mm) 미세 조율 및 방진 가스켓 부착을 완료하였는가?</t>
         </is>
       </c>
-      <c r="O19" s="67" t="inlineStr">
+      <c r="O19" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -8975,7 +9052,7 @@
 2) 설비별 단위시험 절차서 준수 및 단독 기능 시험성적서 작성 표준 적용</t>
         </is>
       </c>
-      <c r="K20" s="67" t="inlineStr">
+      <c r="K20" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -8986,7 +9063,7 @@
 2) 단위성적서 작성: 단위시험 절차서 항목별 성능 측정, 불합격 항목 보완 조치 및 단위시험 성과표 확정</t>
         </is>
       </c>
-      <c r="M20" s="67" t="inlineStr">
+      <c r="M20" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -8997,7 +9074,7 @@
 2) RF 파워메터로 무선장치(RU) 송신 출력을 계측하여 표준 규격(43dBm ±0.5dB) 이내임을 검측하였는가?</t>
         </is>
       </c>
-      <c r="O20" s="78" t="inlineStr">
+      <c r="O20" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9069,7 +9146,7 @@
 2) 통합시험 절차서 준수 및 이종 통신 설비 간 상호 연동성 검측 표준 적용</t>
         </is>
       </c>
-      <c r="K21" s="67" t="inlineStr">
+      <c r="K21" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9080,7 +9157,7 @@
 2) 통합 성과 확인: 관제-현장 장치 간 제어 응답속도 검측, 통합 시험 성과표 작성 및 감리 승인 완료</t>
         </is>
       </c>
-      <c r="M21" s="78" t="inlineStr">
+      <c r="M21" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9091,7 +9168,7 @@
 2) 관제 콘솔에서 PIS 문구 송출 명령 전송 시 현장 안내표시기 반응 지연 시간(≤0.5초 이내)을 검측하였는가?</t>
         </is>
       </c>
-      <c r="O21" s="67" t="inlineStr">
+      <c r="O21" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9161,7 +9238,7 @@
 2) 공종별 시험 항목 검측, 무선 전계강도 측정 및 시험성적서 확정 표준 적용</t>
         </is>
       </c>
-      <c r="K22" s="67" t="inlineStr">
+      <c r="K22" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9172,7 +9249,7 @@
 2) 공종 시험 승인: 무선 전계강도 측정 성과표 및 공종별 시운전 시험 결과 보고서 제출 및 감리 승인</t>
         </is>
       </c>
-      <c r="M22" s="67" t="inlineStr">
+      <c r="M22" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9183,7 +9260,7 @@
 2) 광케이블 융착 접속점 접속 손실 수치가 시방 기준(≤0.1dB/접속점 이하)을 통과함을 확인하였는가?</t>
         </is>
       </c>
-      <c r="O22" s="78" t="inlineStr">
+      <c r="O22" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9257,7 +9334,7 @@
 2) 차량 투입 대비 통신 무무선 연동 안전 상태 확인 표준 적용</t>
         </is>
       </c>
-      <c r="K23" s="67" t="inlineStr">
+      <c r="K23" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9268,7 +9345,7 @@
 2) 투입 안전 승인: 차량 투입 시 무선 통신 끊김 예방 점검 및 차량 투입 전 통신 안전 확인서 작성</t>
         </is>
       </c>
-      <c r="M23" s="67" t="inlineStr">
+      <c r="M23" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9279,7 +9356,7 @@
 2) 궤도 주변 통신 케이블 트레이 및 광점퍼 선로 묶음이 건축한계 이내로 처지거나 돌출되지 않음을 확인하였는가?</t>
         </is>
       </c>
-      <c r="O23" s="67" t="inlineStr">
+      <c r="O23" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9350,7 +9427,7 @@
 2) 주행 중 통신 끊김 여부 및 차상-지상 간 통신 품질 성과표 작성 표준 적용</t>
         </is>
       </c>
-      <c r="K24" s="67" t="inlineStr">
+      <c r="K24" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9361,7 +9438,7 @@
 2) 주행 통신 검측: 차상-지상 간 CCTV 영상 전송 및 관제 데이터 무선 통신 품질 성과표 최종 확정</t>
         </is>
       </c>
-      <c r="M24" s="67" t="inlineStr">
+      <c r="M24" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9372,7 +9449,7 @@
 2) 주행 중 LTE-R 기지국 간 이동 시 핸드오버 성공률 100% 및 음성 무선 통화 끊김 0건을 검측하였는가?</t>
         </is>
       </c>
-      <c r="O24" s="67" t="inlineStr">
+      <c r="O24" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9443,7 +9520,7 @@
 2) 교육 교재 작성, 시스템 운용/장해 조치 실습 및 교육 이수 확인서 작성 표준 적용</t>
         </is>
       </c>
-      <c r="K25" s="67" t="inlineStr">
+      <c r="K25" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9454,7 +9531,7 @@
 2) 교육 이수 확정: 현장 실습 교육 수행, 질문/답변 점검 및 운영자 교육 참석 이수 확인서 최종 작성</t>
         </is>
       </c>
-      <c r="M25" s="67" t="inlineStr">
+      <c r="M25" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9465,7 +9542,7 @@
 2) 주요 장비 장애 시 대응할 수 있는 계통별 긴급 비상 조치 매뉴얼 교재를 편찬하였는가?</t>
         </is>
       </c>
-      <c r="O25" s="67" t="inlineStr">
+      <c r="O25" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9537,7 +9614,7 @@
 2) 사전점검 결과 보고서 작성 및 한국교통안전공단 제출 승인 표준 적용</t>
         </is>
       </c>
-      <c r="K26" s="67" t="inlineStr">
+      <c r="K26" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9548,7 +9625,7 @@
 2) 점검 결과 승인: 기술기준 부합 여부 사전 검증, 지적사항 조치 완료 및 한국교통안전공단 사전점검 보고서 제출</t>
         </is>
       </c>
-      <c r="M26" s="67" t="inlineStr">
+      <c r="M26" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9559,7 +9636,7 @@
 2) 발주처, 운영기관, 책임감리단 및 현장소장이 포함된 3자 합동 사전점검반을 조직하였는가?</t>
         </is>
       </c>
-      <c r="O26" s="67" t="inlineStr">
+      <c r="O26" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9632,7 +9709,7 @@
 2) LTE-R 무선 품질, 관제 데이터 전송률 및 시설물검증 합격 판정 표준 적용</t>
         </is>
       </c>
-      <c r="K27" s="67" t="inlineStr">
+      <c r="K27" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9643,7 +9720,7 @@
 2) 검증 결과 확정: LTE-R 무선망 수신강도, 데이터 전송 지연시간 실측 및 시설물검증시험 합격 판정</t>
         </is>
       </c>
-      <c r="M27" s="67" t="inlineStr">
+      <c r="M27" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9654,7 +9731,7 @@
 2) 전문기관인 한국교통안전공단으로부터 시설물검증시험계획 적격 승인을 수령하였는가?</t>
         </is>
       </c>
-      <c r="O27" s="67" t="inlineStr">
+      <c r="O27" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9729,7 +9806,7 @@
 2) 영업시운전 기간 중 통신 장애 0건 달성 및 시운전 완료 보고서 확정 표준 적용</t>
         </is>
       </c>
-      <c r="K28" s="67" t="inlineStr">
+      <c r="K28" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9740,7 +9817,7 @@
 2) 시운전 준공 확정: 영업시운전 기간 중 통신 장해 0건 달성 및 영업시운전 종합 결과 보고서 확정</t>
         </is>
       </c>
-      <c r="M28" s="78" t="inlineStr">
+      <c r="M28" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9751,7 +9828,7 @@
 2) 전 정거장 행선안내게시기(PIS) 도착 시각 및 열치 위치 안내 오송출 0건을 달성하였는가?</t>
         </is>
       </c>
-      <c r="O28" s="67" t="inlineStr">
+      <c r="O28" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9821,7 +9898,7 @@
 2) 관할 지자체(화성시 등) 제출 및 설치신고 수리증 발급 획득 표준 적용</t>
         </is>
       </c>
-      <c r="K29" s="67" t="inlineStr">
+      <c r="K29" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9832,7 +9909,7 @@
 2) 관할 관청 수리: 관할 지자체(화성시 등) 제출, 현장 서류 검토 수검 및 설치신고 수리증 발급 획득</t>
         </is>
       </c>
-      <c r="M29" s="67" t="inlineStr">
+      <c r="M29" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9843,7 +9920,7 @@
 2) 업체 Pool[적격 업체] 철도/트램 시공 및 영업운행 실적이 입증된 적격 업체 Pool을 검토하였는가?</t>
         </is>
       </c>
-      <c r="O29" s="67" t="inlineStr">
+      <c r="O29" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -9913,7 +9990,7 @@
 2) KCA(한국방송통신전파진흥원) 제출 및 무선국 개설허가서 획득 표준 적용</t>
         </is>
       </c>
-      <c r="K30" s="67" t="inlineStr">
+      <c r="K30" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -9924,7 +10001,7 @@
 2) 무선국 허가 획득: KCA(한국방송통신전파진흥원) 서류 심사 수검 및 무선국 개설허가서 최종 발급</t>
         </is>
       </c>
-      <c r="M30" s="67" t="inlineStr">
+      <c r="M30" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -9935,7 +10012,7 @@
 2) 본선 지상 기지국 안테나 설치 위치, 높이, 이득(dBi) 및 지향각 제원을 조사하였는가?</t>
         </is>
       </c>
-      <c r="O30" s="67" t="inlineStr">
+      <c r="O30" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -10005,7 +10082,7 @@
 2) 국가정보원/KISA 보안 적합성 검증 승인서 및 상호연동 시험 합격 표준 적용</t>
         </is>
       </c>
-      <c r="K31" s="67" t="inlineStr">
+      <c r="K31" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -10016,7 +10093,7 @@
 2) 보안 승인 획득: KISA/국가정보원 보안 적합성 검증 수검 및 상호운용성 검증 합격 승인서 획득</t>
         </is>
       </c>
-      <c r="M31" s="67" t="inlineStr">
+      <c r="M31" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -10027,7 +10104,7 @@
 2) 업체 Pool[적격 업체] 철도/트램 시공 및 영업운행 실적이 입증된 적격 업체 Pool을 검토하였는가?</t>
         </is>
       </c>
-      <c r="O31" s="67" t="inlineStr">
+      <c r="O31" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -10097,7 +10174,7 @@
 2) 관할 지자체 현장 검측 수검 및 정보통신 사용전검사 필증 획득 표준 적용</t>
         </is>
       </c>
-      <c r="K32" s="67" t="inlineStr">
+      <c r="K32" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -10108,7 +10185,7 @@
 2) 필증 발급 획득: 관할 지자체 정보통신 검측 공무원 현장 실측 수검 및 정보통신 사용전검사 필증 획득</t>
         </is>
       </c>
-      <c r="M32" s="67" t="inlineStr">
+      <c r="M32" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -10119,7 +10196,7 @@
 2) 정거장 승강장 및 관제동 배관 입상부 배관 씰링 및 네임택 표기 상태를 확인하였는가?</t>
         </is>
       </c>
-      <c r="O32" s="67" t="inlineStr">
+      <c r="O32" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -10189,7 +10266,7 @@
 2) 무선 전계강도 및 준공 상태 검사 합격 후 무선국 준공검사 합격증명서 획득 표준 적용</t>
         </is>
       </c>
-      <c r="K33" s="67" t="inlineStr">
+      <c r="K33" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -10200,7 +10277,7 @@
 2) 합격 증명 획득: 준공 실측 합격 판정 수검 및 KCA 무선국 준공검사 합격증명서 최종 발급 획득</t>
         </is>
       </c>
-      <c r="M33" s="67" t="inlineStr">
+      <c r="M33" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -10211,7 +10288,7 @@
 2) 개설허가서 사본, 기지국 시공 내역서 및 안테나 제원표 구비를 완료하였는가?</t>
         </is>
       </c>
-      <c r="O33" s="67" t="inlineStr">
+      <c r="O33" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -10518,7 +10595,7 @@
           <t>"전기공사업법, 전기사업법, 한국전기설비규정(KEC), 도로법(점용허가) 및 산업안전보건법 준수 여부를 1:1 검토한다."</t>
         </is>
       </c>
-      <c r="K2" s="72" t="inlineStr">
+      <c r="K2" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -10528,7 +10605,7 @@
           <t>본 지침서는 동탄트램 전기분야 사업 착공 전설계도서의 기술적·법적 적정성 검토 방법과현장 여건, 타공종 간섭, 공법·장비 시공성(Constructability) 검토 절차를 명확히 제시하여, 시공 위험 요소는 사전에 헷지(H...</t>
         </is>
       </c>
-      <c r="M2" s="72" t="inlineStr">
+      <c r="M2" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -10538,7 +10615,7 @@
           <t>본 체크리스트는 철도설계기준(KDS 47 00 00) 및 전기사업법에 의거하여,전기 분야 전반(송변전, 전력, 전차선, 배전, 접지, 인허가 등)에 대한 핵심 설계 적정성을 점검하고, 리스크(Risk) 헷지 및 기회(Oppo...</t>
         </is>
       </c>
-      <c r="O2" s="70" t="inlineStr">
+      <c r="O2" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -10610,7 +10687,7 @@
           <t>공정표 대비 노면전차 특수자재(전차선 강성가선, 변압기 등)의 공장 제작/조달 Lead Time을 사전 반영함.</t>
         </is>
       </c>
-      <c r="K3" s="72" t="inlineStr">
+      <c r="K3" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -10620,7 +10697,7 @@
           <t>본 지침서는 동탄트램 노면전차설비 공사 발주 전설계 및 현장 여건을 정밀 파악하고 8대 현실조건(자재 제작 Lead Time, 철도/경전철 시공 실적 Pool, 예비품, 시공중/후 운전 및 교육지원, 현장 자재창고 임대료, ...</t>
         </is>
       </c>
-      <c r="M3" s="72" t="inlineStr">
+      <c r="M3" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -10630,7 +10707,7 @@
           <t>본 체크리스트는 동탄트램 노면전차설비 공사 발주 착수 전8대 현실조건(자재 Lead Time, 시공 실적 Pool, 예비품, 시공중/후 교육 및 기술지원, 현장 자재창고 임대료, 가설 전원/용수/청소, 개통 후 상주 기술지원...</t>
         </is>
       </c>
-      <c r="O3" s="70" t="inlineStr">
+      <c r="O3" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -10692,7 +10769,7 @@
           <t>"정류기, 변압기, ESS 대형 기자재 반입 동선, 출입문 유효 폭/높이(H x W) 및 양중 훅 위치 실측 검증"</t>
         </is>
       </c>
-      <c r="K4" s="72" t="inlineStr">
+      <c r="K4" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -10702,7 +10779,7 @@
           <t>본 지침서는 동탄트램 전기분야 시공 착수 전자재 반입용 동선, 공동구/횡단관로/인입구 좌표, 전기 기능실 마감, 토목 공사용 매립 배관 검측 및 3D BIM 간섭 해소 절차를 명확히 제시하여, 콘크리트 구조체 타설 완료 후 ...</t>
         </is>
       </c>
-      <c r="M4" s="72" t="inlineStr">
+      <c r="M4" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -10712,7 +10789,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 시공 착수 전자재 반입용 동선, 변전실 개구부, 공동구/인입구 3D BIM 좌표, 전기 기능실 마감 및 토목 공사용 매립 배관의 적정성을 사전에 검측하여 구조체 타설 후 굴착/파쇄 재시공 충...</t>
         </is>
       </c>
-      <c r="O4" s="70" t="inlineStr">
+      <c r="O4" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -10778,7 +10855,7 @@
           <t>"신호, 통신, 기계, PSD 및 트램 차량 전력 공급 관로, 배선 용량 및 트레이 타공 누락 사항 정밀 추출"</t>
         </is>
       </c>
-      <c r="K5" s="72" t="inlineStr">
+      <c r="K5" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -10788,7 +10865,7 @@
           <t>전기분야와 타공종(신호, 통신, 기계, PSD, 트램 차량) 간 인터페이스 설계도서 상 누락 및 협의사항 도출, 관로/배선/트레이/인터록 신호선 사전 조율을 통해 재작업을 원천 예방함</t>
         </is>
       </c>
-      <c r="M5" s="72" t="inlineStr">
+      <c r="M5" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -10798,7 +10875,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 시공 착수 전전기분야와 타공종(신호, 통신, 기계, PSD, 트램 차량) 간 인터페이스 설계도서 상 누락 및 협의사항 도출, 관로/배선/트레이/인터록 신호선 사전 조율을 통해 재작업을 원천 ...</t>
         </is>
       </c>
-      <c r="O5" s="70" t="inlineStr">
+      <c r="O5" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -10859,7 +10936,7 @@
           <t>"SCADA RTU, 변전소 GIS, 정류기, ESS 릴레이 간 IEC 61850 및 Modbus 통신 핀 맵/신호 주소 1:1 검증"</t>
         </is>
       </c>
-      <c r="K6" s="72" t="inlineStr">
+      <c r="K6" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -10869,7 +10946,7 @@
           <t>전기설비(변압기, 정류기, ESS, GIS, SCADA RTU) 제작사 사양 사전 반영, 이종 제작사 간 통신 프로토콜(IEC 61850, Modbus) 핀 맵/제어 랙 치수 조율 및 제작사양서 확정</t>
         </is>
       </c>
-      <c r="M6" s="72" t="inlineStr">
+      <c r="M6" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -10879,7 +10956,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 시공 착수 전전기설비(변압기, 정류기, ESS, GIS, SCADA RTU) 제작사 사양 사전 반영, 이종 제작사 간 통신 프로토콜(IEC 61850, Modbus) 핀 맵/제어 랙 치수 조...</t>
         </is>
       </c>
-      <c r="O6" s="70" t="inlineStr">
+      <c r="O6" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -10945,7 +11022,7 @@
           <t>"지자체(수원시, 화성시) 도로교통관제 센터와 트램 우선신호 제어기 간 통신 인터페이스 및 연동 협의"</t>
         </is>
       </c>
-      <c r="K7" s="72" t="inlineStr">
+      <c r="K7" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -10955,7 +11032,7 @@
           <t>수원시/동탄 도로교통관제 트램 우선신호 연동, 트램관제실(OCC) SCADA MMI 심볼 표준화, 차단기/단로기/접지스위치 안전 인터록 Logic 및 유지보수자 편의 기능 사전 협의</t>
         </is>
       </c>
-      <c r="M7" s="72" t="inlineStr">
+      <c r="M7" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -10965,7 +11042,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 시공 착수 전수원시/동탄 도로교통관제 트램 우선신호 연동, 트램관제실(OCC) SCADA MMI 심볼 표준화, 차단기/단로기/접지스위치 안전 인터록 Logic 및 유지보수자 편의 기능 사전 ...</t>
         </is>
       </c>
-      <c r="O7" s="70" t="inlineStr">
+      <c r="O7" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -11026,7 +11103,7 @@
           <t>"감리/감독원 입회 품질검측계획서(ITP: Inspection &amp; Test Plan) 작성 및 Hold Point(필수정지점) / Witness Point(입회점) 구분 명시"</t>
         </is>
       </c>
-      <c r="K8" s="72" t="inlineStr">
+      <c r="K8" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -11036,7 +11113,7 @@
           <t>감리/감독원 품질검사(ITP/ITC) 항목 검토, Hold Point/Witness Point 입회점 구분 수립, 현장 계측기 교정성적서 관리 및 불합격 자재 48시간 내 반출 통제 수칙</t>
         </is>
       </c>
-      <c r="M8" s="72" t="inlineStr">
+      <c r="M8" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -11046,7 +11123,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 업무 이행에 대해감리/감독원 품질검사(ITP/ITC) 항목 검토, Hold Point/Witness Point 입회점 구분 수립, 현장 계측기 교정성적서 관리 및 불합격 자재 48시간 내 반...</t>
         </is>
       </c>
-      <c r="O8" s="70" t="inlineStr">
+      <c r="O8" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -11107,7 +11184,7 @@
           <t>"변압기, GIS, 정류기, ESS, 전차선 등 주요 전기자재 공장 제작 및 수급 소요 기간(Lead Time 30~60일)을 공정표와 사전 연동 통제"</t>
         </is>
       </c>
-      <c r="K9" s="72" t="inlineStr">
+      <c r="K9" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -11117,7 +11194,7 @@
           <t>현장 여건 및 공정을 기준으로 주요 자재 Lead Time(30~60일) 사전 발주 검증, 한국전기공사협회 기술자 자격 실물 대조, 고소작업차 안전검사합격증 확인 및 투입계획서 승인</t>
         </is>
       </c>
-      <c r="M9" s="81" t="inlineStr">
+      <c r="M9" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -11127,7 +11204,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 업무 이행에 대해현장 여건 및 공정을 기준으로 주요 자재 Lead Time(30~60일) 사전 발주 검증, 한국전기공사협회 기술자 자격 실물 대조, 고소작업차 안전검사합격증 확인 및 투입계획...</t>
         </is>
       </c>
-      <c r="O9" s="70" t="inlineStr">
+      <c r="O9" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -11188,7 +11265,7 @@
           <t>"관할 한전에 수전 용량 계산서, 건축허가서, 22.9kV 수전 단선도 첨부 전기사용신청서 제출(처리기간 1개월) 및 인수점 지중 맨홀 협의"</t>
         </is>
       </c>
-      <c r="K10" s="72" t="inlineStr">
+      <c r="K10" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -11198,7 +11275,7 @@
           <t>한전 22.9kV 수전 전기사용신청, 지자체 전기 공사계획신고, 도로점용허가(도로법 56조), 도로공사신고(도로교통법 69조) 및 KESC 사용전검사 인허가 To-Do List 추적 관리</t>
         </is>
       </c>
-      <c r="M10" s="72" t="inlineStr">
+      <c r="M10" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -11208,7 +11285,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 업무 이행에 대해한전 22.9kV 수전 전기사용신청, 지자체 전기 공사계획신고, 도로점용허가(도로법 56조), 도로공사신고(도로교통법 69조) 및 KESC 사용전검사 인허가 To-Do Lis...</t>
         </is>
       </c>
-      <c r="O10" s="70" t="inlineStr">
+      <c r="O10" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -11279,7 +11356,7 @@
           <t>"노반(궤도), 신호, 통신, 기계, PSD, 차량 인터페이스 및 3D BIM 공간 간섭을 전면 사전 검토한다."</t>
         </is>
       </c>
-      <c r="K11" s="72" t="inlineStr">
+      <c r="K11" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -11289,7 +11366,7 @@
           <t>본 지침서는 동탄트램 전기분야 실공사 착수 전본사, 현장, 협력사 및 토목/신호/차량 3자 협의체 구축 방법,3D BIM 공종 간섭 조율, 자재 반입 동선/야적장 확보, 타 프로젝트 하자사례 분석 및 안전/민원 Risk He...</t>
         </is>
       </c>
-      <c r="M11" s="72" t="inlineStr">
+      <c r="M11" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -11299,7 +11376,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 실공사 착수 전본사, 현장, 협력사 및 토목/신호/차량 3자 협의체를 구축하여 3D BIM 공종 간섭, 자재 반입 동선, 타 현장 하자사례 재발방지책 및 Risk Hedge 방안을 확정하기 ...</t>
         </is>
       </c>
-      <c r="O11" s="70" t="inlineStr">
+      <c r="O11" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -11361,7 +11438,7 @@
           <t>"변압기 용량, 정류기 정격, ESS 배터리 세부 기술사양서 검토 및 시방 규격 1:1 대조 파악"</t>
         </is>
       </c>
-      <c r="K12" s="72" t="inlineStr">
+      <c r="K12" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -11371,7 +11448,7 @@
           <t>전기설비(변압기, 정류기, ESS, GIS, SCADA) 공장 제작 착수 전 발주처 특기시방서 및 KDS 47 00 00 철도설계기준에 따른 상세 기술사양서 및 공장 제작 승인도면(Shop Drawing) 검토</t>
         </is>
       </c>
-      <c r="M12" s="72" t="inlineStr">
+      <c r="M12" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -11381,7 +11458,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 전기설비 제작 사양서 작성 / 승인 업무 이행에 대해전기설비(변압기, 정류기, ESS, GIS, SCADA) 공장 제작 착수 전 발주처 특기시방서 및 KDS 47 00 00 철도설계기준에 따...</t>
         </is>
       </c>
-      <c r="O12" s="70" t="inlineStr">
+      <c r="O12" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -11445,7 +11522,7 @@
           <t>"변전기기 반입, Cable Tray 설치, 전차선 지주 입립 시공 순서 및 3D BIM 공정 수립"</t>
         </is>
       </c>
-      <c r="K13" s="72" t="inlineStr">
+      <c r="K13" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -11455,7 +11532,7 @@
           <t>전기분야 공정별(변전소, 전차선, 케이블 포설) 상세 시공계획서 수립, 예정공정표(Critical Path) 검토, 시공 순서 및 안전/품질 관리대책 수립 후 감리단 공학적 승인 완수</t>
         </is>
       </c>
-      <c r="M13" s="72" t="inlineStr">
+      <c r="M13" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -11465,7 +11542,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 시공 계획 수립 / 승인 업무 이행에 대해전기분야 공정별(변전소, 전차선, 케이블 포설) 상세 시공계획서 수립, 예정공정표(Critical Path) 검토, 시공 순서 및 안전/품질 관리대책...</t>
         </is>
       </c>
-      <c r="O13" s="70" t="inlineStr">
+      <c r="O13" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -11528,7 +11605,7 @@
           <t>"제조사 공장등록증, 사업자등록증, ISO 품질인증서 및 유사 철도/트램 납품 실적 검증"</t>
         </is>
       </c>
-      <c r="K14" s="72" t="inlineStr">
+      <c r="K14" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -11538,7 +11615,7 @@
           <t>전기자재 공급원 자격 검증(KS/KC 인증, 공장등록증, 납품실적), 제조사 시험성적서 대조 및 공장 제작 승인도면(Shop Drawing) 감리단 적격 승인 수검</t>
         </is>
       </c>
-      <c r="M14" s="72" t="inlineStr">
+      <c r="M14" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -11548,7 +11625,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 자재공급원/기자재 제작도서 승인 업무 이행에 대해전기자재 공급원 자격 검증(KS/KC 인증, 공장등록증, 납품실적), 제조사 시험성적서 대조 및 공장 제작 승인도면(Shop Drawing) ...</t>
         </is>
       </c>
-      <c r="O14" s="70" t="inlineStr">
+      <c r="O14" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -11614,7 +11691,7 @@
           <t>"제작사 부품 조달 현황, 외함 판금/도장 및 내부 배선 조립 공정 공정표 100% 관리"</t>
         </is>
       </c>
-      <c r="K15" s="72" t="inlineStr">
+      <c r="K15" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -11624,7 +11701,7 @@
           <t>정류기, 변압기, ESS, GIS, SCADA 제작사 공장 공정 제작 관리 및 감리단/발주처 입회 공장시험(FAT: Factory Acceptance Test) 수행과 시험성적서 승인 완수</t>
         </is>
       </c>
-      <c r="M15" s="72" t="inlineStr">
+      <c r="M15" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -11634,7 +11711,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 전기설비 공정제작 / 제작사 공장검사 업무 이행에 대해정류기, 변압기, ESS, GIS, SCADA 제작사 공장 공정 제작 관리 및 감리단/발주처 입회 공장시험(FAT: Factory Acc...</t>
         </is>
       </c>
-      <c r="O15" s="70" t="inlineStr">
+      <c r="O15" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -11697,7 +11774,7 @@
           <t>"건축 변전실 구조물 완성도, 노반 궤도 시공 상태 및 전기 설치 간섭 여부 정밀 실측"</t>
         </is>
       </c>
-      <c r="K16" s="72" t="inlineStr">
+      <c r="K16" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -11707,7 +11784,7 @@
           <t>토목, 노반(궤도), 건축 선행 공정 완성도 실측, 변전실/개구부/공동구 간섭 점검, 자재 반입구 및 반입 동선 인수인계 합동 점검 수행</t>
         </is>
       </c>
-      <c r="M16" s="72" t="inlineStr">
+      <c r="M16" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -11717,7 +11794,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 본공사 전 선행공정 인수인계 점검 업무 이행에 대해토목, 노반(궤도), 건축 선행 공정 완성도 실측, 변전실/개구부/공동구 간섭 점검, 자재 반입구 및 반입 동선 인수인계 합동 점검 수행 관...</t>
         </is>
       </c>
-      <c r="O16" s="70" t="inlineStr">
+      <c r="O16" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -11780,7 +11857,7 @@
           <t>"장비 진입 경로 및 적치장 사전확인, 타분야 작업 일정 및 지상/지하 구조물 간섭 협의"</t>
         </is>
       </c>
-      <c r="K17" s="72" t="inlineStr">
+      <c r="K17" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -11790,7 +11867,7 @@
           <t>고소작업차, 케이블 포설차, 활선 작업 장비 현장 반입 동선/적치장 확인, 장비 Spec 및 안전검사필증 점검, 작업원 특별안전교육 실시</t>
         </is>
       </c>
-      <c r="M17" s="72" t="inlineStr">
+      <c r="M17" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -11800,7 +11877,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 장비반입 및 안전교육 업무 이행에 대해고소작업차, 케이블 포설차, 활선 작업 장비 현장 반입 동선/적치장 확인, 장비 Spec 및 안전검사필증 점검, 작업원 특별안전교육 실시 관련 실무 요소...</t>
         </is>
       </c>
-      <c r="O17" s="70" t="inlineStr">
+      <c r="O17" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -11863,7 +11940,7 @@
           <t>"자재 하차 통제 구획 설정, 크레인 양중 신호수 배치 및 자재 반입 동선 안전 확보"</t>
         </is>
       </c>
-      <c r="K18" s="72" t="inlineStr">
+      <c r="K18" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -11873,7 +11950,7 @@
           <t>전기자재 현장 반입 하차 위치/동선 통제, 승인된 자재공급원 일치 여부(Serial No., Serial Tag) 검수, 도면 규격 및 수량 1:1 대조 확인</t>
         </is>
       </c>
-      <c r="M18" s="72" t="inlineStr">
+      <c r="M18" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -11883,7 +11960,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 자재 반입 및 검수 업무 이행에 대해전기자재 현장 반입 하차 위치/동선 통제, 승인된 자재공급원 일치 여부(Serial No., Serial Tag) 검수, 도면 규격 및 수량 1:1 대조 ...</t>
         </is>
       </c>
-      <c r="O18" s="70" t="inlineStr">
+      <c r="O18" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -11946,7 +12023,7 @@
           <t>"감리/감독 협의를 통한 시공 샘플 대상 선정, 시험시공 수행 및 시공 기준서 확정"</t>
         </is>
       </c>
-      <c r="K19" s="72" t="inlineStr">
+      <c r="K19" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -11956,7 +12033,7 @@
           <t>변전소 수배전반, 정류기, ESS, 특고압반 및 정거장 전기실 기기 반입/설치, 시공 샘플 감리 협의 후 시험시공 및 도면 일치성 최종 검측</t>
         </is>
       </c>
-      <c r="M19" s="72" t="inlineStr">
+      <c r="M19" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -11966,7 +12043,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 전철전력설비 반입 및 설치 업무 이행에 대해변전소 수배전반, 정류기, ESS, 특고압반 및 정거장 전기실 기기 반입/설치, 시공 샘플 감리 협의 후 시험시공 및 도면 일치성 최종 검측 관련 ...</t>
         </is>
       </c>
-      <c r="O19" s="70" t="inlineStr">
+      <c r="O19" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -12029,7 +12106,7 @@
           <t>"한전 인수점 지중 맨홀부터 수전 전기실까지 Cable Tray 수평도 및 고정 행거 설치"</t>
         </is>
       </c>
-      <c r="K20" s="72" t="inlineStr">
+      <c r="K20" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -12039,7 +12116,7 @@
           <t>한전 책임분계점으로부터 수전 전기실까지 케이블 트레이 수평/수직 고정 설치, 특고압 케이블 포설 및 단말 접속, 절연저항/내전압 시험 완수</t>
         </is>
       </c>
-      <c r="M20" s="72" t="inlineStr">
+      <c r="M20" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -12049,7 +12126,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 수전용 케이블 트레이 및 케이블 포설 업무 이행에 대해한전 책임분계점으로부터 수전 전기실까지 케이블 트레이 수평/수직 고정 설치, 특고압 케이블 포설 및 단말 접속, 절연저항/내전압 시험 완...</t>
         </is>
       </c>
-      <c r="O20" s="70" t="inlineStr">
+      <c r="O20" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -12113,7 +12190,7 @@
           <t>"한국전기안전공사 KESC 사용전검사 합격 필증 수령 및 수전 사전 조건 완수"</t>
         </is>
       </c>
-      <c r="K21" s="72" t="inlineStr">
+      <c r="K21" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -12123,7 +12200,7 @@
           <t>KESC 사용전검사 합격증 수령, 전기가압계획 수립 및 한전 가입 요청, 수전 전 기기별 자체시험 수행 후 통신/신호/기계 공종별 단계적 전기공급(급전) 시행</t>
         </is>
       </c>
-      <c r="M21" s="72" t="inlineStr">
+      <c r="M21" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -12133,7 +12210,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 수전 및 전기공급(급전) 업무 이행에 대해KESC 사용전검사 합격증 수령, 전기가압계획 수립 및 한전 가입 요청, 수전 전 기기별 자체시험 수행 후 통신/신호/기계 공종별 단계적 전기공급(급...</t>
         </is>
       </c>
-      <c r="O21" s="70" t="inlineStr">
+      <c r="O21" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -12198,7 +12275,7 @@
           <t>"감리단 제출용 SCADA 종합연동시험 계획서, 포인트 맵 및 점검 절차서 작성"</t>
         </is>
       </c>
-      <c r="K22" s="72" t="inlineStr">
+      <c r="K22" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -12208,7 +12285,7 @@
           <t>책임감리단 입회하에 트램관제실(OCC)과 현장 변전소/정류기/ESS 기기 간 SCADA 원격 감시/제어/계측(DI/DO/AI/AO) 종합연동시험 수행 및 검측 승인</t>
         </is>
       </c>
-      <c r="M22" s="72" t="inlineStr">
+      <c r="M22" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -12218,7 +12295,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 종합연동시험(SCADA) 실시 업무 이행에 대해책임감리단 입회하에 트램관제실(OCC)과 현장 변전소/정류기/ESS 기기 간 SCADA 원격 감시/제어/계측(DI/DO/AI/AO) 종합연동시험...</t>
         </is>
       </c>
-      <c r="O22" s="70" t="inlineStr">
+      <c r="O22" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -12279,7 +12356,7 @@
           <t>"철도종합시험운행 시행지침 제6조에 따른 전기 공종별 시험 항목 및 절차서 확정"</t>
         </is>
       </c>
-      <c r="K23" s="72" t="inlineStr">
+      <c r="K23" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -12289,7 +12366,7 @@
           <t>철도종합시험운행 시행지침 제6조(공종별시험)에 의거하여 변전, 전차선, 전력 설비 공종별 절연, 보호계전기, 통전 시험을 정밀 수행하고 보고서 승인</t>
         </is>
       </c>
-      <c r="M23" s="72" t="inlineStr">
+      <c r="M23" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -12299,7 +12376,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 공종별 시험 업무 이행에 대해철도종합시험운행 시행지침 제6조(공종별시험)에 의거하여 변전, 전차선, 전력 설비 공종별 절연, 보호계전기, 통전 시험을 정밀 수행하고 보고서 승인 관련 실무 요...</t>
         </is>
       </c>
-      <c r="O23" s="70" t="inlineStr">
+      <c r="O23" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -12363,7 +12440,7 @@
           <t>"궤도 시공 정밀도 확인 및 트램 차량 건축한계(폭 3,600mm) 간섭 여부 레이저 실측"</t>
         </is>
       </c>
-      <c r="K24" s="72" t="inlineStr">
+      <c r="K24" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -12373,7 +12450,7 @@
           <t>노반/궤도 시공상태 점검, 트램 건축한계(폭 3,600mm) 검사, 전차선 750V DC 가압, 차량충전설비, 신호/통신 작동상태 합동 사전 점검 완수</t>
         </is>
       </c>
-      <c r="M24" s="72" t="inlineStr">
+      <c r="M24" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -12383,7 +12460,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 차량 투입 전 점검 업무 이행에 대해노반/궤도 시공상태 점검, 트램 건축한계(폭 3,600mm) 검사, 전차선 750V DC 가압, 차량충전설비, 신호/통신 작동상태 합동 사전 점검 완수 관...</t>
         </is>
       </c>
-      <c r="O24" s="70" t="inlineStr">
+      <c r="O24" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -12445,7 +12522,7 @@
           <t>"철도안전법 철도차량 형식승인 절차에 따른 본선 구간 전기-차량 시운전 계획 수립"</t>
         </is>
       </c>
-      <c r="K25" s="72" t="inlineStr">
+      <c r="K25" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -12455,7 +12532,7 @@
           <t>철도안전법 제26조(철도차량 형식승인)에 의거하여 본선 구간 트램 차량, 전차선 전력, 신호, 통신 시스템 간 인터페이스 시험 및 동력 성능 시운전 수행</t>
         </is>
       </c>
-      <c r="M25" s="72" t="inlineStr">
+      <c r="M25" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -12465,7 +12542,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 차량 시운전 업무 이행에 대해철도안전법 제26조(철도차량 형식승인)에 의거하여 본선 구간 트램 차량, 전차선 전력, 신호, 통신 시스템 간 인터페이스 시험 및 동력 성능 시운전 수행 관련 실...</t>
         </is>
       </c>
-      <c r="O25" s="70" t="inlineStr">
+      <c r="O25" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -12527,7 +12604,7 @@
           <t>"전기자재 제작사 작성 운영/유지보수 매뉴얼, 비상 조치 절차서 및 교육 교재 검토"</t>
         </is>
       </c>
-      <c r="K26" s="72" t="inlineStr">
+      <c r="K26" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -12537,7 +12614,7 @@
           <t>전기설비(변전, 전차선, SCADA, ESS) 제작사 취급 설명 매뉴얼 기반 운영사 및 관제 유지보수자 대상 이론/실습 교육 시행 및 교육 이수증 교부</t>
         </is>
       </c>
-      <c r="M26" s="72" t="inlineStr">
+      <c r="M26" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -12547,7 +12624,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 운영자 교육시행 업무 이행에 대해전기설비(변전, 전차선, SCADA, ESS) 제작사 취급 설명 매뉴얼 기반 운영사 및 관제 유지보수자 대상 이론/실습 교육 시행 및 교육 이수증 교부 관련 ...</t>
         </is>
       </c>
-      <c r="O26" s="70" t="inlineStr">
+      <c r="O26" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -12610,7 +12687,7 @@
           <t>"철도종합시험운행 시행지침 제8조에 의거, 발주처-운영자 합동 사전점검 계획서 수립"</t>
         </is>
       </c>
-      <c r="K27" s="72" t="inlineStr">
+      <c r="K27" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -12620,7 +12697,7 @@
           <t>철도종합시험운행 시행지침 제8조(사전점검)에 따라 발주처-운영자 합동 사전점검계획 수립, 시설물 검증 가능성 점검 후 7일 이내 한국교통안전공단 제출 완수</t>
         </is>
       </c>
-      <c r="M27" s="72" t="inlineStr">
+      <c r="M27" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -12630,7 +12707,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 사전점검 업무 이행에 대해철도종합시험운행 시행지침 제8조(사전점검)에 따라 발주처-운영자 합동 사전점검계획 수립, 시설물 검증 가능성 점검 후 7일 이내 한국교통안전공단 제출 완수 관련 실무...</t>
         </is>
       </c>
-      <c r="O27" s="70" t="inlineStr">
+      <c r="O27" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -12694,7 +12771,7 @@
           <t>"시설물검증시험계획을 운영자와 협의 수립하고 한국교통안전공단 전문기관 승인 수검"</t>
         </is>
       </c>
-      <c r="K28" s="72" t="inlineStr">
+      <c r="K28" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -12704,7 +12781,7 @@
           <t>철도종합시험운행 시행지침 제12조/제13조에 의거 시설물검증시험계획 전문기관 승인, 시설물 정상작동, 안전상태, 차량 운행 적합성 검증 후 7일 내 공단 제출</t>
         </is>
       </c>
-      <c r="M28" s="72" t="inlineStr">
+      <c r="M28" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -12714,7 +12791,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 시설물 검증시험 업무 이행에 대해철도종합시험운행 시행지침 제12조/제13조에 의거 시설물검증시험계획 전문기관 승인, 시설물 정상작동, 안전상태, 차량 운행 적합성 검증 후 7일 내 공단 제출...</t>
         </is>
       </c>
-      <c r="O28" s="70" t="inlineStr">
+      <c r="O28" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -12780,7 +12857,7 @@
           <t>"운영자-발주처 협의 영업시운전계획 수립, 국토부 전문기관(교통안전공단) 승인 완수"</t>
         </is>
       </c>
-      <c r="K29" s="72" t="inlineStr">
+      <c r="K29" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -12790,7 +12867,7 @@
           <t>철도종합시험운행 시행지침 제22조/제23조에 의거 영업시운전계획 수립/승인, 영업 조건 열차운행, 종사자 업무 숙달 검증 후 결과보고서 공단 제출 및 국토부 보고</t>
         </is>
       </c>
-      <c r="M29" s="72" t="inlineStr">
+      <c r="M29" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -12800,7 +12877,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 영업시운전 업무 이행에 대해철도종합시험운행 시행지침 제22조/제23조에 의거 영업시운전계획 수립/승인, 영업 조건 열차운행, 종사자 업무 숙달 검증 후 결과보고서 공단 제출 및 국토부 보고 ...</t>
         </is>
       </c>
-      <c r="O29" s="70" t="inlineStr">
+      <c r="O29" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -12861,7 +12938,7 @@
           <t>"관할 한국전력공사 제출용 전기사용신청서, 변전소 용량 계산서 및 위임장 작성"</t>
         </is>
       </c>
-      <c r="K30" s="72" t="inlineStr">
+      <c r="K30" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -12871,7 +12948,7 @@
           <t>관할 한국전력공사에 전기사용신청서, 건축허가서, 수전 도면 및 위임장 제출 수속(소요 기간 약 1개월 관리) 및 수전 합의 완수</t>
         </is>
       </c>
-      <c r="M30" s="72" t="inlineStr">
+      <c r="M30" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -12881,7 +12958,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 전기 사용신청 업무 이행에 대해관할 한국전력공사에 전기사용신청서, 건축허가서, 수전 도면 및 위임장 제출 수속(소요 기간 약 1개월 관리) 및 수전 합의 완수 관련 실무 요소를 100% 사전...</t>
         </is>
       </c>
-      <c r="O30" s="70" t="inlineStr">
+      <c r="O30" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -12942,7 +13019,7 @@
           <t>"전기사업법 시행규칙에 맞춘 공사계획서 및 전기설비 공사계획신고서 정밀 작성"</t>
         </is>
       </c>
-      <c r="K31" s="72" t="inlineStr">
+      <c r="K31" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -12952,7 +13029,7 @@
           <t>관할 한국전기안전공사에 전기 공사 착수 전 공사계획서, 기술자 자격증, 감리원 배치서 및 도면 제출 수속 완료</t>
         </is>
       </c>
-      <c r="M31" s="72" t="inlineStr">
+      <c r="M31" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -12962,7 +13039,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 공사계획신고 업무 이행에 대해관할 한국전기안전공사에 전기 공사 착수 전 공사계획서, 기술자 자격증, 감리원 배치서 및 도면 제출 수속 완료 관련 실무 요소를 100% 사전 검측하여 시공 하자...</t>
         </is>
       </c>
-      <c r="O31" s="70" t="inlineStr">
+      <c r="O31" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -13023,7 +13100,7 @@
           <t>"노면전차선로 지주, 강성 가선, 브래킷 수량조서 및 시공 승인도면(Shop Drawing) 작성"</t>
         </is>
       </c>
-      <c r="K32" s="72" t="inlineStr">
+      <c r="K32" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -13033,7 +13110,7 @@
           <t>한국전기철도기술협회에 차량 시운전 전까지 수량조서, 시공도면 및 시험성적서 제출(처리기간 15일)하여 적합성 검증 승인 완수</t>
         </is>
       </c>
-      <c r="M32" s="72" t="inlineStr">
+      <c r="M32" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -13043,7 +13120,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 노면전차선로 적합성 검증 업무 이행에 대해한국전기철도기술협회에 차량 시운전 전까지 수량조서, 시공도면 및 시험성적서 제출(처리기간 15일)하여 적합성 검증 승인 완수 관련 실무 요소를 100...</t>
         </is>
       </c>
-      <c r="O32" s="70" t="inlineStr">
+      <c r="O32" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -13117,7 +13194,7 @@
           <t>"전기설비 설치 완료 후 7일 전 사용전검사신청서, 감리배치서, 단선도, 자재성적서 제출"</t>
         </is>
       </c>
-      <c r="K33" s="72" t="inlineStr">
+      <c r="K33" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -13127,7 +13204,7 @@
           <t>전기사업법 제63조, 도로법 제56조, 도로교통법 제69조에 의거 한국전기안전공사 사용전검사(7일전 신청), 지자체 도로점용허가(2주전), 경찰서 도로공사신고(3일전) 통합 수검 완료</t>
         </is>
       </c>
-      <c r="M33" s="72" t="inlineStr">
+      <c r="M33" s="133" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -13137,7 +13214,7 @@
           <t>본 체크리스트는 동탄트램 전기분야 전기 사용전검사 (전력/전차선/송변전) 업무 이행에 대해전기사업법 제63조, 도로법 제56조, 도로교통법 제69조에 의거 한국전기안전공사 사용전검사(7일전 신청), 지자체 도로점용허가(2주전...</t>
         </is>
       </c>
-      <c r="O33" s="70" t="inlineStr">
+      <c r="O33" s="134" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -13461,7 +13538,7 @@
           <t>KDS 47 10 00 철도지반 설계기준 | 현장 가설 둔차선, 용지 경계 및 원지반 고저차 3D 레벨 현측 | 토공사 사전 현장 조사 보고서</t>
         </is>
       </c>
-      <c r="L2" s="17" t="inlineStr">
+      <c r="L2" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -13471,7 +13548,7 @@
           <t>1) 현장 가설 도로 및 용지 경계 현측 ➔ 2) 광학 레벨 원지반 고저차 측정 ➔ 3) 진입 도로 장애 요소 매핑 ➔ 4) 현장 조사 보고서 감리 제출</t>
         </is>
       </c>
-      <c r="N2" s="17" t="inlineStr">
+      <c r="N2" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -13481,7 +13558,7 @@
           <t>가설 도로 폭/구배 현측, 원지반 고저차 레벨 측량 및 3D BIM 도면 오차 점검 (현장 조사 보고서)</t>
         </is>
       </c>
-      <c r="P2" s="17" t="inlineStr">
+      <c r="P2" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -13555,7 +13632,7 @@
           <t>KCS 47 10 25 시방 검토 | 사전 토공 토사/암석 깎기 및 성토 시방 규정 | 발주처·감리·시공 3자 킥오프 결재</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -13565,7 +13642,7 @@
           <t>1) 사전 토공 시방 요구조건 분석 ➔ 2) 3D BIM 도면 깎기/성토 수량 검증 ➔ 3) 토공 리스크 예비비 수립 ➔ 4) 발주·감리·시공 3자 킥오프 결재</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -13575,7 +13652,7 @@
           <t>KCS 47 10 25 사전 토공 시방 검토, 토사/암석 깎기 수량 산출 및 3D BIM 간섭 zero (3자 킥오프 결재)</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -13649,7 +13726,7 @@
           <t>지하안전법 제23조 | 현장 지장물, 연약 지반 층후 및 사면 붕괴 위험 요소 추출 | 사전 토공 리스크 대책 승인</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -13659,7 +13736,7 @@
           <t>1) 지하 매설 지장물 &amp; 연약지반 현출 ➔ 2) 사면 붕괴 위험 구간 추출 ➔ 3) 흙막이 가설재 보강 수립 ➔ 4) 토공 리스크 대책서 감리 승인</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -13669,7 +13746,7 @@
           <t>지중 매설물 탐사, 연약 지반 층후 분석 및 사면 붕괴 위험 구간 흙막이 가설재 보강 수립</t>
         </is>
       </c>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="P4" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -13743,7 +13820,7 @@
           <t>건산법 상생협력 수칙 | 토공 전문 기술자 1:1 전담 배치 &amp; 3자 주간 소통 회의 | 일일 Safety TBM 100% 이행</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -13753,7 +13830,7 @@
           <t>1) 토공 전담 기술자 1:1 배치 ➔ 2) 3자 주간 소통 회의 개최 ➔ 3) 근로자 복지 지원 &amp; Safety TBM ➔ 4) One-Team 조직표 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -13763,7 +13840,7 @@
           <t>토공 전담 기술자 1:1 현장 배치, 발주·감리·시공 3자 주간 소통 회의 및 일일 Safety TBM/음주 측정</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="P5" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -13837,7 +13914,7 @@
           <t>도로교통법 제69조 | 동탄경찰서 교통안전 심의 및 우회 차선 설계 | 전담 신호수(2인 2조) &amp; LED 경광등 배치</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -13847,7 +13924,7 @@
           <t>1) 교통 우회 차선 &amp; 둔차선 도면 설계 ➔ 2) 동탄경찰서 도로점용 허가 ➔ 3) 전담 신호수(2인 2조) 배치 ➔ 4) 교통소통 대책서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -13857,7 +13934,7 @@
           <t>동탄경찰서 도로점용 허가, 가설 우회 차선 설계 및 전담 안전 신호수(2인 2조)/LED 경광등 배치</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P6" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -13931,7 +14008,7 @@
           <t>KCS 47 10 25 자재 시방 | 굴착 장비, 가설 펜스 및 배수관 자재 발주 승인 | 공인시험기관 성적표 수속</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -13941,7 +14018,7 @@
           <t>1) 굴착 장비 및 가설 펜스 자재 선정 ➔ 2) 공인시험기관 시험성적서 검수 ➔ 3) 자재 발주 신청서 제출 ➔ 4) 자재 반입 검수 통보서 결재</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -13951,7 +14028,7 @@
           <t>KCS 47 10 25 굴착 장비/가설재 자재 승인, 공인시험기관 시험성적서 검수 및 자재 반입 통보</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="P7" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -14021,7 +14098,7 @@
           <t>토지보상법 준수 | 미보상 사유지 경계 현출 및 가설 펜스(H=1.8m) 차단 | 3D 우회 토공 동선 마일스톤 연동</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -14031,7 +14108,7 @@
           <t>1) 미보상 사유지 경계 현출 ➔ 2) 가설 펜스(H=1.8m) 차단 ➔ 3) 3D 우회 토공 동선 수립 ➔ 4) 용지 보상 리스크 대책 감리 승인</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -14041,7 +14118,7 @@
           <t>미보상 사유지 경계 현출, 가설 펜스(H=1.8m) 차단 및 3D 우회 토공 동선 마일스톤 연동</t>
         </is>
       </c>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="P8" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -14115,7 +14192,7 @@
           <t>현장 통합 관리 지침 | 발주처·감리·지자체·시공사 4자 빅룸 회의 | 사전 토공 마일스톤 서명 결재</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -14125,7 +14202,7 @@
           <t>1) 4자(발주·감리·지자체·시공) 빅룸 결성 ➔ 2) 사전 토공 마일스톤 연동 ➔ 3) 간섭 리스크 즉시 해소 ➔ 4) 빅룸 회의록 4자 서명 완수</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -14135,7 +14212,7 @@
           <t>4자(발주·감리·지자체·시공) 빅룸 회의 결성, 사전 토공 마일스톤 연동 및 간섭 리스크 서명</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P9" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -14209,7 +14286,7 @@
           <t>도로법 및 환경영향평가법 | 지자체 도로점용 허가 및 비산먼지 발생신고 수속 | 법정 인허가 필증 수속</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -14219,7 +14296,7 @@
           <t>1) 지자체 도로/하천점용 허가서 작성 ➔ 2) 관련 부서 서류 제출 &amp; 심의 ➔ 3) 보증보험 증권 부착 ➔ 4) 법정 인허가 필증 감리 수속</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -14229,7 +14306,7 @@
           <t>지자체 도로/하천점용 허가서 접수, 비산먼지 발생사업 신고 필증 수속 및 보증보험 제출</t>
         </is>
       </c>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="P10" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -14303,7 +14380,7 @@
           <t>도로교통법 안전 수칙 | 경찰서 차선 점용 허가 및 가설 둔차선 도로 복구 이행 보증보험 | 교통대책 감리 승인</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -14313,7 +14390,7 @@
           <t>1) 경찰서 차선 점용 허가증 수령 ➔ 2) 도로 복구 보증보험 증권 제출 ➔ 3) 전담 신호수 &amp; LED 경광등 배치 ➔ 4) 교통대책서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -14323,7 +14400,7 @@
           <t>동탄경찰서 차선 점용 허가, 도로 복구 이행 보증보험 제출 및 전담 신호수(2인 2조) 100% 배치</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="P11" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -14397,7 +14474,7 @@
           <t>지하안전관리에 관한 특별법 | GPR 3D 관로 탐사 &amp; 인력 시탐 줄파기(깊이 1.5m) | 점용기관 현장 입회 이설 방호</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -14407,7 +14484,7 @@
           <t>1) GPR 3D 지중 관로 탐사 ➔ 2) 인력 시탐 줄파기(깊이 1.5m) ➔ 3) 관할 점용기관 1:1 현장 입회 ➔ 4) 매달기 방호 &amp; 지장물 서면 승인</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -14417,7 +14494,7 @@
           <t>GPR 3D 관로 탐사, 인력 시탐 줄파기(폭 0.5m, 깊이 1.5m) 및 점용기관 1:1 현장 입회 매달기 방호</t>
         </is>
       </c>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="P12" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -14491,7 +14568,7 @@
           <t>국유재산법 및 공유재산법 | 토지 기공승낙서 인허가 확인 및 진입로 점용 범위 실측 | 토지 사용 승인서 결재</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -14501,7 +14578,7 @@
           <t>1) 국유지/공유지 기공승낙서 수속 ➔ 2) 진입 도로 점용 범위 실측 ➔ 3) 토지 소유주 사용 협의 ➔ 4) 기공승낙서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="N13" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -14511,7 +14588,7 @@
           <t>국유지/공유지 기공승낙서 인허가 검증, 진입 도로 점용 범위 실측 및 토지 사용 승인서 결재</t>
         </is>
       </c>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="P13" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -14585,7 +14662,7 @@
           <t>소음진동관리법 준수 | 야간 공사 소음 방음벽(H=3m) 및 세륜기(깊이 1.2m) 가동 | 단수/단전 주민 사전 안내</t>
         </is>
       </c>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="L14" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -14595,7 +14672,7 @@
           <t>1) 야간 공사 소음 방음벽(H=3m) 설치 ➔ 2) 세륜기 가동 &amp; 분무 살수 ➔ 3) 단수/단전 사전 주민 공지 ➔ 4) 민원 대응반 서면 승인</t>
         </is>
       </c>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="N14" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -14605,7 +14682,7 @@
           <t>야간 공사 소음 방음벽(H=3m) 가동, 세륜기(깊이 1.2m) 가동 및 단수/단전 주민 사전 고지</t>
         </is>
       </c>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="P14" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -14679,7 +14756,7 @@
           <t>토지보상법 준수 | 지장물 이설 부지 용지보상 현황 및 점용 경계 실측 | 미보상 사유지 가설 펜스 차단</t>
         </is>
       </c>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="L15" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -14689,7 +14766,7 @@
           <t>1) 미보상 필지 현출 &amp; 지적 대조 ➔ 2) 가설 펜스(H=1.8m) 차단 ➔ 3) 우회 토공 동선 수립 ➔ 4) 용지 보상 대책서 감리 승인</t>
         </is>
       </c>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="N15" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -14699,7 +14776,7 @@
           <t>미보상 필지 지적 대조, 경계 가설 펜스(H=1.8m) 차단 및 우회 토공 동선 서면 승인</t>
         </is>
       </c>
-      <c r="P15" s="17" t="inlineStr">
+      <c r="P15" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -14773,7 +14850,7 @@
           <t>건진법 시행령 제89조 | 사전 토공 시공계획서 표준 8대 목차 검토 | 착공 14일 전 감리 서면 승인</t>
         </is>
       </c>
-      <c r="L16" s="17" t="inlineStr">
+      <c r="L16" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -14783,7 +14860,7 @@
           <t>1) 사전 토공 시공계획서 작성 ➔ 2) 8대 목차 &amp; KCS 수치 명시 ➔ 3) 착공 14일 전 감리단 제출 ➔ 4) 시공계획서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N16" s="17" t="inlineStr">
+      <c r="N16" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -14793,7 +14870,7 @@
           <t>사전 토공 시공계획서 표준 8대 목차, KCS 수치 수록 및 착공 14일 전 감리 서면 승인</t>
         </is>
       </c>
-      <c r="P16" s="17" t="inlineStr">
+      <c r="P16" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -14867,7 +14944,7 @@
           <t>KCS 47 10 25 토공 시방 | 깎기/성토 토공 유동표 작성 및 3D BIM 도면 대조 | 책임감리원 최종 승인</t>
         </is>
       </c>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="L17" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -14877,7 +14954,7 @@
           <t>1) 토공 깎기/성토 유동표 작성 ➔ 2) 3D BIM 모델 표고 대조 ➔ 3) 사면 안성성 계산서 부착 ➔ 4) 토공 시공계획서 감리 최종 결재</t>
         </is>
       </c>
-      <c r="N17" s="17" t="inlineStr">
+      <c r="N17" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -14887,7 +14964,7 @@
           <t>토공 깎기/성토 유동표 작성, 3D BIM 모델 표고 대조 및 사면 안전성 계산서 감리 결재</t>
         </is>
       </c>
-      <c r="P17" s="17" t="inlineStr">
+      <c r="P17" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -14961,7 +15038,7 @@
           <t>건진법 설계변경 수칙 | 궤도/구조물 후행 공종 요구 표고 오차(±10mm) 반영 | 설계변경 실정보고서 작성</t>
         </is>
       </c>
-      <c r="L18" s="17" t="inlineStr">
+      <c r="L18" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -14971,7 +15048,7 @@
           <t>1) 궤도/구조물 후행 요구 조건 수집 ➔ 2) 마무리면 표고 오차(±10mm) 반영 ➔ 3) 설계변경 실정보고서 작성 ➔ 4) 책임감리원 기술 승인</t>
         </is>
       </c>
-      <c r="N18" s="17" t="inlineStr">
+      <c r="N18" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -14981,7 +15058,7 @@
           <t>궤도/구조물 후행 요구 조건 반영, 마무리면 표고 오차(±10mm) 반영 및 설계변경 실정보고</t>
         </is>
       </c>
-      <c r="P18" s="17" t="inlineStr">
+      <c r="P18" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -15055,7 +15132,7 @@
           <t>지방계약법 정산 수칙 | 착수 전 토종 변경 및 수량 증감 실정보고 작성 | 총사업비 변경 승인 수속</t>
         </is>
       </c>
-      <c r="L19" s="17" t="inlineStr">
+      <c r="L19" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -15065,7 +15142,7 @@
           <t>1) 토질 변경 &amp; 수량 증감 실정보고 작성 ➔ 2) 단가 비교표 작성 ➔ 3) 설계변경 도서 제출 ➔ 4) 총사업비 변경 승인 결재</t>
         </is>
       </c>
-      <c r="N19" s="17" t="inlineStr">
+      <c r="N19" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -15075,7 +15152,7 @@
           <t>토질 변경 &amp; 수량 증감 실정보고서 작성, 단가 비교표 작성 및 총사업비 변경 승인 결재</t>
         </is>
       </c>
-      <c r="P19" s="17" t="inlineStr">
+      <c r="P19" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -15149,7 +15226,7 @@
           <t>건진법 설계변경 규정 | 수량 산출서 및 단가 비교표 작성 | 책임감리원 기술 검토 의견서 첨부</t>
         </is>
       </c>
-      <c r="L20" s="17" t="inlineStr">
+      <c r="L20" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -15159,7 +15236,7 @@
           <t>1) 변경 수량 산출서 정밀 집계 ➔ 2) 신규 단가 산정 서류 부착 ➔ 3) 감리단 기술 검토 수속 ➔ 4) 설계변경 제출 서면 결재</t>
         </is>
       </c>
-      <c r="N20" s="17" t="inlineStr">
+      <c r="N20" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -15169,7 +15246,7 @@
           <t>변경 수량 산출서 정밀 집계, 신규 단가 산정 서류 첨부 및 책임감리원 기술 검토 수속</t>
         </is>
       </c>
-      <c r="P20" s="17" t="inlineStr">
+      <c r="P20" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -15243,7 +15320,7 @@
           <t>도로교통법 안전 수칙 | 게이트 바리케이트, 야간 LED 경광등 부설 | 전담 안전 신호수(2인 2조) 100% 배치</t>
         </is>
       </c>
-      <c r="L21" s="17" t="inlineStr">
+      <c r="L21" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -15253,7 +15330,7 @@
           <t>1) 게이트 바리케이트 &amp; 경광등 부설 ➔ 2) 우회 차선 표지판 설치 ➔ 3) 전담 신호수(2인 2조) 배치 ➔ 4) 교통 안전 점검 대장 결재</t>
         </is>
       </c>
-      <c r="N21" s="17" t="inlineStr">
+      <c r="N21" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -15263,7 +15340,7 @@
           <t>게이트 바리케이트/LED 경광등 설치, 우회 차선 표지판 검측 및 전담 신호수(2인 2조) 배치</t>
         </is>
       </c>
-      <c r="P21" s="17" t="inlineStr">
+      <c r="P21" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -15337,7 +15414,7 @@
           <t>건설기계관리법 제13조 | 자중 10t+ 굴착기, 덤프 정기검사증 검수 | 후방 센서 점검 및 반입 허가</t>
         </is>
       </c>
-      <c r="L22" s="17" t="inlineStr">
+      <c r="L22" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -15347,7 +15424,7 @@
           <t>1) 10t+ 굴착기/덤프 사양 검수 ➔ 2) 건설기계 정기검사증 점검 ➔ 3) 후방 카메라/경보음 시동 점검 ➔ 4) 장비 반입 승인서 감리 결재</t>
         </is>
       </c>
-      <c r="N22" s="17" t="inlineStr">
+      <c r="N22" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -15357,7 +15434,7 @@
           <t>자중 10t+ 굴착기/덤프 정기검사증, 후방 카메라/경보음 시동 점검 및 반입 허가 결재</t>
         </is>
       </c>
-      <c r="P22" s="17" t="inlineStr">
+      <c r="P22" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -15431,7 +15508,7 @@
           <t>KCS 47 10 25 산림 벌목 시방 | 수목 벌목 및 뿌리 제거(벌근) 깊이 30cm 이상 | 임목 폐기물 수속 처리</t>
         </is>
       </c>
-      <c r="L23" s="17" t="inlineStr">
+      <c r="L23" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -15441,7 +15518,7 @@
           <t>1) 현장 지반 수목 벌목 시행 ➔ 2) 뿌리 제거(벌근) 깊이 30cm 굴착 ➔ 3) 임목 폐기물 수속 처리 ➔ 4) 벌목 벌근 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N23" s="17" t="inlineStr">
+      <c r="N23" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -15451,7 +15528,7 @@
           <t>현장 수목 벌목 시행, 뿌리 제거(벌근) 깊이 30cm 이상 굴착 및 임목 폐기물 수속 처리</t>
         </is>
       </c>
-      <c r="P23" s="17" t="inlineStr">
+      <c r="P23" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -15525,7 +15602,7 @@
           <t>폐기물관리법 준수 | 기존 아스콘/콘크리트 구조물 안전 삭평 철거 | 건설 폐기물 성적표 수속</t>
         </is>
       </c>
-      <c r="L24" s="17" t="inlineStr">
+      <c r="L24" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -15535,7 +15612,7 @@
           <t>1) 기존 아스콘/콘크리트 삭평 철거 ➔ 2) 폐기물 분리 수거 &amp; 적재 ➔ 3) 건설 폐기물 위탁 처리 ➔ 4) 지장물 처리 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N24" s="17" t="inlineStr">
+      <c r="N24" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -15545,7 +15622,7 @@
           <t>기존 아스콘/콘크리트 삭평 철거, 건설 폐기물 분리 수거 적재 및 폐기물 성적서 수속</t>
         </is>
       </c>
-      <c r="P24" s="17" t="inlineStr">
+      <c r="P24" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -15619,7 +15696,7 @@
           <t>KCS 47 10 25 가설 도로 | 덤프트럭 진입 가설 도로 폭 6m 포설 | 쇄석 골재(두께 20cm) 부설 &amp; 살수</t>
         </is>
       </c>
-      <c r="L25" s="17" t="inlineStr">
+      <c r="L25" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -15629,7 +15706,7 @@
           <t>1) 가설 도로 폭 6m 성토 굴착 ➔ 2) 쇄석 골재(두께 20cm) 부설 ➔ 3) 10t 롤러 다짐 &amp; 살수 ➔ 4) 진입로 조성 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N25" s="17" t="inlineStr">
+      <c r="N25" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -15639,7 +15716,7 @@
           <t>가설 도로 폭 6m 성토 굴착, 쇄석 골재(두께 20cm) 부설, 10t 롤러 다짐 및 살수 점검</t>
         </is>
       </c>
-      <c r="P25" s="17" t="inlineStr">
+      <c r="P25" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -15713,7 +15790,7 @@
           <t>KCS 47 10 25 배수 시방 | 가배수로(0.6×0.6m) &amp; 가침사지 설치 | 세륜기(깊이 1.2m) 가동 및 배수 검측</t>
         </is>
       </c>
-      <c r="L26" s="17" t="inlineStr">
+      <c r="L26" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -15723,7 +15800,7 @@
           <t>1) 가배수로(0.6×0.6m) &amp; 가침사지 터파기 ➔ 2) 세륜기(깊이 1.2m) 부설 ➔ 3) 양수 펌프 비치 ➔ 4) 배수 환경 시설 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N26" s="17" t="inlineStr">
+      <c r="N26" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -15733,7 +15810,7 @@
           <t>가배수로(0.6×0.6m) &amp; 가침사지 설치, 세륜기(깊이 1.2m) 가동 및 수중 양수 펌프 비치</t>
         </is>
       </c>
-      <c r="P26" s="17" t="inlineStr">
+      <c r="P26" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -15807,7 +15884,7 @@
           <t>KCS 47 10 25 굴착 규정 | 3D GPS 굴착기 표고 오차 ±20mm 통제 | 사면 비탈면 경사(1:1.5) 준수</t>
         </is>
       </c>
-      <c r="L27" s="17" t="inlineStr">
+      <c r="L27" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -15817,7 +15894,7 @@
           <t>1) 3D GPS 굴착기 정밀 세팅 ➔ 2) 토사 깎기 &amp; 사면 비탈면(1:1.5) 굴착 ➔ 3) 표고 오차(±20mm) 검측 ➔ 4) 토공 굴착 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N27" s="17" t="inlineStr">
+      <c r="N27" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -15827,7 +15904,7 @@
           <t>3D GPS 굴착기 표고 오차 ±20mm 통제, 사면 비탈면 경사(1:1.5 이하) 준수 및 굴착 검측</t>
         </is>
       </c>
-      <c r="P27" s="17" t="inlineStr">
+      <c r="P27" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -15901,7 +15978,7 @@
           <t>KS F 2310 규정 준수 | 굴착 바닥 원지반 평판재하시험 K30 ≥ 70 MN/m³ | 덤프트럭 펌핑 연약 지반 점검</t>
         </is>
       </c>
-      <c r="L28" s="17" t="inlineStr">
+      <c r="L28" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -15911,7 +15988,7 @@
           <t>1) 굴착 바닥 원지반 수평 정리 ➔ 2) K30 평판재하시험(≥70 MN/m³) ➔ 3) 덤프트럭 펌핑 연약 지반 점검 ➔ 4) 노상토 지지력 성과표 승인</t>
         </is>
       </c>
-      <c r="N28" s="17" t="inlineStr">
+      <c r="N28" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -15921,7 +15998,7 @@
           <t>굴착 바닥 평판재하시험 K30 ≥ 70 MN/m³, 덤프트럭 펌핑 연약 지반 점검 및 노상토 승인</t>
         </is>
       </c>
-      <c r="P28" s="17" t="inlineStr">
+      <c r="P28" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -15995,7 +16072,7 @@
           <t>KCS 47 10 25 성토 시방 | 층두께 ≤ 30cm 토사 포설 | 10t 강동 롤러 다짐(들밀도 다짐도 ≥ 90%)</t>
         </is>
       </c>
-      <c r="L29" s="17" t="inlineStr">
+      <c r="L29" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -16005,7 +16082,7 @@
           <t>1) 성토 토사 30cm 층포설 ➔ 2) 살수차 최적함수비 살수 ➔ 3) 10t 강동 롤러 다짐(다짐도≥90%) ➔ 4) 성토 다짐 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N29" s="17" t="inlineStr">
+      <c r="N29" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -16015,7 +16092,7 @@
           <t>성토 토사 30cm 층포설, 살수차 최적함수비 OMC 살수 및 10t 롤러 다짐(다짐도 ≥ 90%)</t>
         </is>
       </c>
-      <c r="P29" s="17" t="inlineStr">
+      <c r="P29" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -16089,7 +16166,7 @@
           <t>현장 통합 소통 수칙 | 일일 TBM 및 품질/안전 지원 대장 수록 | 감리 입회 검측 서면 승인</t>
         </is>
       </c>
-      <c r="L30" s="17" t="inlineStr">
+      <c r="L30" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -16099,7 +16176,7 @@
           <t>1) 일일 현장 품질/안전 지원 ➔ 2) TBM 및 근로자 교육 ➔ 3) 공정 장애 요소 해소 ➔ 4) 현장 지원 대장 서면 승인</t>
         </is>
       </c>
-      <c r="N30" s="17" t="inlineStr">
+      <c r="N30" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -16109,7 +16186,7 @@
           <t>일일 현장 품질/안전 지원 대장, TBM 및 근로자 교육 시행 서면 승인</t>
         </is>
       </c>
-      <c r="P30" s="17" t="inlineStr">
+      <c r="P30" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -16183,7 +16260,7 @@
           <t>KCS 47 10 25 인계인수 수칙 | 토공-강화노반 시공팀 3자 합동 레벨 측량 | 마무리면 인계인수서 서명</t>
         </is>
       </c>
-      <c r="L31" s="17" t="inlineStr">
+      <c r="L31" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -16193,7 +16270,7 @@
           <t>1) 토공-강화노반 시공팀 3자 합동 현측 ➔ 2) 마무리면 레벨 오차(±10mm) 확인 ➔ 3) 인계인수 합의서 서명 ➔ 4) 토공 마무리면 인계 완료</t>
         </is>
       </c>
-      <c r="N31" s="17" t="inlineStr">
+      <c r="N31" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -16203,7 +16280,7 @@
           <t>토공-강화노반 시공팀 3자 합동 레벨 측량, 마무리면 레벨 오차(±10mm) 인계인수서 서명</t>
         </is>
       </c>
-      <c r="P31" s="17" t="inlineStr">
+      <c r="P31" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -16498,7 +16575,7 @@
           <t>발주처 기본계획 사전 검토 | 발주처 기본계획 보고서</t>
         </is>
       </c>
-      <c r="M2" s="101" t="inlineStr">
+      <c r="M2" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -16508,7 +16585,7 @@
           <t>• 조사설계 용역 기본계획 도서 확보 여부 확인 • 핵심이슈 (미시추 사유, 지층/암반등급 조정여부 등) 확보 여부 확인 • 사업지 연접 지질/지반조사 자료 확보 여부 확인</t>
         </is>
       </c>
-      <c r="O2" s="101" t="inlineStr">
+      <c r="O2" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -16518,7 +16595,7 @@
           <t>1) 발주처 계획 입수(비공식) 적정성을 확인하였는가? 2) 발주처 기본계획 보고서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q2" s="101" t="inlineStr">
+      <c r="Q2" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -16586,7 +16663,7 @@
           <t>입수된 발주정보 평가를 통한 관심 Project 선정 | 관심사업 List</t>
         </is>
       </c>
-      <c r="M3" s="107" t="inlineStr">
+      <c r="M3" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -16596,7 +16673,7 @@
           <t>• 해당 프로젝트별 발주처/경쟁동향 / 사업성평가 수행 • 기술형입찰 입찰참여 Guide Line으로 해당 프로젝트 평가</t>
         </is>
       </c>
-      <c r="O3" s="107" t="inlineStr">
+      <c r="O3" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -16606,7 +16683,7 @@
           <t>1) 관심프로젝트 선정 적정성을 확인하였는가? 2) 관심사업 List 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q3" s="107" t="inlineStr">
+      <c r="Q3" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -16674,7 +16751,7 @@
           <t>발주처 지반조사 수립업체 파악 | 발주처 기본계획 수행 List + Contact Point List</t>
         </is>
       </c>
-      <c r="M4" s="101" t="inlineStr">
+      <c r="M4" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -16684,7 +16761,7 @@
           <t>• 발주처 지반조사업체 확인 후 당사 Pool List와 비교 • 발주처 지반조사 업체 확인팀 Contact Point 확보</t>
         </is>
       </c>
-      <c r="O4" s="101" t="inlineStr">
+      <c r="O4" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -16694,7 +16771,7 @@
           <t>1) 발주처 지반조사 모니터링 적정성을 확인하였는가? 2) 발주처 기본계획 수행 List + Contact Point List 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q4" s="101" t="inlineStr">
+      <c r="Q4" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -16762,7 +16839,7 @@
           <t>지반조사 품질향상을 위한 제3자 검증 수행 지반조사 전문가 Pool 관리 | 외부지질전문가 Pool List</t>
         </is>
       </c>
-      <c r="M5" s="107" t="inlineStr">
+      <c r="M5" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -16772,7 +16849,7 @@
           <t>• Academic 전문가와 현장 전문가를 포함한 Pool 구성 • 전문가 Pool의 학력/기술사 등 경력사항(조사 15년) 확인</t>
         </is>
       </c>
-      <c r="O5" s="107" t="inlineStr">
+      <c r="O5" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -16782,7 +16859,7 @@
           <t>1) 외부 지질전문가 Pool 관리 적정성을 확인하였는가? 2) 외부지질전문가 Pool List 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q5" s="107" t="inlineStr">
+      <c r="Q5" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -16853,7 +16930,7 @@
           <t>발주처 계획 대응 및 개략 지반조사 결과 사전 예측을 위한 업체 관리 | 조사업체 POOL/필요시 Update</t>
         </is>
       </c>
-      <c r="M6" s="101" t="inlineStr">
+      <c r="M6" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -16863,7 +16940,7 @@
           <t>• 공공기관별 입찰공고 모니터링 통한 지반조사업체 입찰참여 유치(입찰 공사 여부 확인) • 업체 Pool List 갱신 여부 확인 • 지반조사업체 역량 및 기술수준 평가표 평가 여부 확인 (Pool 갱신 및 신규업체...</t>
         </is>
       </c>
-      <c r="O6" s="101" t="inlineStr">
+      <c r="O6" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -16873,7 +16950,7 @@
           <t>1) 지반조사 Pool 관리 적정성을 확인하였는가? 2) 조사업체 POOL/필요시 Update 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q6" s="101" t="inlineStr">
+      <c r="Q6" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -16940,7 +17017,7 @@
           <t>발주처 기본계획 및 지반조사 결과 사전 획득 | 발주처 기본계획 보고서 및 지반조사 보고서(비공식)</t>
         </is>
       </c>
-      <c r="M7" s="107" t="inlineStr">
+      <c r="M7" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -16950,7 +17027,7 @@
           <t>• 기본계획 지반조사결과 및 실시설계 Contact을 통한 자료입수</t>
         </is>
       </c>
-      <c r="O7" s="107" t="inlineStr">
+      <c r="O7" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -16960,7 +17037,7 @@
           <t>1) 기본계획 지반조사 자료 및 R/O 정보 입수 적정성을 확인하였는가? 2) 발주처 기본계획 보고서 및 지반조사 보고서(비공식) 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q7" s="107" t="inlineStr">
+      <c r="Q7" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17030,7 +17107,7 @@
           <t>발주처 기본계획 지반조사 문제점 검토 | 기본계획 지반조사 검토서(설계, 공정, 기획)</t>
         </is>
       </c>
-      <c r="M8" s="101" t="inlineStr">
+      <c r="M8" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17040,7 +17117,7 @@
           <t>• 시추조사 위치, 수량 적정성 검토 • 지질이상 구간 상세 조사 여부 및 적정성 검토 확인 • 미시추 구간 지반 특성 적정성 검토확인 (측점 검토, 위치 및 물량검토) • 인근 사업 지반조사자료 비교 통해 당사 지...</t>
         </is>
       </c>
-      <c r="O8" s="101" t="inlineStr">
+      <c r="O8" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17050,7 +17127,7 @@
           <t>1) 기본계획 지반조사 R/O 검토 (설계, 공정, 기획) 적정성을 확인하였는가? 2) 기본계획 지반조사 검토서(설계, 공정, 기획) 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q8" s="101" t="inlineStr">
+      <c r="Q8" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17117,7 +17194,7 @@
           <t>발주처 지반조사 문제점 R/O 분석 | 기본계획 지반조사 개략 검토서</t>
         </is>
       </c>
-      <c r="M9" s="107" t="inlineStr">
+      <c r="M9" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17127,7 +17204,7 @@
           <t>• 발주처 기본계획 지반조사 R/O별 Cost effect 분석</t>
         </is>
       </c>
-      <c r="O9" s="107" t="inlineStr">
+      <c r="O9" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17137,7 +17214,7 @@
           <t>1) 기본계획 지반조사 R/O 종합검토 (원가) 적정성을 확인하였는가? 2) 기본계획 지반조사 개략 검토서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q9" s="107" t="inlineStr">
+      <c r="Q9" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17204,7 +17281,7 @@
           <t>지반조사업체 Pool 내 최적의 업체 선정 | 지반조사 입찰 참여 Pool</t>
         </is>
       </c>
-      <c r="M10" s="101" t="inlineStr">
+      <c r="M10" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17214,7 +17291,7 @@
           <t>• 지반조사업체 Pool/실적 검토 및 공종별 적합성 정합 및 견적 본부 연계 검토</t>
         </is>
       </c>
-      <c r="O10" s="101" t="inlineStr">
+      <c r="O10" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17224,7 +17301,7 @@
           <t>1) 지반조사 업체 선정 적정성을 확인하였는가? 2) 지반조사 입찰 참여 Pool 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q10" s="101" t="inlineStr">
+      <c r="Q10" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17291,7 +17368,7 @@
           <t>지반조사업체 용역 계약 | 지반조사 용역 계약서</t>
         </is>
       </c>
-      <c r="M11" s="107" t="inlineStr">
+      <c r="M11" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17301,7 +17378,7 @@
           <t>• 일반구매시스템을 이용한 용역계약</t>
         </is>
       </c>
-      <c r="O11" s="107" t="inlineStr">
+      <c r="O11" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17311,7 +17388,7 @@
           <t>1) 지반조사 업체 계약 적정성을 확인하였는가? 2) 지반조사 용역 계약서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q11" s="107" t="inlineStr">
+      <c r="Q11" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17379,7 +17456,7 @@
           <t>프로젝트 정합에 부합하는 지반조사 항목 사전조사 수행, 위치 선정 | 지반조사 계획서</t>
         </is>
       </c>
-      <c r="M12" s="101" t="inlineStr">
+      <c r="M12" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17389,7 +17466,7 @@
           <t>• 현장답사 수행 • 공종별 실시설계에 준하여 수량 및 위치 검토</t>
         </is>
       </c>
-      <c r="O12" s="101" t="inlineStr">
+      <c r="O12" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17399,7 +17476,7 @@
           <t>1) 지반조사 항목, 수량 및 위치검토 적정성을 확인하였는가? 2) 지반조사 계획서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q12" s="101" t="inlineStr">
+      <c r="Q12" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17466,7 +17543,7 @@
           <t>지반조사 항목, 수량 및 위치 적정성 검토 | 지반조사계획 의견서</t>
         </is>
       </c>
-      <c r="M13" s="107" t="inlineStr">
+      <c r="M13" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17476,7 +17553,7 @@
           <t>• 지반조사 계획서 검토 및 검토</t>
         </is>
       </c>
-      <c r="O13" s="107" t="inlineStr">
+      <c r="O13" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17486,7 +17563,7 @@
           <t>1) 지반조사계획 적정성 심사의뢰 적정성을 확인하였는가? 2) 지반조사계획 의견서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q13" s="107" t="inlineStr">
+      <c r="Q13" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17555,7 +17632,7 @@
           <t>지반조사 수행을 위한 인허가 승인 | 인허가 서류</t>
         </is>
       </c>
-      <c r="M14" s="101" t="inlineStr">
+      <c r="M14" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17565,7 +17642,7 @@
           <t>• 산지일시사용 신고(사업계획서, 지형도, 산지일시사용예정실측도, 복구계획서, 복지봉투) • 굴착행위 신고(굴착행위신고서, 위치 또는 평면도, 원상복구계획서, 토지사용 승낙서) • 하천점용 허가(위치도, 이해관계인 ...</t>
         </is>
       </c>
-      <c r="O14" s="101" t="inlineStr">
+      <c r="O14" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17575,7 +17652,7 @@
           <t>1) 지반조사 인허가 적정성을 확인하였는가? 2) 인허가 서류 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q14" s="101" t="inlineStr">
+      <c r="Q14" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17643,7 +17720,7 @@
           <t>외부지질전문가 의견을 반영한 지반조사 계획 확정 | 지반조사 용역 계약서</t>
         </is>
       </c>
-      <c r="M15" s="107" t="inlineStr">
+      <c r="M15" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17653,7 +17730,7 @@
           <t>• 외부지질전문가 지반조사 의견 검토 • 입찰설계 지반조사 계획 보완</t>
         </is>
       </c>
-      <c r="O15" s="107" t="inlineStr">
+      <c r="O15" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17663,7 +17740,7 @@
           <t>1) 지반조사 항목, 수량 및 위치 보완 적정성을 확인하였는가? 2) 지반조사 용역 계약서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q15" s="107" t="inlineStr">
+      <c r="Q15" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17732,7 +17809,7 @@
           <t>과업구간 지반여건 상세 파악 | 지반조사 보고서, 시추 Core 및 샘플</t>
         </is>
       </c>
-      <c r="M16" s="101" t="inlineStr">
+      <c r="M16" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17742,7 +17819,7 @@
           <t>• 물리탐사 수행(전기 비저항, 탄성파탐사 등) • 시추조사 및 현장 시험 수행(공내재하시험, 실내전단시험 등) • 실내시험 수행(요동시험, 입도시험 등)</t>
         </is>
       </c>
-      <c r="O16" s="101" t="inlineStr">
+      <c r="O16" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17752,7 +17829,7 @@
           <t>1) 지반조사 수행 적정성을 확인하였는가? 2) 지반조사 보고서, 시추 Core 및 샘플 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q16" s="101" t="inlineStr">
+      <c r="Q16" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17822,7 +17899,7 @@
           <t>지반조사 결과 오류 및 지반정수의 적합성 검토 | 지반조사 결과 분석 의견서</t>
         </is>
       </c>
-      <c r="M17" s="107" t="inlineStr">
+      <c r="M17" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17832,7 +17909,7 @@
           <t>• 입찰설계 지반조사 보고서 검토 • 시추조사 위치 및 심도의 적정성 검토 • 실내시험 결과 등급 적정성 검토 • 실시설계시 추가지반조사 필요구간 검토</t>
         </is>
       </c>
-      <c r="O17" s="107" t="inlineStr">
+      <c r="O17" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17842,7 +17919,7 @@
           <t>1) 지반조사 수렴 결과 분석 적정성을 확인하였는가? 2) 지반조사 결과 분석 의견서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q17" s="107" t="inlineStr">
+      <c r="Q17" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17911,7 +17988,7 @@
           <t>입찰설계 지반조사 결과에 따른 직분야 R/O 및 Cost impact 반영 사항 검토 | 입찰설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
         </is>
       </c>
-      <c r="M18" s="101" t="inlineStr">
+      <c r="M18" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -17921,7 +17998,7 @@
           <t>• 입찰설계 지반조사 결과 분석을 통한 원가 및 공정 영향 검토 • 미시추 구간 평가 및 공정 Risk 반영 사항 검토 • 지반조건을 고려한 발파공법성 여부 검토</t>
         </is>
       </c>
-      <c r="O18" s="101" t="inlineStr">
+      <c r="O18" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -17931,7 +18008,7 @@
           <t>1) 입찰설계 지반조사 R/O 검토 (설계, 원가, 공정, 기타) 적정성을 확인하였는가? 2) 입찰설계 지반조사 검토서(설계, 원가, 공정, 기타) 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q18" s="101" t="inlineStr">
+      <c r="Q18" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -17999,7 +18076,7 @@
           <t>원가 및 공정 검토 결과에 따른 입찰설계 R/O 최종 확정 | 입찰설계 R/O 검토서</t>
         </is>
       </c>
-      <c r="M19" s="107" t="inlineStr">
+      <c r="M19" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18009,7 +18086,7 @@
           <t>• 입찰설계 지반조사 R/O별 Cost effect 분석 • 유사사업 L/L 분석, R/P 검토를 통한 실시설계시 고려사항 검토</t>
         </is>
       </c>
-      <c r="O19" s="107" t="inlineStr">
+      <c r="O19" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18019,7 +18096,7 @@
           <t>1) 지반조사 결과 R/O 종합검토 적정성을 확인하였는가? 2) 입찰설계 R/O 검토서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q19" s="107" t="inlineStr">
+      <c r="Q19" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18088,7 +18165,7 @@
           <t>REM 차트 작성(회사의 Core Risk, T/C 공정검토 결과, 경쟁사 동향, 발주 경향) 및 보고 | REM 회의록</t>
         </is>
       </c>
-      <c r="M20" s="101" t="inlineStr">
+      <c r="M20" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18098,7 +18175,7 @@
           <t>• Risk Profiling/Merge 방안 검토 • 공정 착공성 검토 및 T/C 검토 • 설계차별화 및 Idea Frame 검토</t>
         </is>
       </c>
-      <c r="O20" s="101" t="inlineStr">
+      <c r="O20" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18108,7 +18185,7 @@
           <t>1) REM 수립 적정성을 확인하였는가? 2) REM 회의록 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q20" s="101" t="inlineStr">
+      <c r="Q20" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18176,7 +18253,7 @@
           <t>R/O 분석 결과에 기반한 추가지반조사 항목 도출 | 추가지반조사 List</t>
         </is>
       </c>
-      <c r="M21" s="107" t="inlineStr">
+      <c r="M21" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18186,7 +18263,7 @@
           <t>• 지반조사 수렴 결과 분석보고서 검토 • 지반조사 결과 R/O 종합검토 결과 검토</t>
         </is>
       </c>
-      <c r="O21" s="107" t="inlineStr">
+      <c r="O21" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18196,7 +18273,7 @@
           <t>1) 추가지반조사 계획 수립 적정성을 확인하였는가? 2) 추가지반조사 List 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q21" s="107" t="inlineStr">
+      <c r="Q21" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18268,7 +18345,7 @@
           <t>적정 추가지반조사 규명을 위한 장비 사양 검토 | -</t>
         </is>
       </c>
-      <c r="M22" s="101" t="inlineStr">
+      <c r="M22" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18278,7 +18355,7 @@
           <t>• 3D GPR탐사 장비 사양(차량형) - 3D Radar(노르웨이)_200~3000Hz, 2.0m~3.0m : 하상도 높음 - MIRA(스웨덴)_400~1300Hz, 1.0m~2.0m : 정밀한 입체 형상 - St...</t>
         </is>
       </c>
-      <c r="O22" s="101" t="inlineStr">
+      <c r="O22" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18288,7 +18365,7 @@
           <t>1) 3D GPR탐사 장비 사양(차량형) 검토 적정성을 확인하였는가? 2) - 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q22" s="101" t="inlineStr">
+      <c r="Q22" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18357,7 +18434,7 @@
           <t>입찰설계 지반조사 결과에 따른 직분야 R/O 및 Cost impact 반영 사항 검토 | 입찰설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
         </is>
       </c>
-      <c r="M23" s="107" t="inlineStr">
+      <c r="M23" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18367,7 +18444,7 @@
           <t>• 입찰설계 지반조사 결과 분석을 통한 원가 및 공정 영향 검토 • 미시추 구간 평가 및 공정 Risk 반영 사항 검토 • 지반조건을 고려한 발파공법성 여부 검토</t>
         </is>
       </c>
-      <c r="O23" s="107" t="inlineStr">
+      <c r="O23" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18377,7 +18454,7 @@
           <t>1) ECRM 수립 적정성을 확인하였는가? 2) 입찰설계 지반조사 검토서(설계, 원가, 공정, 기타) 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q23" s="107" t="inlineStr">
+      <c r="Q23" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18444,7 +18521,7 @@
           <t>입찰 | 투찰내역서</t>
         </is>
       </c>
-      <c r="M24" s="101" t="inlineStr">
+      <c r="M24" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18454,7 +18531,7 @@
           <t>• 최종 R/O를 반영한 투찰내역서 작성</t>
         </is>
       </c>
-      <c r="O24" s="101" t="inlineStr">
+      <c r="O24" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18464,7 +18541,7 @@
           <t>1) 최종 Cost 검토 / 입찰 적정성을 확인하였는가? 2) 투찰내역서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q24" s="101" t="inlineStr">
+      <c r="Q24" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18531,7 +18608,7 @@
           <t>지반조사 포함 전체 R/O 승계자료 인수인계 및 추가지반조사 계획 공유 | 인수인계서</t>
         </is>
       </c>
-      <c r="M25" s="107" t="inlineStr">
+      <c r="M25" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18541,7 +18618,7 @@
           <t>• 최종 R/O 결과 및 입찰도서 인출</t>
         </is>
       </c>
-      <c r="O25" s="107" t="inlineStr">
+      <c r="O25" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18551,7 +18628,7 @@
           <t>1) 입찰설계 현장 인수인계 적정성을 확인하였는가? 2) 인수인계서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q25" s="107" t="inlineStr">
+      <c r="Q25" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18622,7 +18699,7 @@
           <t>미시추구간 지반조사 수행을 통한 지반 Risk Hedge | 추가 지반조사 보고서</t>
         </is>
       </c>
-      <c r="M26" s="113" t="inlineStr">
+      <c r="M26" s="128" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18632,7 +18709,7 @@
           <t>• 추가 지반조사 계획 및 시점 확인 - 탄성파탐사/전기비저항탐사 등 물리탐사 추가조사 (현장 및 위치 확인) - 추가시추조사 수행(물리탐사, 시추조사) - 토질 및 암석 실내시험 수행 및 결과분석 확인 - 공종별 ...</t>
         </is>
       </c>
-      <c r="O26" s="113" t="inlineStr">
+      <c r="O26" s="128" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18642,7 +18719,7 @@
           <t>1) 추가지반조사 수행 적정성을 확인하였는가? 2) 추가 지반조사 보고서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q26" s="113" t="inlineStr">
+      <c r="Q26" s="128" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18710,7 +18787,7 @@
           <t>추가지반조사 결과에 기반한 최종 R/O 확정 | 추가 지반조사결과 종합보고서</t>
         </is>
       </c>
-      <c r="M27" s="113" t="inlineStr">
+      <c r="M27" s="128" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18720,7 +18797,7 @@
           <t>• 외부전문가 검토 통한 지반특성 최종 Cross-check 확인 • 입찰설계 지반조사 대비 지반특성 변경구간 제원도 확인</t>
         </is>
       </c>
-      <c r="O27" s="113" t="inlineStr">
+      <c r="O27" s="128" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18730,7 +18807,7 @@
           <t>1) 추가지반조사 결과 분석 적정성을 확인하였는가? 2) 추가 지반조사결과 종합보고서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q27" s="113" t="inlineStr">
+      <c r="Q27" s="128" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18799,7 +18876,7 @@
           <t>실시설계 지반조사 결과에 따른 직분야 R/O 및 Cost impact 반영 사항 검토 | 실시설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
         </is>
       </c>
-      <c r="M28" s="101" t="inlineStr">
+      <c r="M28" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18809,7 +18886,7 @@
           <t>• 실시설계 추가지반조사 결과 분석을 통한 원가 및 공정 영향 검토 • 미시추 구간 평가 및 공정 Risk 반영 사항 검토 • 지반조건을 고려한 발파공법성 검토</t>
         </is>
       </c>
-      <c r="O28" s="101" t="inlineStr">
+      <c r="O28" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18819,7 +18896,7 @@
           <t>1) 실시설계 지반조사 R/O 검토 (설계, 원가, 공정, 기타) 적정성을 확인하였는가? 2) 실시설계 지반조사 검토서(설계, 원가, 공정, 기타) 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q28" s="101" t="inlineStr">
+      <c r="Q28" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18886,7 +18963,7 @@
           <t>추가지반조사 결과에 기반한 최종 R/O 확정 | 실시설계 최종 R/O</t>
         </is>
       </c>
-      <c r="M29" s="107" t="inlineStr">
+      <c r="M29" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18896,7 +18973,7 @@
           <t>• 추가지반조사 결과 검토</t>
         </is>
       </c>
-      <c r="O29" s="107" t="inlineStr">
+      <c r="O29" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18906,7 +18983,7 @@
           <t>1) 실시설계 추가지반조사 결과 검토 적정성을 확인하였는가? 2) 실시설계 최종 R/O 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q29" s="107" t="inlineStr">
+      <c r="Q29" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -18974,7 +19051,7 @@
           <t>최종 지반조사 결과에 따른 R/O 이행방안 수립 | 최종 R/O 이행계획서</t>
         </is>
       </c>
-      <c r="M30" s="101" t="inlineStr">
+      <c r="M30" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -18984,7 +19061,7 @@
           <t>• Core Risk 및 Hedge 방안 수립 • Opportunity에 따른 본공 상가 추가 개선 방안 수립</t>
         </is>
       </c>
-      <c r="O30" s="101" t="inlineStr">
+      <c r="O30" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -18994,7 +19071,7 @@
           <t>1) 최종 R/O 이행방안 수립 적정성을 확인하였는가? 2) 최종 R/O 이행계획서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q30" s="101" t="inlineStr">
+      <c r="Q30" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -19061,7 +19138,7 @@
           <t>참여인력 전문성 평가 및 특이사항 기록 | 외부지질 전문가 업무평가서</t>
         </is>
       </c>
-      <c r="M31" s="107" t="inlineStr">
+      <c r="M31" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -19071,7 +19148,7 @@
           <t>• 외부지질 전문가 업무평가서 작성</t>
         </is>
       </c>
-      <c r="O31" s="107" t="inlineStr">
+      <c r="O31" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -19081,7 +19158,7 @@
           <t>1) 외부지질전문가 업무평가 적정성을 확인하였는가? 2) 외부지질 전문가 업무평가서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q31" s="107" t="inlineStr">
+      <c r="Q31" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -19148,7 +19225,7 @@
           <t>조사업체 PM 전문성 평가 및 특이사항 기록 | PM업무평가서</t>
         </is>
       </c>
-      <c r="M32" s="101" t="inlineStr">
+      <c r="M32" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -19158,7 +19235,7 @@
           <t>• 지반조사 PM 업무평가서 작성</t>
         </is>
       </c>
-      <c r="O32" s="101" t="inlineStr">
+      <c r="O32" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -19168,7 +19245,7 @@
           <t>1) 조사업체 PM 업무평가 적정성을 확인하였는가? 2) PM업무평가서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q32" s="101" t="inlineStr">
+      <c r="Q32" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -19235,7 +19312,7 @@
           <t>조사업체 업무평가 및 특이사항 기록 | 협력업체 업무평가서</t>
         </is>
       </c>
-      <c r="M33" s="107" t="inlineStr">
+      <c r="M33" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -19245,7 +19322,7 @@
           <t>• 협력업체 업무평가서</t>
         </is>
       </c>
-      <c r="O33" s="107" t="inlineStr">
+      <c r="O33" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -19255,7 +19332,7 @@
           <t>1) 지반조사업체 업무평가 적정성을 확인하였는가? 2) 협력업체 업무평가서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q33" s="107" t="inlineStr">
+      <c r="Q33" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -19323,7 +19400,7 @@
           <t>설계변경 사항 기록 | LL리포트</t>
         </is>
       </c>
-      <c r="M34" s="101" t="inlineStr">
+      <c r="M34" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -19333,7 +19410,7 @@
           <t>• 설계변경 사유 기록관리 • 예상 R/O대비 설계변경 사항 비교 검토</t>
         </is>
       </c>
-      <c r="O34" s="101" t="inlineStr">
+      <c r="O34" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -19343,7 +19420,7 @@
           <t>1) 설계변경 LL 리포트 작성 적정성을 확인하였는가? 2) LL리포트 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q34" s="101" t="inlineStr">
+      <c r="Q34" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -19410,7 +19487,7 @@
           <t>전체 현장 설계변경 사항 기록 | LL리포트 List</t>
         </is>
       </c>
-      <c r="M35" s="107" t="inlineStr">
+      <c r="M35" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -19420,7 +19497,7 @@
           <t>• 현장별 설계변경 LL 리포트 취합 관리</t>
         </is>
       </c>
-      <c r="O35" s="107" t="inlineStr">
+      <c r="O35" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -19430,7 +19507,7 @@
           <t>1) 설계변경 LL 리포트 관리 적정성을 확인하였는가? 2) LL리포트 List 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q35" s="107" t="inlineStr">
+      <c r="Q35" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -19498,7 +19575,7 @@
           <t>지반조사업체 정산 | 정산계약서</t>
         </is>
       </c>
-      <c r="M36" s="101" t="inlineStr">
+      <c r="M36" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -19508,7 +19585,7 @@
           <t>• 조사도 수량 Check 후 구매시스템 변경계약 수행 • 변경계약 후 정산금 집행</t>
         </is>
       </c>
-      <c r="O36" s="101" t="inlineStr">
+      <c r="O36" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -19518,7 +19595,7 @@
           <t>1) 지반조사업체 정산계약 적정성을 확인하였는가? 2) 정산계약서 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q36" s="101" t="inlineStr">
+      <c r="Q36" s="126" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -19585,7 +19662,7 @@
           <t>지반조사 매뉴얼 Update | 지반조사 매뉴얼</t>
         </is>
       </c>
-      <c r="M37" s="107" t="inlineStr">
+      <c r="M37" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -19595,7 +19672,7 @@
           <t>• 매뉴얼 Update 및 개정사항 사내공지</t>
         </is>
       </c>
-      <c r="O37" s="107" t="inlineStr">
+      <c r="O37" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -19605,13 +19682,123 @@
           <t>1) 매뉴얼 Update 적정성을 확인하였는가? 2) 지반조사 매뉴얼 산출물을 확보하였는가?</t>
         </is>
       </c>
-      <c r="Q37" s="107" t="inlineStr">
+      <c r="Q37" s="127" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId108"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19702,7 +19889,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="115" t="n"/>
+      <c r="B3" s="129" t="n"/>
       <c r="C3" s="119" t="inlineStr">
         <is>
           <t>Start</t>
@@ -19720,16 +19907,16 @@
           <t>공통_사전준비_지반조사(기술형)</t>
         </is>
       </c>
-      <c r="B4" s="121" t="n"/>
-      <c r="C4" s="121" t="n"/>
-      <c r="D4" s="121" t="n"/>
-      <c r="E4" s="121" t="n"/>
-      <c r="F4" s="121" t="n"/>
-      <c r="G4" s="121" t="n"/>
-      <c r="H4" s="121" t="n"/>
-      <c r="I4" s="121" t="n"/>
-      <c r="J4" s="121" t="n"/>
-      <c r="K4" s="121" t="n"/>
+      <c r="B4" s="130" t="n"/>
+      <c r="C4" s="130" t="n"/>
+      <c r="D4" s="130" t="n"/>
+      <c r="E4" s="130" t="n"/>
+      <c r="F4" s="130" t="n"/>
+      <c r="G4" s="130" t="n"/>
+      <c r="H4" s="130" t="n"/>
+      <c r="I4" s="130" t="n"/>
+      <c r="J4" s="130" t="n"/>
+      <c r="K4" s="118" t="n"/>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="96" t="inlineStr"/>
@@ -19771,8 +19958,16 @@
           <t>발주처 기본계획 보고서</t>
         </is>
       </c>
-      <c r="J5" s="96" t="inlineStr"/>
-      <c r="K5" s="96" t="inlineStr"/>
+      <c r="J5" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K5" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="96" t="inlineStr"/>
@@ -19813,8 +20008,16 @@
           <t>관심사업 List</t>
         </is>
       </c>
-      <c r="J6" s="96" t="inlineStr"/>
-      <c r="K6" s="96" t="inlineStr"/>
+      <c r="J6" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K6" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="96" t="inlineStr">
@@ -19859,8 +20062,16 @@
           <t>발주처 기본계획 수행 List + Contact Point List</t>
         </is>
       </c>
-      <c r="J7" s="96" t="inlineStr"/>
-      <c r="K7" s="96" t="inlineStr"/>
+      <c r="J7" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K7" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="96" t="inlineStr">
@@ -19905,8 +20116,16 @@
           <t>외부지질전문가 Pool List</t>
         </is>
       </c>
-      <c r="J8" s="96" t="inlineStr"/>
-      <c r="K8" s="96" t="inlineStr"/>
+      <c r="J8" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K8" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="96" t="inlineStr">
@@ -19954,8 +20173,16 @@
           <t>조사업체 POOL/필요시 Update</t>
         </is>
       </c>
-      <c r="J9" s="96" t="inlineStr"/>
-      <c r="K9" s="96" t="inlineStr"/>
+      <c r="J9" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K9" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="96" t="inlineStr"/>
@@ -19999,8 +20226,16 @@
           <t>발주처 기본계획 보고서 및 지반조사 보고서(비공식)</t>
         </is>
       </c>
-      <c r="J10" s="96" t="inlineStr"/>
-      <c r="K10" s="96" t="inlineStr"/>
+      <c r="J10" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K10" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="96" t="inlineStr"/>
@@ -20047,8 +20282,16 @@
           <t>기본계획 지반조사 검토서(설계, 공정, 기획)</t>
         </is>
       </c>
-      <c r="J11" s="96" t="inlineStr"/>
-      <c r="K11" s="96" t="inlineStr"/>
+      <c r="J11" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K11" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="96" t="inlineStr">
@@ -20096,8 +20339,16 @@
           <t>기본계획 지반조사 개략 검토서</t>
         </is>
       </c>
-      <c r="J12" s="96" t="inlineStr"/>
-      <c r="K12" s="96" t="inlineStr"/>
+      <c r="J12" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K12" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="96" t="inlineStr">
@@ -20145,8 +20396,16 @@
           <t>지반조사 입찰 참여 Pool</t>
         </is>
       </c>
-      <c r="J13" s="96" t="inlineStr"/>
-      <c r="K13" s="96" t="inlineStr"/>
+      <c r="J13" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K13" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="96" t="inlineStr"/>
@@ -20190,8 +20449,16 @@
           <t>지반조사 용역 계약서</t>
         </is>
       </c>
-      <c r="J14" s="96" t="inlineStr"/>
-      <c r="K14" s="96" t="inlineStr"/>
+      <c r="J14" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K14" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="96" t="inlineStr">
@@ -20240,8 +20507,16 @@
           <t>지반조사 계획서</t>
         </is>
       </c>
-      <c r="J15" s="96" t="inlineStr"/>
-      <c r="K15" s="96" t="inlineStr"/>
+      <c r="J15" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K15" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="96" t="inlineStr">
@@ -20289,8 +20564,16 @@
           <t>지반조사계획 의견서</t>
         </is>
       </c>
-      <c r="J16" s="96" t="inlineStr"/>
-      <c r="K16" s="96" t="inlineStr"/>
+      <c r="J16" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K16" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="96" t="inlineStr"/>
@@ -20336,8 +20619,16 @@
           <t>인허가 서류</t>
         </is>
       </c>
-      <c r="J17" s="96" t="inlineStr"/>
-      <c r="K17" s="96" t="inlineStr"/>
+      <c r="J17" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K17" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="96" t="inlineStr"/>
@@ -20382,8 +20673,16 @@
           <t>지반조사 용역 계약서</t>
         </is>
       </c>
-      <c r="J18" s="96" t="inlineStr"/>
-      <c r="K18" s="96" t="inlineStr"/>
+      <c r="J18" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K18" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="96" t="inlineStr">
@@ -20433,8 +20732,16 @@
           <t>지반조사 보고서, 시추 Core 및 샘플</t>
         </is>
       </c>
-      <c r="J19" s="96" t="inlineStr"/>
-      <c r="K19" s="96" t="inlineStr"/>
+      <c r="J19" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K19" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="96" t="inlineStr">
@@ -20485,8 +20792,16 @@
           <t>지반조사 결과 분석 의견서</t>
         </is>
       </c>
-      <c r="J20" s="96" t="inlineStr"/>
-      <c r="K20" s="96" t="inlineStr"/>
+      <c r="J20" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K20" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="96" t="inlineStr"/>
@@ -20532,8 +20847,16 @@
           <t>입찰설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
         </is>
       </c>
-      <c r="J21" s="96" t="inlineStr"/>
-      <c r="K21" s="96" t="inlineStr"/>
+      <c r="J21" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K21" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="96" t="inlineStr">
@@ -20582,8 +20905,16 @@
           <t>입찰설계 R/O 검토서</t>
         </is>
       </c>
-      <c r="J22" s="96" t="inlineStr"/>
-      <c r="K22" s="96" t="inlineStr"/>
+      <c r="J22" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K22" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="96" t="inlineStr"/>
@@ -20629,8 +20960,16 @@
           <t>REM 회의록</t>
         </is>
       </c>
-      <c r="J23" s="96" t="inlineStr"/>
-      <c r="K23" s="96" t="inlineStr"/>
+      <c r="J23" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K23" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="96" t="inlineStr">
@@ -20679,8 +21018,16 @@
           <t>추가지반조사 List</t>
         </is>
       </c>
-      <c r="J24" s="96" t="inlineStr"/>
-      <c r="K24" s="96" t="inlineStr"/>
+      <c r="J24" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K24" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="96" t="inlineStr"/>
@@ -20729,8 +21076,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J25" s="96" t="inlineStr"/>
-      <c r="K25" s="96" t="inlineStr"/>
+      <c r="J25" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K25" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="96" t="inlineStr"/>
@@ -20776,8 +21131,16 @@
           <t>입찰설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
         </is>
       </c>
-      <c r="J26" s="96" t="inlineStr"/>
-      <c r="K26" s="96" t="inlineStr"/>
+      <c r="J26" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K26" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="96" t="inlineStr"/>
@@ -20821,8 +21184,16 @@
           <t>투찰내역서</t>
         </is>
       </c>
-      <c r="J27" s="96" t="inlineStr"/>
-      <c r="K27" s="96" t="inlineStr"/>
+      <c r="J27" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K27" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="96" t="inlineStr">
@@ -20870,8 +21241,16 @@
           <t>인수인계서</t>
         </is>
       </c>
-      <c r="J28" s="96" t="inlineStr"/>
-      <c r="K28" s="96" t="inlineStr"/>
+      <c r="J28" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K28" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="96" t="inlineStr">
@@ -20923,12 +21302,12 @@
           <t>추가 지반조사 보고서</t>
         </is>
       </c>
-      <c r="J29" s="96" t="inlineStr">
+      <c r="J29" s="126" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K29" s="96" t="inlineStr">
+      <c r="K29" s="126" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -20981,12 +21360,12 @@
           <t>추가 지반조사결과 종합보고서</t>
         </is>
       </c>
-      <c r="J30" s="96" t="inlineStr">
+      <c r="J30" s="126" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K30" s="96" t="inlineStr">
+      <c r="K30" s="126" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -21036,8 +21415,16 @@
           <t>실시설계 지반조사 검토서(설계, 원가, 공정, 기타)</t>
         </is>
       </c>
-      <c r="J31" s="96" t="inlineStr"/>
-      <c r="K31" s="96" t="inlineStr"/>
+      <c r="J31" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K31" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="96" t="inlineStr">
@@ -21085,8 +21472,16 @@
           <t>실시설계 최종 R/O</t>
         </is>
       </c>
-      <c r="J32" s="96" t="inlineStr"/>
-      <c r="K32" s="96" t="inlineStr"/>
+      <c r="J32" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K32" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="96" t="inlineStr">
@@ -21135,8 +21530,16 @@
           <t>최종 R/O 이행계획서</t>
         </is>
       </c>
-      <c r="J33" s="96" t="inlineStr"/>
-      <c r="K33" s="96" t="inlineStr"/>
+      <c r="J33" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K33" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="96" t="inlineStr">
@@ -21184,8 +21587,16 @@
           <t>외부지질 전문가 업무평가서</t>
         </is>
       </c>
-      <c r="J34" s="96" t="inlineStr"/>
-      <c r="K34" s="96" t="inlineStr"/>
+      <c r="J34" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K34" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="96" t="inlineStr">
@@ -21233,8 +21644,16 @@
           <t>PM업무평가서</t>
         </is>
       </c>
-      <c r="J35" s="96" t="inlineStr"/>
-      <c r="K35" s="96" t="inlineStr"/>
+      <c r="J35" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K35" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="96" t="inlineStr">
@@ -21282,8 +21701,16 @@
           <t>협력업체 업무평가서</t>
         </is>
       </c>
-      <c r="J36" s="96" t="inlineStr"/>
-      <c r="K36" s="96" t="inlineStr"/>
+      <c r="J36" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K36" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="96" t="inlineStr"/>
@@ -21328,8 +21755,16 @@
           <t>LL리포트</t>
         </is>
       </c>
-      <c r="J37" s="96" t="inlineStr"/>
-      <c r="K37" s="96" t="inlineStr"/>
+      <c r="J37" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K37" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="96" t="inlineStr"/>
@@ -21373,8 +21808,16 @@
           <t>LL리포트 List</t>
         </is>
       </c>
-      <c r="J38" s="96" t="inlineStr"/>
-      <c r="K38" s="96" t="inlineStr"/>
+      <c r="J38" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K38" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="96" t="inlineStr"/>
@@ -21419,8 +21862,16 @@
           <t>정산계약서</t>
         </is>
       </c>
-      <c r="J39" s="96" t="inlineStr"/>
-      <c r="K39" s="96" t="inlineStr"/>
+      <c r="J39" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K39" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="96" t="inlineStr">
@@ -21468,8 +21919,16 @@
           <t>지반조사 매뉴얼</t>
         </is>
       </c>
-      <c r="J40" s="96" t="inlineStr"/>
-      <c r="K40" s="96" t="inlineStr"/>
+      <c r="J40" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\수행지침\지반조사 상세검토_수행지침.html</t>
+        </is>
+      </c>
+      <c r="K40" s="126" t="inlineStr">
+        <is>
+          <t>매뉴얼BODY(집행단계-첨부폴더)v8\4.상부강화노반\1_지반조사 상세검토\표준서\1_지반조사 상세검토_표준서.html</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -21485,6 +21944,80 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="G2:G3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId72"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21680,7 +22213,7 @@
           <t>지하안전관리에 관한 특별법 제23조 | 현장 지반 조사, GPR 탐사 데이터 및 신설 궤도 간섭 리스크 사전 분석 | 지장물 이설 리스크 관리계획 수립</t>
         </is>
       </c>
-      <c r="L2" s="17" t="inlineStr">
+      <c r="L2" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -21690,7 +22223,7 @@
           <t>1) 지반 조사 주상도 &amp; GPR 데이터 대조 ➔ 2) 신설 궤도 구조물 간섭 관로 추출 ➔ 3) 기관별 이설 우선순위 수립 ➔ 4) 지장물 리스크 보고서 결재</t>
         </is>
       </c>
-      <c r="N2" s="17" t="inlineStr">
+      <c r="N2" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -21700,7 +22233,7 @@
           <t>지반 시추 주상도, GPR 3D 지중 관로 탐사 데이터 대조 및 신설 궤도 구조물 간섭 관로 사전 현출 점검</t>
         </is>
       </c>
-      <c r="P2" s="17" t="inlineStr">
+      <c r="P2" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -21778,7 +22311,7 @@
           <t>KCS 47 10 25 시방 준수 | 도급분 지장물 이설 발주 시방서 검토 &amp; 3D BIM 도면 대조 | 발주처·감리·시공 3자 킥오프 미팅 결재</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -21788,7 +22321,7 @@
           <t>1) 도급분 이설 시방서 요구조건 검토 ➔ 2) 3D BIM 도면 관로 좌표 대조 ➔ 3) 공기 지연 예비비 수립 ➔ 4) 발주·감리·시공 3자 킥오프 결재</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -21798,7 +22331,7 @@
           <t>KCS 47 10 25 시방 요구조건, 도급분 지장물 이설 수량 및 3D BIM 도면 간섭 zero 검증</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -21876,7 +22409,7 @@
           <t>지방계약법 및 관할 점용기관 규정 | 위수탁 지장물 이설 협약서 작성 &amp; 공문 발송 | 기관별 이설 소요 기간 및 예산 확보</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -21886,7 +22419,7 @@
           <t>1) 관할 점용기관 이설 요청 공문 작성 ➔ 2) 이설 협약서 정산 조건 수속 ➔ 3) 기관별 이설 소요 기간 협의 ➔ 4) 위수탁 이설 확약 공문 수령</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -21896,7 +22429,7 @@
           <t>위수탁 이설 요청 공문 부착, 점용기관 협약 조건 수속 및 이설 예비비 계상 서약</t>
         </is>
       </c>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="P4" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -21974,7 +22507,7 @@
           <t>건설산업기본법 제29조 | 상하수도 설비 전문건설업 면허 및 적정성(≥ 82%) 평가 | 노무비 전용계좌 지정 및 계약 승인</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -21984,7 +22517,7 @@
           <t>1) 상하수도 전문건설업 면허 심사 ➔ 2) 하도급 적정성(≥ 82%) 평가 ➔ 3) 노무비 전용계좌 개설 ➔ 4) 하도급 계약 승인 통보서 결재</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -21994,7 +22527,7 @@
           <t>상하수도 전문건설업 면허/실적 심사, 하도급 적정성 평가(≥ 82%) 및 노무비 전용계좌 지정</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="P5" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -22072,7 +22605,7 @@
           <t>지하안전법 수칙 | 한국전력, 도시가스, 수자원공사 1:1 현장 합동 조사 | 매설 위치, 관경(mm), 깊이 3D BIM 매핑</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -22082,7 +22615,7 @@
           <t>1) 한전/가스/수자원공사 1:1 현장 입회 ➔ 2) 관로 위치, 관경(mm), 깊이 현측 ➔ 3) 3D BIM 매설 관로 매핑 ➔ 4) 지장물 조사서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -22092,7 +22625,7 @@
           <t>한국전력, 도시가스, 수자원공사 1:1 현장 입회 및 지하 매설물 관경(mm), 심도 깊이 3D BIM 매핑</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P6" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -22170,7 +22703,7 @@
           <t>KCS 47 10 25 배수 및 관체 수칙 | 지장물 이설 공정표, 가설 방호 및 교통 우회 계획 수립 | 공사 착수 14일 전 감리 서면 승인</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -22180,7 +22713,7 @@
           <t>1) 지장물 이설 공정표 수립 ➔ 2) 가설 매달기 방호 &amp; 우회 차선 설계 ➔ 3) 착공 14일 전 감리단 제출 ➔ 4) 이설 계획서 책임감리원 승인</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -22190,7 +22723,7 @@
           <t>지장물 이설 공정표 수립, 가설 매달기 방호/우회 차선 설계 및 착공 14일 전 감리 서면 승인</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="P7" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -22268,7 +22801,7 @@
           <t>건산법 상생협력 규정 | 지장물 전담 기술자 1:1 현장 배치 | 주간 3자 소통 회의 및 일일 TBM/안전교육 시행</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -22278,7 +22811,7 @@
           <t>1) 지장물 전담 기술자 1:1 배치 ➔ 2) 3자 주간 소통 회의 개최 ➔ 3) 근로자 환경 개선 &amp; TBM ➔ 4) One-Team 조직표 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -22288,7 +22821,7 @@
           <t>지장물 전담 기술자 1:1 현장 배치, 발주·감리·시공 3자 주간 소통 회의 및 일일 TBM/음주 측정(0.00%)</t>
         </is>
       </c>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="P8" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -22366,7 +22899,7 @@
           <t>현장 통합 관리 지침 | 발주처·감리·지자체·시공사 합동 빅룸 회의 | 지장물 간섭 Zero 및 마일스톤 연동 확정</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -22376,7 +22909,7 @@
           <t>1) 4자(발주·감리·지자체·시공) 빅룸 결성 ➔ 2) 지장물 이설 마일스톤 연동 ➔ 3) 간섭 리스크 즉시 해소 ➔ 4) 빅룸 회의록 4자 서명 완수</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -22386,7 +22919,7 @@
           <t>4자(발주·감리·지자체·시공) 빅룸 회의 결성, 지장물 간섭 Zero 및 마일스톤 연동 회의록 서명</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P9" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -22464,7 +22997,7 @@
           <t>도로법 및 하천법 준수 | 지자체 도로점용 허가 및 하천점용 허가서 접수 | 관련 부서 협의 및 법정 인허가 필증 수속</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -22474,7 +23007,7 @@
           <t>1) 지자체 도로/하천점용 허가서 작성 ➔ 2) 관련 부서 서류 제출 &amp; 심의 ➔ 3) 보증보험 증권 부착 ➔ 4) 법정 인허가 필증 감리 수속</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -22484,7 +23017,7 @@
           <t>지자체 도로점용 허가 &amp; 하천점용 허가서 수속, 보증보험 증권 제출 및 법정 인허가 필증 검수</t>
         </is>
       </c>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="P10" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -22562,7 +23095,7 @@
           <t>도로교통법 제69조 | 관할 경찰서 교통안전 심의 및 점용 허가 수령 | 우회 차선 도면 작성 및 안전 신호수 배치</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -22572,7 +23105,7 @@
           <t>1) 교통 우회 도면 &amp; 차선 설계 ➔ 2) 동탄경찰서 도로점용 허가 ➔ 3) 전담 신호수(2인 2조) 배치 ➔ 4) 교통소통 대책서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -22582,7 +23115,7 @@
           <t>동탄경찰서 도로점용 허가, 우회 차선 설계 및 전담 안전 신호수(2인 2조)/LED 경광등 배치</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="P11" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -22660,7 +23193,7 @@
           <t>대기환경보전법 및 소음진동관리법 | 야간 공사 소음 억제 방음벽(H=3m) 및 세륜기 가동 | 단수/단전 사전 안내 및 민원 대응반 가동</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -22670,7 +23203,7 @@
           <t>1) 야간 공사 소음 방음벽(H=3m) 설치 ➔ 2) 세륜기 가동 &amp; 분무 살수 ➔ 3) 단수/단전 사전 주민 공지 ➔ 4) 민원 대응반 서면 승인</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -22680,7 +23213,7 @@
           <t>야간 공사 소음 방음벽(H=3m) 가동, 이동식 세륜기(깊이 1.2m) 가동 및 단수 사전 주민 알림</t>
         </is>
       </c>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="P12" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -22758,7 +23291,7 @@
           <t>토지보상법 준수 | 지장물 이설 부지 용지보상 현황 및 점용 경계 실측 | 미보상 사유지 가설 펜스 차단 및 우회 동선</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -22768,7 +23301,7 @@
           <t>1) 미보상 사유지 경계 현출 ➔ 2) 가설 펜스(H=1.8m) 차단 ➔ 3) 3D 우회 토공 동선 수립 ➔ 4) 용지 보상 리스크 대책 승인</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="N13" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -22778,7 +23311,7 @@
           <t>미보상 사유지 경계 현출, 가설 펜스(H=1.8m) 차단 및 3D 우회 토공 동선 마일스톤 연동</t>
         </is>
       </c>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="P13" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -22856,7 +23389,7 @@
           <t>수도법 및 하수도법 규정 | 맑은물사업소 합동 이설 위치 검토 &amp; 수돗물 단수 일정 수협 | 신구관 접속 설계도서 서면 결재</t>
         </is>
       </c>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="L14" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -22866,7 +23399,7 @@
           <t>1) 맑은물사업소 이설 위치 현측 ➔ 2) 단수 일정(최대 6시간) 협의 ➔ 3) 신구관 접속 도면 검토 ➔ 4) 이설 승인 공문 수령</t>
         </is>
       </c>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="N14" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -22876,7 +23409,7 @@
           <t>맑은물사업소 합동 이설 위치 검토, 수돗물 단수 일정(최대 6h) 수협 및 신구관 접속 도면 결재</t>
         </is>
       </c>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="P14" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -22954,7 +23487,7 @@
           <t>지하관로 설계기준 준수 | 위수탁 기관 설계도서 기술 검토 &amp; 3D BIM 간섭 점검 | 총사업비 변경 승인 및 설계 도서 수록</t>
         </is>
       </c>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="L15" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -22964,7 +23497,7 @@
           <t>1) 위수탁 기관 설계도서 수속 ➔ 2) 3D BIM 간섭 리스크 점검 ➔ 3) 총사업비 변경 수량 검증 ➔ 4) 위수탁 설계도서 감리 승인</t>
         </is>
       </c>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="N15" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -22974,7 +23507,7 @@
           <t>위수탁 기관 설계도서 기술 검토, 3D BIM 간섭 리스크 점검 및 총사업비 변경 수량 승인</t>
         </is>
       </c>
-      <c r="P15" s="17" t="inlineStr">
+      <c r="P15" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -23052,7 +23585,7 @@
           <t>건진법 시행령 규정 | 현장 지장물 현출에 따른 실정보고서 작성 | 공법 변경 및 수량 증감에 대한 책임감리 승인</t>
         </is>
       </c>
-      <c r="L16" s="17" t="inlineStr">
+      <c r="L16" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -23062,7 +23595,7 @@
           <t>1) 현장 지장물 현출 실정보고 작성 ➔ 2) 공법 변경 &amp; 수량 증감 산출 ➔ 3) 기술 검토 의견서 첨부 ➔ 4) 실정보고서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N16" s="17" t="inlineStr">
+      <c r="N16" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -23072,7 +23605,7 @@
           <t>현장 지장물 현출 실정보고서 작성, 공법 변경 및 수량 증감 산출 책임감리원 승인</t>
         </is>
       </c>
-      <c r="P16" s="17" t="inlineStr">
+      <c r="P16" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -23150,7 +23683,7 @@
           <t>지방자치단체 계약법 | 관할 점용기관과 위수탁 이설 협약서 정산 조건 체결 | 공사비 분담금 및 예비비 계상 합의</t>
         </is>
       </c>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="L17" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -23160,7 +23693,7 @@
           <t>1) 관할 점용기관 협약 조건 수속 ➔ 2) 정산 분담금 &amp; 예비비 협의 ➔ 3) 위수탁 계약서 작성 ➔ 4) 위수탁 이설 계약 체결 승인</t>
         </is>
       </c>
-      <c r="N17" s="17" t="inlineStr">
+      <c r="N17" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -23170,7 +23703,7 @@
           <t>관할 점용기관 위수탁 이설 협약서 체결, 공사비 분담금 및 예비비 계상 합의 서약</t>
         </is>
       </c>
-      <c r="P17" s="17" t="inlineStr">
+      <c r="P17" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -23248,7 +23781,7 @@
           <t>도로법 제61조 준수 | 지자체 도로 굴착 허가 신청서 접수 및 심의 필 | 도로 복구 이행 보증보험 증권 제출</t>
         </is>
       </c>
-      <c r="L18" s="17" t="inlineStr">
+      <c r="L18" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -23258,7 +23791,7 @@
           <t>1) 도로 굴착 허가 신청서 작성 ➔ 2) 지자체 도로굴착 심의 필 ➔ 3) 복구 보증보험 증권 제출 ➔ 4) 도로 굴착 허가증 감리 결재</t>
         </is>
       </c>
-      <c r="N18" s="17" t="inlineStr">
+      <c r="N18" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -23268,7 +23801,7 @@
           <t>지자체 도로 굴착 허가 신청서 접수, 심의 필증 수령 및 도로 복구 보증보험 증권 제출</t>
         </is>
       </c>
-      <c r="P18" s="17" t="inlineStr">
+      <c r="P18" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -23346,7 +23879,7 @@
           <t>도로교통법 안전 수칙 | 게이트 및 굴착 구간 안전 바리케이트, LED 경광등 부설 | 전담 신호수(2인 2조) 100% 현장 배치</t>
         </is>
       </c>
-      <c r="L19" s="17" t="inlineStr">
+      <c r="L19" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -23356,7 +23889,7 @@
           <t>1) 굴착 구간 안전 바리케이트 부설 ➔ 2) 야간 LED 경광등 &amp; 표지판 설치 ➔ 3) 전담 신호수(2인 2조) 배치 ➔ 4) 교통 안전 점검 대장 결재</t>
         </is>
       </c>
-      <c r="N19" s="17" t="inlineStr">
+      <c r="N19" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -23366,7 +23899,7 @@
           <t>굴착 구간 안전 바리케이트 부설, 야간 LED 경광등 설치 및 전담 신호수(2인 2조) 배치</t>
         </is>
       </c>
-      <c r="P19" s="17" t="inlineStr">
+      <c r="P19" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -23444,7 +23977,7 @@
           <t>지하안전법 제23조 | GPR 3D 탐사 후 인력 시탐 줄파기(폭 0.5m, 깊이 1.5m) | 실체 관로 노출 및 위치 표지판 비치</t>
         </is>
       </c>
-      <c r="L20" s="17" t="inlineStr">
+      <c r="L20" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -23454,7 +23987,7 @@
           <t>1) GPR 3D 지중 관로 탐사 ➔ 2) 인력 시탐 줄파기(깊이 1.5m) ➔ 3) 실체 관로 노출 &amp; 위치 매핑 ➔ 4) 지장물 현측표 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N20" s="17" t="inlineStr">
+      <c r="N20" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -23464,7 +23997,7 @@
           <t>GPR 3D 지중 관로 탐사, 인력 시탐 줄파기(폭 0.5m, 깊이 1.5m) 및 실체 관로 노출 매핑</t>
         </is>
       </c>
-      <c r="P20" s="17" t="inlineStr">
+      <c r="P20" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -23542,7 +24075,7 @@
           <t>KCS 47 10 25 굴착 시방 | 굴착 사면 비탈면 경사(1:1.5) 준수 및 흙막이 가설재 부설 | 굴착 바닥 원지반 K30 ≥ 70 지비력 검측</t>
         </is>
       </c>
-      <c r="L21" s="17" t="inlineStr">
+      <c r="L21" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -23552,7 +24085,7 @@
           <t>1) 굴착 비탈면 경사(1:1.5) 측량 ➔ 2) 굴착 &amp; 흙막이 가설재 부설 ➔ 3) 바닥 원지반 K30(≥70) 검측 ➔ 4) 굴착 완료 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N21" s="17" t="inlineStr">
+      <c r="N21" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -23562,7 +24095,7 @@
           <t>굴착 비탈면 경사(1:1.5 이하) 측량, 흙막이 가설재 부설 및 바닥 원지반 K30 ≥ 70 지비력 검측</t>
         </is>
       </c>
-      <c r="P21" s="17" t="inlineStr">
+      <c r="P21" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -23640,7 +24173,7 @@
           <t>KS 관로 자재 규정 준수 | 신규 상하수도관/가스관 부설 및 모래 기초(두께 10cm) 부설 | 관로 경사(≥ 0.5%) 및 수평 위치 검측</t>
         </is>
       </c>
-      <c r="L22" s="17" t="inlineStr">
+      <c r="L22" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -23650,7 +24183,7 @@
           <t>1) 관로 모래 기초(10cm) 부설 ➔ 2) 신규 상하수도관/가스관 부설 ➔ 3) 관로 종단 구배(≥0.5%) 검측 ➔ 4) 신규 관로 부설 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N22" s="17" t="inlineStr">
+      <c r="N22" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -23660,7 +24193,7 @@
           <t>관로 모래 기초(두께 10cm) 부설, 신규 상하수도관/가스관 부설 및 종단 구배(≥ 0.5%) 검측</t>
         </is>
       </c>
-      <c r="P22" s="17" t="inlineStr">
+      <c r="P22" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -23738,7 +24271,7 @@
           <t>수도시설 공학 규정 | 무단수 천공기 및 밸브 차단 장치 정밀 세팅 | 수압 시험 및 밸브 가동 상태 시운전 검측</t>
         </is>
       </c>
-      <c r="L23" s="17" t="inlineStr">
+      <c r="L23" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -23748,7 +24281,7 @@
           <t>1) 무단수 천공기 정밀 세팅 ➔ 2) 차단 밸브 &amp; 챔버 설치 ➔ 3) 수압 시험 및 가동 시운전 ➔ 4) 무단수 시설 검측 감리 승인</t>
         </is>
       </c>
-      <c r="N23" s="17" t="inlineStr">
+      <c r="N23" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -23758,7 +24291,7 @@
           <t>무단수 천공기 정밀 세팅, 차단 밸브 &amp; 챔버 설치 및 수압 시험/가동 시운전 검측</t>
         </is>
       </c>
-      <c r="P23" s="17" t="inlineStr">
+      <c r="P23" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -23836,7 +24369,7 @@
           <t>관로 연결 시방 수칙 | 신구 관로 접속 부위 수압 시험(10kgf/cm², 1시간 유지) | 누수 여부 점검 및 부식 방지 랩핑 부설</t>
         </is>
       </c>
-      <c r="L24" s="17" t="inlineStr">
+      <c r="L24" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -23846,7 +24379,7 @@
           <t>1) 신구 관로 접속 부위 부설 ➔ 2) 수압 시험(10kgf/cm², 1h 유지) ➔ 3) 부식 방지 피복 랩핑 시행 ➔ 4) 관로 접속 검측 성과표 승인</t>
         </is>
       </c>
-      <c r="N24" s="17" t="inlineStr">
+      <c r="N24" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -23856,7 +24389,7 @@
           <t>신구 관로 접속 부위 부설, 수압 시험(10kgf/cm², 1h 유지) 및 부식 방지 피복 랩핑 검측</t>
         </is>
       </c>
-      <c r="P24" s="17" t="inlineStr">
+      <c r="P24" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -23934,7 +24467,7 @@
           <t>폐기물관리법 준수 | 폐관로 수거 및 토사 30cm 층다짐(다짐도 ≥ 95%) 원상복구 | 아스콘 가포설 및 평탄성 통제</t>
         </is>
       </c>
-      <c r="L25" s="17" t="inlineStr">
+      <c r="L25" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -23944,7 +24477,7 @@
           <t>1) 기존 폐관로 안전 철거/수거 ➔ 2) 토사 30cm 층다짐(다짐도≥95%) ➔ 3) 아스콘 가포설 &amp; 평탄성 검측 ➔ 4) 원상복구 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N25" s="17" t="inlineStr">
+      <c r="N25" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -23954,7 +24487,7 @@
           <t>기존 폐관로 안전 철거/수거, 토사 30cm 층다짐(다짐도 ≥ 95%) 원상복구 및 아스콘 가포설</t>
         </is>
       </c>
-      <c r="P25" s="17" t="inlineStr">
+      <c r="P25" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -24032,7 +24565,7 @@
           <t>수도법 규정 준수 | 광역상수관(Ø500mm+) 이설 수압 시험 및 수질 검사 합격 | 한국수자원공사 입회 인수 완료</t>
         </is>
       </c>
-      <c r="L26" s="17" t="inlineStr">
+      <c r="L26" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -24042,7 +24575,7 @@
           <t>1) 광역상수관(Ø500mm+) 부설 ➔ 2) 수압 시험 &amp; 수질 검사 시행 ➔ 3) 한국수자원공사 현장 입회 ➔ 4) 광역상수관 이설 완료 승인</t>
         </is>
       </c>
-      <c r="N26" s="17" t="inlineStr">
+      <c r="N26" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -24052,7 +24585,7 @@
           <t>광역상수관(Ø500mm+) 부설, 수압 시험 및 수질 검사 합격 (한국수자원공사 1:1 입회 검측)</t>
         </is>
       </c>
-      <c r="P26" s="17" t="inlineStr">
+      <c r="P26" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -24130,7 +24663,7 @@
           <t>지자체 상수도 시방 | 배수관(Ø200~300mm) 이설, 탁수 퇴수 작업 및 잔류염소 시험 | 맑은물사업소 합동 현측 승인</t>
         </is>
       </c>
-      <c r="L27" s="17" t="inlineStr">
+      <c r="L27" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -24140,7 +24673,7 @@
           <t>1) 배수관(Ø200~300mm) 이설 부설 ➔ 2) 탁수 퇴수 &amp; 잔류염소 시험 ➔ 3) 맑은물사업소 합동 현측 ➔ 4) 상수도 관로 이설 감리 승인</t>
         </is>
       </c>
-      <c r="N27" s="17" t="inlineStr">
+      <c r="N27" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -24150,7 +24683,7 @@
           <t>배수관(Ø200~300mm) 이설, 탁수 퇴수 작업 및 잔류염소 시험 합격 (맑은물사업소 현측)</t>
         </is>
       </c>
-      <c r="P27" s="17" t="inlineStr">
+      <c r="P27" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -24228,7 +24761,7 @@
           <t>하수도정비 기본계획 | 하수관(Ø400mm+) 연결, CCTV 관로 내부 검사 및 통수 담수 시험 | 하수도사업소 현장 인수</t>
         </is>
       </c>
-      <c r="L28" s="17" t="inlineStr">
+      <c r="L28" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -24238,7 +24771,7 @@
           <t>1) 하수관(Ø400mm+) 연결 부설 ➔ 2) CCTV 관로 내부 검사 시행 ➔ 3) 통수 담수 시험 완료 ➔ 4) 하수도 관로 이설 감리 승인</t>
         </is>
       </c>
-      <c r="N28" s="17" t="inlineStr">
+      <c r="N28" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -24248,7 +24781,7 @@
           <t>하수관(Ø400mm+) 연결 부설, CCTV 관로 내부 검사 &amp; 통수 담수 시험 합격 (하수도사업소 인수)</t>
         </is>
       </c>
-      <c r="P28" s="17" t="inlineStr">
+      <c r="P28" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -24326,7 +24859,7 @@
           <t>도시가스사업법 규정 | 가스관(중압/아중압) 비파괴검사(RT 100%) 및 기밀 시험 합격 | 도시가스사 1:1 입회 검측</t>
         </is>
       </c>
-      <c r="L29" s="17" t="inlineStr">
+      <c r="L29" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -24336,7 +24869,7 @@
           <t>1) 도시가스관 매설 &amp; 용접 ➔ 2) 비파괴검사(RT 100%) &amp; 기밀 시험 ➔ 3) 도시가스사 1:1 입회 검측 ➔ 4) 가스관 이설 완료 승인</t>
         </is>
       </c>
-      <c r="N29" s="17" t="inlineStr">
+      <c r="N29" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -24346,7 +24879,7 @@
           <t>도시가스관 매설 &amp; 용접, 비파괴검사(RT 100%) 및 기밀 시험 합격 (도시가스사 1:1 입회)</t>
         </is>
       </c>
-      <c r="P29" s="17" t="inlineStr">
+      <c r="P29" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -24424,7 +24957,7 @@
           <t>집단에너지사업법 규정 | 난방 수송관 100% 비파괴검사 및 보온재 피복 랩핑 검수 | 지역난방공사 시운전 인수</t>
         </is>
       </c>
-      <c r="L30" s="17" t="inlineStr">
+      <c r="L30" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -24434,7 +24967,7 @@
           <t>1) 난방 수송관 매설 &amp; 용접 ➔ 2) 100% 비파괴검사 &amp; 피복 랩핑 ➔ 3) 지역난방공사 시운전 인수 ➔ 4) 지역난방관 이설 감리 승인</t>
         </is>
       </c>
-      <c r="N30" s="17" t="inlineStr">
+      <c r="N30" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -24444,7 +24977,7 @@
           <t>난방 수송관 매설 &amp; 용접, 100% 비파괴검사 및 피복 랩핑 검수 (지역난방공사 인수)</t>
         </is>
       </c>
-      <c r="P30" s="17" t="inlineStr">
+      <c r="P30" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -24522,7 +25055,7 @@
           <t>전기통신사업법 준수 | 통신 광케이블 관로 부설 및 절연 저항/광손실 실측 | KT/SKT 통신사 광신호 시험 승인</t>
         </is>
       </c>
-      <c r="L31" s="17" t="inlineStr">
+      <c r="L31" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -24532,7 +25065,7 @@
           <t>1) 통신 광케이블 관로 부설 ➔ 2) 광케이블 포설 &amp; 접속 ➔ 3) 절연저항 &amp; 광손실 시험 ➔ 4) KT/SKT 통신사 광신호 승인</t>
         </is>
       </c>
-      <c r="N31" s="17" t="inlineStr">
+      <c r="N31" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -24542,7 +25075,7 @@
           <t>통신 광케이블 관로 부설, 절연 저항 &amp; 광손실 실측 합격 (KT/SKT 광신호 승인)</t>
         </is>
       </c>
-      <c r="P31" s="17" t="inlineStr">
+      <c r="P31" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -24620,7 +25153,7 @@
           <t>전기공사업법 규정 | 22.9kV 특고압 전력 관로/맨홀 부설 및 절연내력 시험 | 한전(KEPCO) 현장 입회 휴전 Cut-over</t>
         </is>
       </c>
-      <c r="L32" s="17" t="inlineStr">
+      <c r="L32" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -24630,7 +25163,7 @@
           <t>1) 22.9kV 특고압 관로/맨홀 부설 ➔ 2) 전력 케이블 인입 &amp; 내력 시험 ➔ 3) 한전 입회 휴전 Cut-over ➔ 4) 전력관로 이설 완료 승인</t>
         </is>
       </c>
-      <c r="N32" s="17" t="inlineStr">
+      <c r="N32" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -24640,7 +25173,7 @@
           <t>22.9kV 특고압 관로/맨홀 부설, 절연내력 시험 합격 (한전 KEPCO 입회 휴전 Cut-over)</t>
         </is>
       </c>
-      <c r="P32" s="17" t="inlineStr">
+      <c r="P32" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -24717,7 +25250,7 @@
           <t>송유관안전관리법 규정 | 송유관 비파괴 NDT 검사 및 초음파 탐상 시험 100% | 대한송유관공사 안전 인계</t>
         </is>
       </c>
-      <c r="L33" s="17" t="inlineStr">
+      <c r="L33" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -24727,7 +25260,7 @@
           <t>1) 송유관 용접 부설 ➔ 2) NDT 비파괴검사 &amp; 초음파 탐상 ➔ 3) 송유관공사 안전 점검 ➔ 4) 송유관 이설 완료 서면 승인</t>
         </is>
       </c>
-      <c r="N33" s="17" t="inlineStr">
+      <c r="N33" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -24737,7 +25270,7 @@
           <t>송유관 용접 부설, NDT 비파괴검사 및 초음파 탐상 시험 100% 합격 (대한송유관공사 인수)</t>
         </is>
       </c>
-      <c r="P33" s="17" t="inlineStr">
+      <c r="P33" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -24814,7 +25347,7 @@
           <t>상하수도 총괄 지침 | 신설 관로 수압·수질·CCTV 검사 종합 대장 작성 | 지자체 3자 합동 최종 현현 점검</t>
         </is>
       </c>
-      <c r="L34" s="17" t="inlineStr">
+      <c r="L34" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -24824,7 +25357,7 @@
           <t>1) 신설 관로 종합 현측 ➔ 2) 수압/수질/CCTV 검사 종합 ➔ 3) 지자체 3자 합동 점검 ➔ 4) 상하수도 최종 점검 대장 승인</t>
         </is>
       </c>
-      <c r="N34" s="17" t="inlineStr">
+      <c r="N34" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -24834,7 +25367,7 @@
           <t>신설 관로 종합 현측, 수압/수질/CCTV 검사 종합 대장 작성 및 지자체 3자 합동 점검</t>
         </is>
       </c>
-      <c r="P34" s="17" t="inlineStr">
+      <c r="P34" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -24911,7 +25444,7 @@
           <t>위수탁 총괄 지침 | 위탁기관 1:1 현장 최종 인수 검측 및 3D BIM 준공 도면 대조 | 지장물 이설 준공 보고서</t>
         </is>
       </c>
-      <c r="L35" s="17" t="inlineStr">
+      <c r="L35" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -24921,7 +25454,7 @@
           <t>1) 위탁기관 1:1 인수 검측 ➔ 2) 3D BIM 준공 도면 대조 ➔ 3) 이설 완료 현장 서명 ➔ 4) 준공 보고서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N35" s="17" t="inlineStr">
+      <c r="N35" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -24931,7 +25464,7 @@
           <t>위탁기관 1:1 인수 검측, 3D BIM 준공 도면 대조 및 이설 준공 보고서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="P35" s="17" t="inlineStr">
+      <c r="P35" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -25008,7 +25541,7 @@
           <t>지방계약법 정산 수칙 | 실제 실정보고 투입 물량 및 단가 산정 정산서 작성 | 책임감리원 정산 금액 서면 승인</t>
         </is>
       </c>
-      <c r="L36" s="17" t="inlineStr">
+      <c r="L36" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -25018,7 +25551,7 @@
           <t>1) 실정보고 투입 물량 집계 ➔ 2) 정산 단가 산정 서류 작성 ➔ 3) 정산서 감리 기술 검토 ➔ 4) 정산 금액 최종 서면 승인</t>
         </is>
       </c>
-      <c r="N36" s="17" t="inlineStr">
+      <c r="N36" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -25028,7 +25561,7 @@
           <t>실정보고 투입 물량 집계, 정산 단가 산정 서류 작성 및 책임감리원 정산 금액 서면 승인</t>
         </is>
       </c>
-      <c r="P36" s="17" t="inlineStr">
+      <c r="P36" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -25105,7 +25638,7 @@
           <t>위수탁 정산 규정 | 관할 위탁기관에 최종 정산금 청구서 및 집행 영수증 작성 | 이설 정산금 집행 완료</t>
         </is>
       </c>
-      <c r="L37" s="17" t="inlineStr">
+      <c r="L37" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -25115,7 +25648,7 @@
           <t>1) 위탁기관 정산 청구서 작성 ➔ 2) 증빙 영수증 &amp; 성과표 첨부 ➔ 3) 정산금 지급 수속 ➔ 4) 이설 정산금 집행 완료</t>
         </is>
       </c>
-      <c r="N37" s="17" t="inlineStr">
+      <c r="N37" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -25125,7 +25658,7 @@
           <t>위탁기관 정산 청구서 작성, 증빙 영수증 &amp; 성과표 부착 및 이설 정산금 집행 완료</t>
         </is>
       </c>
-      <c r="P37" s="17" t="inlineStr">
+      <c r="P37" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -25202,7 +25735,7 @@
           <t>건진법 설계변경 수칙 | 도급분 및 위수탁분 총사업비 변경 계약 체결 | 발주처 변경 공문 수령 완료</t>
         </is>
       </c>
-      <c r="L38" s="17" t="inlineStr">
+      <c r="L38" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -25212,7 +25745,7 @@
           <t>1) 설계변경 총사업비 산정 ➔ 2) 도급/위수탁 변경 변경 수속 ➔ 3) 발주처 변경 공문 수령 ➔ 4) 설계변경 정산 최종 승인</t>
         </is>
       </c>
-      <c r="N38" s="17" t="inlineStr">
+      <c r="N38" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -25222,7 +25755,7 @@
           <t>설계변경 총사업비 산정, 도급/위수탁 변경 변경 수속 및 발주처 변경 공문 수령</t>
         </is>
       </c>
-      <c r="P38" s="17" t="inlineStr">
+      <c r="P38" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -25299,7 +25832,7 @@
           <t>공정 간섭 관리 지침 | 선행 토공 및 측량 기준점 성과 인수 대장 작성 | 3자 인계인수서 서명 완료</t>
         </is>
       </c>
-      <c r="L39" s="17" t="inlineStr">
+      <c r="L39" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -25309,7 +25842,7 @@
           <t>1) 선행 토공 &amp; 측량 성과 인수 ➔ 2) 현장 지장물 인계인수 ➔ 3) 3자 합동 현측 실시 ➔ 4) 인계인수서 3자 서명 완료</t>
         </is>
       </c>
-      <c r="N39" s="17" t="inlineStr">
+      <c r="N39" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -25319,7 +25852,7 @@
           <t>선행 토공 및 측량 성과 인수 대장 작성, 3자 합동 현측 및 인계인수서 서명 완료</t>
         </is>
       </c>
-      <c r="P39" s="17" t="inlineStr">
+      <c r="P39" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -25340,6 +25873,9 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
     <row r="43">
       <c r="G43" s="45" t="n"/>
     </row>
@@ -25720,7 +26256,7 @@
           <t>KDS 47 10 00 철도지반 설계기준 준수 | 시추 주상도, GPR 3D 매핑 및 N치 &lt; 4 연약지반 층후 경출 | PVD/DCM 개량 공법 확정</t>
         </is>
       </c>
-      <c r="L2" s="24" t="inlineStr">
+      <c r="L2" s="131" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -25730,7 +26266,7 @@
           <t>1) 시추 주상도 &amp; GPR 3D 매핑 분석 ➔ 2) N치 &lt; 4 연약지반 심도 경계 추출 ➔ 3) PVD/DCM 개량 공법 검토 ➔ 4) 기술사 서명 지반조사 보고서 감리 승인</t>
         </is>
       </c>
-      <c r="N2" s="79" t="inlineStr">
+      <c r="N2" s="131" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -25740,7 +26276,7 @@
           <t>시추 주상도 대조, GPR 지중 탐사 3D 매핑 및 N치 &lt; 4 연약지반 층후 경출 (PVD/DCM 개량 승인)</t>
         </is>
       </c>
-      <c r="P2" s="24" t="inlineStr">
+      <c r="P2" s="131" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -25814,7 +26350,7 @@
           <t>KCS 47 10 25 시방 검토 | 쇄석 입도 50mm 및 다짐도 ≥ 95% 명시 | 3D BIM 도면 대조 &amp; 리스크 예비비 수립 킥오프 승인</t>
         </is>
       </c>
-      <c r="L3" s="24" t="inlineStr">
+      <c r="L3" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -25824,7 +26360,7 @@
           <t>1) 발주처 시방서 요구조건 분석 ➔ 2) 3D BIM 도면 표고/구배 검증 ➔ 3) 지장물/용지 리스크 예비비 수립 ➔ 4) 발주·감리·시공 3자 킥오프 결재</t>
         </is>
       </c>
-      <c r="N3" s="79" t="inlineStr">
+      <c r="N3" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -25834,7 +26370,7 @@
           <t>KCS 47 10 25 시방 검토, 쇄석 입도 50mm/다짐도 95% 명시 및 3D BIM 도면 대조 (발주전략 킥오프 결재)</t>
         </is>
       </c>
-      <c r="P3" s="24" t="inlineStr">
+      <c r="P3" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -25908,7 +26444,7 @@
           <t>철도안전법 제45조 준수 | 궤도 중심 30m 법정 경계 측량(오차 ≤ 5mm) | 행위신고서 작성 및 운행선안전관리자 1:1 배치</t>
         </is>
       </c>
-      <c r="L4" s="24" t="inlineStr">
+      <c r="L4" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -25918,7 +26454,7 @@
           <t>1) 궤도 중심 30m 법정 경계 측량 ➔ 2) 행위신고서/안전계획서 접수 ➔ 3) 관할 철도운영기관 기술 심의 ➔ 4) 운행선안전관리자 현장 1:1 배치</t>
         </is>
       </c>
-      <c r="N4" s="79" t="inlineStr">
+      <c r="N4" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -25928,7 +26464,7 @@
           <t>궤도 중심 30m 법정 경계 측량(오차 ≤ 5mm), 행위신고서 접수 및 운행선안전관리자 1:1 현장 배치</t>
         </is>
       </c>
-      <c r="P4" s="24" t="inlineStr">
+      <c r="P4" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -26002,7 +26538,7 @@
           <t>공공측량 작업규정 준수 | 국가 CP/TBM 기준점 인수 및 GRS80 수준측량(폐합오차 ≤ 5mm√K) | 현장 인조점 3개소 매설 성과 확보</t>
         </is>
       </c>
-      <c r="L5" s="24" t="inlineStr">
+      <c r="L5" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -26012,7 +26548,7 @@
           <t>1) 국가 CP/TBM 기준점 인수 ➔ 2) GRS80 수준측량(폐합오차 ≤ 5mm√K) ➔ 3) 현장 인조점 3개소 매설 ➔ 4) 측량 성과표 작성 &amp; 3D BIM 승인</t>
         </is>
       </c>
-      <c r="N5" s="79" t="inlineStr">
+      <c r="N5" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -26022,7 +26558,7 @@
           <t>국가 CP/TBM 기준점 인수, GRS80 수준측량(폐합오차 ≤ 5mm√K) 및 현장 인조점 3개소 매설 성과</t>
         </is>
       </c>
-      <c r="P5" s="24" t="inlineStr">
+      <c r="P5" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -26096,7 +26632,7 @@
           <t>지하안전관리에 관한 특별법 제23조 | GPR 지중 탐사 &amp; 인력 줄파기(깊이 1.5m) | 점용기관 입회 매달기 방호 및 이설 완료 승인</t>
         </is>
       </c>
-      <c r="L6" s="24" t="inlineStr">
+      <c r="L6" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -26106,7 +26642,7 @@
           <t>1) GPR 3D 지중 관로 탐사 ➔ 2) 인력 시탐 줄파기(깊이 1.5m) ➔ 3) 관할 점용기관 1:1 현장 입회 ➔ 4) 매달기 방호 &amp; 지장물 이설 완료 승인</t>
         </is>
       </c>
-      <c r="N6" s="79" t="inlineStr">
+      <c r="N6" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -26116,7 +26652,7 @@
           <t>GPR 3D 관로 탐사, 인력 시탐 줄파기(깊이 1.5m) 및 점용기관 1:1 현장 입회 매달기 방호</t>
         </is>
       </c>
-      <c r="P6" s="24" t="inlineStr">
+      <c r="P6" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -26190,7 +26726,7 @@
           <t>토지보상법 준수 | 미보상 사유지 경계 현출 및 가설 펜스(H=1.8m) 설치 | 3D 우회 토공 동선 수립 및 마일스톤 연동</t>
         </is>
       </c>
-      <c r="L7" s="24" t="inlineStr">
+      <c r="L7" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -26200,7 +26736,7 @@
           <t>1) 미보상 사유지 필지 추출 ➔ 2) 경계 가설 펜스(H=1.8m) 차단 ➔ 3) 3D 우회 토공 동선 수립 ➔ 4) 용지 보상 리스크 대책 감리 승인</t>
         </is>
       </c>
-      <c r="N7" s="79" t="inlineStr">
+      <c r="N7" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -26210,7 +26746,7 @@
           <t>미보상 사유지 경계 현출, 가설 펜스(H=1.8m) 차단 및 3D 우회 토공 동선 마일스톤 연동</t>
         </is>
       </c>
-      <c r="P7" s="24" t="inlineStr">
+      <c r="P7" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -26284,7 +26820,7 @@
           <t>건산법 상생협력 규정 | 토공 전문 기술자 1:1 전담 배치 | 발주·감리·시공 3자 주간 소통 회의 및 일일 TBM 시행</t>
         </is>
       </c>
-      <c r="L8" s="24" t="inlineStr">
+      <c r="L8" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -26294,7 +26830,7 @@
           <t>1) 전담 기술자 1:1 배치 ➔ 2) 3자 주간 소통 회의 개최 ➔ 3) 근로자 환경 개선 &amp; TBM ➔ 4) One-Team 전담 조직표 서면 승인</t>
         </is>
       </c>
-      <c r="N8" s="79" t="inlineStr">
+      <c r="N8" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -26304,7 +26840,7 @@
           <t>토공 전담 기술자 1:1 배치, 발주·감리·시공 3자 주간 소통 회의 및 일일 TBM/복지 지원</t>
         </is>
       </c>
-      <c r="P8" s="24" t="inlineStr">
+      <c r="P8" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -26378,7 +26914,7 @@
           <t>건진법 시행령 제89조 | KCS 47 10 25 다짐 수칙(다짐도 ≥ 95%, K30 ≥ 110) 명시 | 착공 14일 전 책임감리단 기술 승인</t>
         </is>
       </c>
-      <c r="L9" s="24" t="inlineStr">
+      <c r="L9" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -26388,7 +26924,7 @@
           <t>1) 시공계획서 표준 8대 목차 작성 ➔ 2) KCS 47 10 25 수치 명시 ➔ 3) 착공 14일 전 감리단 제출 ➔ 4) 책임감리원 최종 서면 승인</t>
         </is>
       </c>
-      <c r="N9" s="79" t="inlineStr">
+      <c r="N9" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -26398,7 +26934,7 @@
           <t>시공계획서 표준 8대 목차, KCS 47 10 25 다짐 수칙 수록 및 착공 14일 전 감리 서면 승인</t>
         </is>
       </c>
-      <c r="P9" s="24" t="inlineStr">
+      <c r="P9" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -26472,7 +27008,7 @@
           <t>건설근로자법 준수 | 공종별 기술 수첩 및 장비 조종원 면허 1:1 현측 | 일일 음주 측정(0.00%) 및 작업조 조직표 승인</t>
         </is>
       </c>
-      <c r="L10" s="24" t="inlineStr">
+      <c r="L10" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -26482,7 +27018,7 @@
           <t>1) 토공 롤러/그레이더 조종원 자격 검증 ➔ 2) 건설기계 면허증 1:1 대조 ➔ 3) 일일 음주 측정 &amp; Safety TBM ➔ 4) 작업조 편성표 감리 승인</t>
         </is>
       </c>
-      <c r="N10" s="79" t="inlineStr">
+      <c r="N10" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -26492,7 +27028,7 @@
           <t>조종원/기술자 자격 수첩 1:1 대조, 건설기계 면허증 검증 및 일일 음주 측정(0.00%)/TBM</t>
         </is>
       </c>
-      <c r="P10" s="24" t="inlineStr">
+      <c r="P10" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -26566,7 +27102,7 @@
           <t>건설기계관리법 제13조 | 자중 10t+ 강동/타이어 롤러 및 3D GPS 모터그레이더 정기검사 검수 | 후방 센서 점검 및 반입 허가</t>
         </is>
       </c>
-      <c r="L11" s="24" t="inlineStr">
+      <c r="L11" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -26576,7 +27112,7 @@
           <t>1) 10t+ 강동/타이어 롤러 사양 확정 ➔ 2) 정기검사증 &amp; 등록증 검수 ➔ 3) 3D GPS 수신기/후방 카메라 점검 ➔ 4) 장비 반입 승인서 감리 결재</t>
         </is>
       </c>
-      <c r="N11" s="79" t="inlineStr">
+      <c r="N11" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -26586,7 +27122,7 @@
           <t>자중 10t+ 강동/타이어 롤러 정기검사증, 3D GPS 수신기/후방 카메라 센서 테스트 및 반입 승인</t>
         </is>
       </c>
-      <c r="P11" s="24" t="inlineStr">
+      <c r="P11" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -26660,7 +27196,7 @@
           <t>KCS 47 10 25 쇄석 입도 규정 | 최대입경 50mm 이하, #200체 통과량 ≤ 5% | 수정다짐 CBR ≥ 30% 성적 산출 및 입도 DB 구축</t>
         </is>
       </c>
-      <c r="L12" s="24" t="inlineStr">
+      <c r="L12" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -26670,7 +27206,7 @@
           <t>1) 석산 공급원 사전 승인 수속 ➔ 2) 쇄석 입도(Dmax 50mm) 체가름 시험 ➔ 3) 수정다짐 CBR(≥30%) 성적 산출 ➔ 4) 노반 재료 입도 DB 감리 승인</t>
         </is>
       </c>
-      <c r="N12" s="79" t="inlineStr">
+      <c r="N12" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -26680,7 +27216,7 @@
           <t>쇄석 최대입경(Dmax ≤ 50mm), #200체 통과량(≤ 5%) 및 수정다짐 CBR(≥ 30%) 성적서 DB</t>
         </is>
       </c>
-      <c r="P12" s="24" t="inlineStr">
+      <c r="P12" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -26754,7 +27290,7 @@
           <t>토양환경보전법 준수 | 화성시 정식 사토장 인허가 확인 | 최대건조밀도 γd max ≥ 1.90g/cm³ &amp; 토양오염 8개 항목 검사 완수</t>
         </is>
       </c>
-      <c r="L13" s="24" t="inlineStr">
+      <c r="L13" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -26764,7 +27300,7 @@
           <t>1) 화성시 정식 사토장 허가 검증 ➔ 2) γd max ≥ 1.90g/cm³ &amp; 오염 시험 ➔ 3) 덤프 운행 송장 일일 집계 ➔ 4) 사토 계획서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N13" s="79" t="inlineStr">
+      <c r="N13" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -26774,7 +27310,7 @@
           <t>화성시 정식 사토장 인허가, 최대건조밀도 γd max ≥ 1.90g/cm³ 및 토양오염 8개 항목 검사 합격</t>
         </is>
       </c>
-      <c r="P13" s="24" t="inlineStr">
+      <c r="P13" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -26848,7 +27384,7 @@
           <t>KCS 47 10 25 임시 배수 시방 | 성토 사면 가배수로(0.6×0.6m) &amp; 가침사지 2개소 | HDPE 유공관(Ø200mm, 구배 ≥ 0.5%) 부설</t>
         </is>
       </c>
-      <c r="L14" s="24" t="inlineStr">
+      <c r="L14" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -26858,7 +27394,7 @@
           <t>1) 가배수로(0.6×0.6m) &amp; 가침사지 설계 ➔ 2) HDPE 유공관(Ø200mm) 자재 검수 ➔ 3) 비상 양수 펌프(200L/min) 비치 ➔ 4) 배수 처리 계획서 감리 승인</t>
         </is>
       </c>
-      <c r="N14" s="79" t="inlineStr">
+      <c r="N14" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -26868,7 +27404,7 @@
           <t>성토 사면 가배수로(0.6×0.6m), 가침사지 2개소 및 HDPE 유공관(Ø200mm, 구배 ≥ 0.5%) 설치</t>
         </is>
       </c>
-      <c r="P14" s="24" t="inlineStr">
+      <c r="P14" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -26942,7 +27478,7 @@
           <t>건진법 제62조 준수 | 국토안전관리원 전산 적정 심사 필 | CSI 건설공사 안전관리 종합망 전산 등록 및 감리 승인</t>
         </is>
       </c>
-      <c r="L15" s="24" t="inlineStr">
+      <c r="L15" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -26952,7 +27488,7 @@
           <t>1) 건진법 제62조 안전관리계획 작성 ➔ 2) 국토안전관리원 전산 적정 심사 ➔ 3) CSI 안전관리 종합망 등록 ➔ 4) 책임감리원 서면 승인</t>
         </is>
       </c>
-      <c r="N15" s="79" t="inlineStr">
+      <c r="N15" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -26962,7 +27498,7 @@
           <t>건진법 제62조 안전관리계획서 작성, 국토안전관리원 적정 심사 및 CSI 전산망 등록 결재</t>
         </is>
       </c>
-      <c r="P15" s="24" t="inlineStr">
+      <c r="P15" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -27036,7 +27572,7 @@
           <t>건진법 제55조 준수 | 노반 다짐도(500m³당 1회), K30(2,000m²당 1회), Ev2(1,000m²당 1회) | 현장 시험실 장비 교정 검수</t>
         </is>
       </c>
-      <c r="L16" s="24" t="inlineStr">
+      <c r="L16" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -27046,7 +27582,7 @@
           <t>1) 다짐도/K30/Ev2 시험 빈도 수립 ➔ 2) 현장 시험실 장비 교정 검수 ➔ 3) 착공 14일 전 감리단 제출 ➔ 4) 품질관리계획서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N16" s="79" t="inlineStr">
+      <c r="N16" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -27056,7 +27592,7 @@
           <t>노반 다짐도(500m³당 1회), K30(2,000m²당 1회), Ev2(1,000m²당 1회) 시험 빈도 &amp; 장비 교정</t>
         </is>
       </c>
-      <c r="P16" s="24" t="inlineStr">
+      <c r="P16" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -27130,7 +27666,7 @@
           <t>대기환경보전법 제44조 | 지자체 비산먼지 발생사업 신고 필 | 이동식 세륜기(깊이 1.2m) &amp; 가설 방음벽(H=3m) 가동</t>
         </is>
       </c>
-      <c r="L17" s="24" t="inlineStr">
+      <c r="L17" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -27140,7 +27676,7 @@
           <t>1) 세륜기(깊이 1.2m) &amp; 방음벽(3m) 설계 ➔ 2) 지자체 비산먼지 발생신고 ➔ 3) 살수차 1일 3회 살수 ➔ 4) 환경관리계획서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N17" s="79" t="inlineStr">
+      <c r="N17" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -27150,7 +27686,7 @@
           <t>지자체 비산먼지 발생신고 필증, 이동식 세륜기(깊이 1.2m) &amp; 가설 방음벽(H=3m) 가동 점검</t>
         </is>
       </c>
-      <c r="P17" s="24" t="inlineStr">
+      <c r="P17" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -27224,7 +27760,7 @@
           <t>도로교통법 제69조 | 동탄경찰서 교통안전 심의 및 도로점용 허가 수령 | 전담 안전 신호수(2인 2조) 및 LED 경광등 배치</t>
         </is>
       </c>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="L18" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -27234,7 +27770,7 @@
           <t>1) 교통 우회 도면 &amp; 차선 설계 ➔ 2) 동탄경찰서 도로점용 허가 ➔ 3) 전담 신호수(2인 2조) 배치 ➔ 4) 교통소통 대책서 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N18" s="79" t="inlineStr">
+      <c r="N18" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -27244,7 +27780,7 @@
           <t>동탄경찰서 도로점용 허가, 우회 차선 설계 및 전담 안전 신호수(2인 2조)/LED 경광등 배치</t>
         </is>
       </c>
-      <c r="P18" s="24" t="inlineStr">
+      <c r="P18" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -27318,7 +27854,7 @@
           <t>건산법 제29조 준수 | 토공 전문건설업 면허 및 하도급율(≥ 82%) 적정성 심사 | 노무비 지급 전용계좌 지정 및 계약 승인</t>
         </is>
       </c>
-      <c r="L19" s="24" t="inlineStr">
+      <c r="L19" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -27328,7 +27864,7 @@
           <t>1) 토공 전문 면허 &amp; 실적 심사 ➔ 2) 하도급 적정성 평가(≥82%) ➔ 3) 노무비 지급 전용계좌 지정 ➔ 4) 하도급 계약 승인 통보서 결재</t>
         </is>
       </c>
-      <c r="N19" s="79" t="inlineStr">
+      <c r="N19" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -27338,7 +27874,7 @@
           <t>토공 전문건설업 면허/실적 심사, 하도급 비율(≥ 82%) 평가 및 노무비 지급 전용계좌 지정</t>
         </is>
       </c>
-      <c r="P19" s="24" t="inlineStr">
+      <c r="P19" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -27412,7 +27948,7 @@
           <t>KCS 47 10 25 자재 검수 | KS F 2527 쇄석골재, HDPE 유공관, 부직포(200g/m²) 공인성적서 | 현장 반입 검수 및 승인 통보</t>
         </is>
       </c>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="L20" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -27422,7 +27958,7 @@
           <t>1) KS F 2527 쇄석/유공관 서류 검토 ➔ 2) 공인시험기관 시험성적서 부착 ➔ 3) 자재 승인 신청서 제출 ➔ 4) 자재 반입 검수 및 승인 결재</t>
         </is>
       </c>
-      <c r="N20" s="79" t="inlineStr">
+      <c r="N20" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -27432,7 +27968,7 @@
           <t>KS F 2527 쇄석골재, HDPE 유공관, 투수성 부직포(200g/m²) 공인성적서 및 현장 반입 검수</t>
         </is>
       </c>
-      <c r="P20" s="24" t="inlineStr">
+      <c r="P20" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -27506,7 +28042,7 @@
           <t>KCS 47 10 25 현장 시험 수칙 | 50m 시험 구간 쇄석 30cm 부설 | 패스별 침하량 실측(침하 정지 Δh ≤ 1mm) 강동 4회 다짐 확정</t>
         </is>
       </c>
-      <c r="L21" s="24" t="inlineStr">
+      <c r="L21" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -27516,7 +28052,7 @@
           <t>1) 50m 시험 다짐 구간 지정 ➔ 2) 쇄석 30cm 두께 포설 ➔ 3) 패스별 침하량(Δh≤1mm) 측정 ➔ 4) 다짐 횟수(강동 4회) 보고서 승인</t>
         </is>
       </c>
-      <c r="N21" s="79" t="inlineStr">
+      <c r="N21" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -27526,7 +28062,7 @@
           <t>50m 시험 구간 쇄석 30cm 포설, 패스별 침하량(Δh ≤ 1mm) 실측 및 강동 4회 다짐 횟수 확정</t>
         </is>
       </c>
-      <c r="P21" s="24" t="inlineStr">
+      <c r="P21" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -27600,7 +28136,7 @@
           <t>KCS 47 10 25 원지반 규정 | 유기질 표토(15~30cm) 제거 및 전압 다짐 | 원지반 K30 ≥ 70 MN/m³ 시험 &amp; 덤프트럭 펌핑 점검</t>
         </is>
       </c>
-      <c r="L22" s="24" t="inlineStr">
+      <c r="L22" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -27610,7 +28146,7 @@
           <t>1) 표토(15~30cm) 제거 &amp; 정전압 다짐 ➔ 2) 원지반 표고 레벨 측량 ➔ 3) K30(≥70 MN/m³) &amp; 펌핑 검측 ➔ 4) 원지반 검측 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N22" s="79" t="inlineStr">
+      <c r="N22" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -27620,7 +28156,7 @@
           <t>유기질 표토(15~30cm) 제거전압 다짐, 원지반 K30 ≥ 70 MN/m³ 평판재하 및 덤프 펌핑 점검</t>
         </is>
       </c>
-      <c r="P22" s="24" t="inlineStr">
+      <c r="P22" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -27694,7 +28230,7 @@
           <t>KCS 47 10 25 하부노반 시방 | 토사 층두께 ≤ 30cm 포설 다짐 | 들밀도 다짐도 ≥ 90% (KS F 2311) &amp; K30 ≥ 90 MN/m³ 검측</t>
         </is>
       </c>
-      <c r="L23" s="24" t="inlineStr">
+      <c r="L23" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -27704,7 +28240,7 @@
           <t>1) 하부노반 30cm 층포설 &amp; 다짐 ➔ 2) 들밀도(≥90%) &amp; K30(≥90) 시험 ➔ 3) 마무리면 레벨 오차(±20mm) 검측 ➔ 4) 하부노반 검측서 감리 승인</t>
         </is>
       </c>
-      <c r="N23" s="79" t="inlineStr">
+      <c r="N23" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -27714,7 +28250,7 @@
           <t>토사 층두께 ≤ 30cm 포설 다짐, 들밀도 다짐도 ≥ 90% (KS F 2311) 및 K30 ≥ 90 MN/m³ 검측</t>
         </is>
       </c>
-      <c r="P23" s="24" t="inlineStr">
+      <c r="P23" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -27788,7 +28324,7 @@
           <t>KCS 47 10 25 상부노반 시방 | 토사 30cm 포설 다짐 | 맹암거 투수성 부직포(200g/m²) &amp; HDPE 유공관(Ø200mm) 매몰 검측</t>
         </is>
       </c>
-      <c r="L24" s="24" t="inlineStr">
+      <c r="L24" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -27798,7 +28334,7 @@
           <t>1) 상부노반 토사 30cm 포설 ➔ 2) 맹암거 부직포(200g/m²) 부설 ➔ 3) HDPE 유공관(Ø200mm) 종단 연결 ➔ 4) 상부노반 시공 감리 서면 승인</t>
         </is>
       </c>
-      <c r="N24" s="79" t="inlineStr">
+      <c r="N24" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -27808,7 +28344,7 @@
           <t>상부노반 토사 30cm 포설, 맹암거 투수성 부직포(200g/m²) 및 HDPE 유공관(Ø200mm) 매몰 검측</t>
         </is>
       </c>
-      <c r="P24" s="24" t="inlineStr">
+      <c r="P24" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -27882,7 +28418,7 @@
           <t>KCS 47 10 25 강화노반 쇄석 시방 | 3D GPS 쇄석(50mm) 30cm 포설 | 최적함수비 OMC 살수 &amp; 강동 4회/타이어 2회 다짐 (표고 오차 ±10mm)</t>
         </is>
       </c>
-      <c r="L25" s="24" t="inlineStr">
+      <c r="L25" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -27892,7 +28428,7 @@
           <t>1) 3D GPS 모터그레이더 쇄석(50mm) 30cm 포설 ➔ 2) 살수차 최적함수비 OMC 살수 ➔ 3) 강동 4회 + 타이어 2회 다짐 ➔ 4) 표고 오차(±10mm) 검측 감리 승인</t>
         </is>
       </c>
-      <c r="N25" s="79" t="inlineStr">
+      <c r="N25" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -27902,7 +28438,7 @@
           <t>3D GPS 쇄석(50mm) 30cm 포설, OMC 분무 살수 및 강동 4회/타이어 2회 다짐 (표고 오차 ±10mm)</t>
         </is>
       </c>
-      <c r="P25" s="24" t="inlineStr">
+      <c r="P25" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -27976,7 +28512,7 @@
           <t>KCS 47 10 25 다짐 검측 수칙 | 노반 들밀도 다짐도 ≥ 95% | K30 ≥ 110 MN/m³ &amp; 동적변형계수 Ev2 ≥ 60 MPa (Ev2/Ev1 ≤ 2.2) 검측</t>
         </is>
       </c>
-      <c r="L26" s="24" t="inlineStr">
+      <c r="L26" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -27986,7 +28522,7 @@
           <t>1) 들밀도 시험(다짐도 ≥ 95%) ➔ 2) K30 평판재하시험(≥ 110 MN/m³) ➔ 3) 동적변형계수 Ev2(≥ 60 MPa) 시험 ➔ 4) 다짐 검측 종합 보고서 승인</t>
         </is>
       </c>
-      <c r="N26" s="79" t="inlineStr">
+      <c r="N26" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -27996,7 +28532,7 @@
           <t>노반 들밀도 다짐도 ≥ 95%, 평판재하 K30 ≥ 110 MN/m³ 및 동적변형계수 Ev2 ≥ 60 MPa (Ev2/Ev1 ≤ 2.2)</t>
         </is>
       </c>
-      <c r="P26" s="24" t="inlineStr">
+      <c r="P26" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -28070,7 +28606,7 @@
           <t>KS F 2310 규정 준수 | Ø300mm 재하판 산모래 밀착 및 15t 유압 잭 하중 재하 | 1.25mm 침하 P-S 곡선 산출 K30 ≥ 110 MN/m³ 성적서</t>
         </is>
       </c>
-      <c r="L27" s="24" t="inlineStr">
+      <c r="L27" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -28080,7 +28616,7 @@
           <t>1) Ø300mm 재하판 산모래 밀착 ➔ 2) 15t 유압 잭 &amp; 다이얼 게이지 교정 ➔ 3) 1.25mm 침하 P-S 곡선 산출 ➔ 4) K30 ≥ 110 MN/m³ 성적서 승인</t>
         </is>
       </c>
-      <c r="N27" s="79" t="inlineStr">
+      <c r="N27" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -28090,7 +28626,7 @@
           <t>Ø300mm 재하판 산모래 밀착, 15t 유압 잭 재하 및 1.25mm 침하 P-S 곡선 K30 ≥ 110 MN/m³ 성적서</t>
         </is>
       </c>
-      <c r="P27" s="24" t="inlineStr">
+      <c r="P27" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -28164,7 +28700,7 @@
           <t>DIN 18134 규정 준수 | LWD 동적 평판재하시험 1,000m²당 1회 | 2차 변형계수 Ev2 ≥ 60 MPa &amp; 변형계수 비율 Ev2/Ev1 ≤ 2.2 검측</t>
         </is>
       </c>
-      <c r="L28" s="24" t="inlineStr">
+      <c r="L28" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -28174,7 +28710,7 @@
           <t>1) LWD 동적 평판재하시험기 교정 ➔ 2) 1,000m²당 1회 무작위 시험 ➔ 3) 1차/2차 하중 재하 Ev2/Ev1 산출 ➔ 4) Ev2 ≥ 60 MPa 성적서 감리 승인</t>
         </is>
       </c>
-      <c r="N28" s="79" t="inlineStr">
+      <c r="N28" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -28184,7 +28720,7 @@
           <t>LWD 동적 평판재하시험 1,000m²당 1회, 2차 변형계수 Ev2 ≥ 60 MPa 및 비율 Ev2/Ev1 ≤ 2.2 검측</t>
         </is>
       </c>
-      <c r="P28" s="24" t="inlineStr">
+      <c r="P28" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -28258,7 +28794,7 @@
           <t>KCS 47 10 25 평탄성 수칙 | 3m 알루미늄 직선자 20m 간격 연속 측정 | 최대 갭 오차 ±10mm 이내 통제 &amp; 요철 부위 삭평 재다짐</t>
         </is>
       </c>
-      <c r="L29" s="24" t="inlineStr">
+      <c r="L29" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -28268,7 +28804,7 @@
           <t>1) 3m 알루미늄 직선자 교정 ➔ 2) 20m 간격 종횡단 연속 검측 ➔ 3) 갭 오차(±10mm) 요철 삭평/재다짐 ➔ 4) 평탄성 검측 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N29" s="79" t="inlineStr">
+      <c r="N29" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -28278,7 +28814,7 @@
           <t>3m 알루미늄 직선자 20m 간격 연속 측정, 최대 갭 오차 ±10mm 이내 통제 및 요철 삭평/재다짐</t>
         </is>
       </c>
-      <c r="P29" s="24" t="inlineStr">
+      <c r="P29" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -28352,7 +28888,7 @@
           <t>KCS 47 10 25 측량 지침 | GRS80 광학 토탈스테이션 10m 간격 연속 측량 | 중심선(X,Y) 및 표고(Z) 오차 ±10mm 3D BIM 검측</t>
         </is>
       </c>
-      <c r="L30" s="24" t="inlineStr">
+      <c r="L30" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -28362,7 +28898,7 @@
           <t>1) GRS80 토탈스테이션 정밀 세팅 ➔ 2) 10m 간격 중심선 &amp; 표고 실측 ➔ 3) 3D BIM CAD 좌표(오차 ±10mm) 대조 ➔ 4) 종횡단 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N30" s="79" t="inlineStr">
+      <c r="N30" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -28372,7 +28908,7 @@
           <t>GRS80 광학 토탈스테이션 10m 간격 측정, 궤도 중심선(X,Y) 및 표고(Z) 오차 ±10mm 3D BIM 검측</t>
         </is>
       </c>
-      <c r="P30" s="24" t="inlineStr">
+      <c r="P30" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -28446,7 +28982,7 @@
           <t>건진법 NCR 조치 절차 | 감리단 부적합 통지서 수령 후 표면 15cm 파쇄 | OMC 살수 재다짐 및 1:1 재검측 NCR 서면 종결 승인</t>
         </is>
       </c>
-      <c r="L31" s="24" t="inlineStr">
+      <c r="L31" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -28456,7 +28992,7 @@
           <t>1) 감리단 NCR 통지서 수령 ➔ 2) 해당 구역 표면 15cm 파쇄 &amp; OMC 재다짐 ➔ 3) 1:1 재검측(다짐도/K30/Ev2) ➔ 4) NCR 조치 결과 보고서 감리 종결 승인</t>
         </is>
       </c>
-      <c r="N31" s="79" t="inlineStr">
+      <c r="N31" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -28466,7 +29002,7 @@
           <t>감리단 부적합(NCR) 수령 후 해당 구역 표면 15cm 파쇄, OMC 살수 재다짐 및 1:1 재검측 서면 종결</t>
         </is>
       </c>
-      <c r="P31" s="24" t="inlineStr">
+      <c r="P31" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -28540,7 +29076,7 @@
           <t>KCS 47 10 25 성토 사면 수칙 | 사면 비탈면 경사(1:1.5 이하) 측량 | 사면 다짐도 ≥ 90% 검측 &amp; 식생 거적 덮개(Jute Mat) 부설</t>
         </is>
       </c>
-      <c r="L32" s="24" t="inlineStr">
+      <c r="L32" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -28550,7 +29086,7 @@
           <t>1) 성토 사면 경사(1:1.5 이하) 측량 ➔ 2) 사면 다짐도(≥ 90%) 검측 ➔ 3) 식생 거적(Jute Mat) 30cm 겹침 부설 ➔ 4) 사면 다짐 성과표 감리 승인</t>
         </is>
       </c>
-      <c r="N32" s="79" t="inlineStr">
+      <c r="N32" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -28560,7 +29096,7 @@
           <t>성토 사면 비탈면 경사(1:1.5 이하) 측량, 사면 다짐도 ≥ 90% 검측 및 식생 거적(Jute Mat) 부설</t>
         </is>
       </c>
-      <c r="P32" s="24" t="inlineStr">
+      <c r="P32" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -28634,7 +29170,7 @@
           <t>KCS 47 10 25 노반 배수 시방 | U형 측구(0.4×0.4m, 버림 10cm) 부설 | 집수정 인버트 모타르 사춤, 주철 그레이팅 체결 &amp; 담수 시험</t>
         </is>
       </c>
-      <c r="L33" s="24" t="inlineStr">
+      <c r="L33" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -28644,7 +29180,7 @@
           <t>1) U형 측구 기초 버림(10cm) 타설 ➔ 2) U형 측구(0.4×0.4m) 부설 &amp; 인버트 사춤 ➔ 3) 주철 그레이팅 체결 &amp; 담수 시험 ➔ 4) 배수시설 검측서 감리 승인</t>
         </is>
       </c>
-      <c r="N33" s="79" t="inlineStr">
+      <c r="N33" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -28654,7 +29190,7 @@
           <t>U형 측구(0.4×0.4m, 버림 10cm) 부설, 집수정 인버트 모타르 사춤 및 주철 그레이팅 체결/담수 시험</t>
         </is>
       </c>
-      <c r="P33" s="24" t="inlineStr">
+      <c r="P33" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -28728,7 +29264,7 @@
           <t>KCS 47 10 25 완성면 관리 규정 | 통제 바리케이트(중장비 진입 100% 차단) | 미세 분무 살수(골재이탈 예방) &amp; 완성면 보호 대장 작성</t>
         </is>
       </c>
-      <c r="L34" s="24" t="inlineStr">
+      <c r="L34" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -28738,7 +29274,7 @@
           <t>1) 완성면 통제 바리케이트 설치 ➔ 2) 미세 분무 살수 &amp; 비닐 덮개 야적 ➔ 3) 일일 완성면 훼손 점검 ➔ 4) 완성면 보호 점검 대장 감리 승인</t>
         </is>
       </c>
-      <c r="N34" s="79" t="inlineStr">
+      <c r="N34" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -28748,7 +29284,7 @@
           <t>통제 바리케이트(중장비 진입 100% 차단), 미세 분무 살수(골재이탈 예방) 및 완성면 보호 대장 작성</t>
         </is>
       </c>
-      <c r="P34" s="24" t="inlineStr">
+      <c r="P34" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -28822,7 +29358,7 @@
           <t>건진법 시행규칙 공사기록 | 일일 투입 인원, 장비, 성토 물량(m³) 정밀 집계 | CSI 건설공사 관리 시스템 전산 등록 &amp; 감리 일일 직인</t>
         </is>
       </c>
-      <c r="L35" s="24" t="inlineStr">
+      <c r="L35" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -28832,7 +29368,7 @@
           <t>1) 일일 인원/장비/물량 집계 ➔ 2) 품질 시험 성적 &amp; TBM 수록 ➔ 3) CSI 전산 시스템 등록 ➔ 4) 책임감리원 일일 서면 직인 결재</t>
         </is>
       </c>
-      <c r="N35" s="79" t="inlineStr">
+      <c r="N35" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -28842,7 +29378,7 @@
           <t>일일 투입 인원/장비/성토 물량(m³) 집계, CSI 전산 관리 시스템 등록 및 감리 일일 서면 직인</t>
         </is>
       </c>
-      <c r="P35" s="24" t="inlineStr">
+      <c r="P35" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -28916,7 +29452,7 @@
           <t>건진법 &amp; KCS 47 10 25 총괄 수칙 | 공사 착수 24시간 전 검측 요청서 제출 | 책임감리원 1:1 현장 입회 &amp; 16개 체크리스트 서명 대장</t>
         </is>
       </c>
-      <c r="L36" s="24" t="inlineStr">
+      <c r="L36" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -28926,7 +29462,7 @@
           <t>1) 공종별 검측요청서 24시간 전 제출 ➔ 2) 책임감리원 1:1 현장 입회 ➔ 3) 16개 체크리스트 서명 ➔ 4) 검측 총괄 승인 대장 감리 결재</t>
         </is>
       </c>
-      <c r="N36" s="79" t="inlineStr">
+      <c r="N36" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -28936,7 +29472,7 @@
           <t>공사 착수 24시간 전 검측 요청서 제출, 책임감리원 1:1 현장 입회 및 16개 체크리스트 서명 대장</t>
         </is>
       </c>
-      <c r="P36" s="24" t="inlineStr">
+      <c r="P36" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -29010,7 +29546,7 @@
           <t>KCS 47 10 25 최종 인계인수 | 토공-궤도-감리 3자 합동 현측(표고 ±10mm, K30 ≥ 110) | 인계인수 합의서 서명 및 노반 완공 통보</t>
         </is>
       </c>
-      <c r="L37" s="24" t="inlineStr">
+      <c r="L37" s="131" t="inlineStr">
         <is>
           <t>표준서 보기 (HTML)</t>
         </is>
@@ -29020,7 +29556,7 @@
           <t>1) 3자(토공-궤도-감리) 합동 현측 ➔ 2) 표고(±10mm) &amp; K30(≥110) 재검측 ➔ 3) 인계인수 합의서 3자 서명 ➔ 4) 상부강화노반 최종 완공 통보</t>
         </is>
       </c>
-      <c r="N37" s="79" t="inlineStr">
+      <c r="N37" s="131" t="inlineStr">
         <is>
           <t>수행지침 보기 (HTML)</t>
         </is>
@@ -29030,7 +29566,7 @@
           <t>토공-궤도-감리 3자 합동 현측(표고 ±10mm, K30 ≥ 110), 인계인수 합의서 서명 및 완공 통보</t>
         </is>
       </c>
-      <c r="P37" s="24" t="inlineStr">
+      <c r="P37" s="131" t="inlineStr">
         <is>
           <t>체크리스트 보기 (HTML)</t>
         </is>
@@ -29356,7 +29892,7 @@
           <t>KDS 47 30 00 궤도 설계기준 및 국토교통부 트램 건설 규칙을 엄격히 준수한다. 노반부-궤도부 선형 및 종단 계획고 일치 오차 0mm 검토.</t>
         </is>
       </c>
-      <c r="L2" s="17" t="inlineStr">
+      <c r="L2" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -29367,7 +29903,7 @@
 2) 궤도 정밀 검측: 궤간(1435mm), 캔트(±2mm), 수평(±2mm), 고저(±2mm/10m), 비틀림(1.5mm/3m) 실시간 검측</t>
         </is>
       </c>
-      <c r="N2" s="53" t="inlineStr">
+      <c r="N2" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -29377,7 +29913,7 @@
           <t>설계 도면 간섭 검속, 궤도 중심선 계획 표고 대조, 종단 구배 한계치 준수 확인</t>
         </is>
       </c>
-      <c r="P2" s="53" t="inlineStr">
+      <c r="P2" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -29452,7 +29988,7 @@
           <t>침목, 체결구, 홈레일 등 궤도 주요 자재의 현장 보관 기준 수립. 배수 경사 2% 및 지반 다짐도 95% 이상 야적장 확보.</t>
         </is>
       </c>
-      <c r="L3" s="53" t="inlineStr">
+      <c r="L3" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -29463,7 +29999,7 @@
 2) 장대레일 운반 트레일러(길이 30m 이상) 회전반경 및 크레인 인양 진입로 확보</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -29473,7 +30009,7 @@
           <t>야적장 지반 다짐도 95% 이상, 배수 경사 2% 이상 확보, 자재 천막 덮개 구비</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -29548,7 +30084,7 @@
           <t>EN 14730 테르밋 및 EN 14587 가스압접 용접을 위한 작업 공간 확보. 정척레일(25m)을 200m 장대로 용접하는 평탄 작업대 수평 오차 ±1mm 이내 확보.</t>
         </is>
       </c>
-      <c r="L4" s="53" t="inlineStr">
+      <c r="L4" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -29559,7 +30095,7 @@
 2) 가스압접/플래시버트 용접용 대용량 전력 및 아세틸렌/산소 가스 안전 저장소 확보</t>
         </is>
       </c>
-      <c r="N4" s="53" t="inlineStr">
+      <c r="N4" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -29569,7 +30105,7 @@
           <t>용접장 평탄성 오차 ±1mm 이내, 전력 공급 및 방풍 시설 완비, NDT(비파괴) 대기 공간 확보</t>
         </is>
       </c>
-      <c r="P4" s="53" t="inlineStr">
+      <c r="P4" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -29649,7 +30185,7 @@
           <t>KCS 47 30 00 시방 기준 준수. 궤도 자재 품질 확인서 및 외산 홈레일 조달 리스크 대응 전략 수립.</t>
         </is>
       </c>
-      <c r="L5" s="53" t="inlineStr">
+      <c r="L5" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -29660,7 +30196,7 @@
 2) KDS 47 30 00 및 KS 규격 만족 자재 목록 및 세부 발주 물량 확정</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -29670,7 +30206,7 @@
           <t>품질 요구조건 특기시방서 의결, 외산 홈레일 선적일정 검토, 자재 인도 시점 확약</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="P5" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -29745,7 +30281,7 @@
           <t>EN ISO 9606-1 용접 자격자 및 궤도 정밀 검측원(Track Master 운용원) 확보 심사 기준.</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -29756,7 +30292,7 @@
 2) 스핀들 게이지 조정, 캔트 달성구배, 테르밋 산화반응 제어 사전 모의 훈련</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -29766,7 +30302,7 @@
           <t>용접공 자격증 원본 대조, 정밀 검측 장비 검교정 확인, 궤도 전문 기술사 면허 검토</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P6" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -29842,7 +30378,7 @@
           <t>KCS 47 30 00 콘크리트 궤도 시방 준수. 펌프카 타설압력에 의한 궤광 변위 방지 지지 계획 수립.</t>
         </is>
       </c>
-      <c r="L7" s="53" t="inlineStr">
+      <c r="L7" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -29853,7 +30389,7 @@
 2) 레미콘 운반시간(60분 이내) 및 펌프카 배치 공간 사전 확보</t>
         </is>
       </c>
-      <c r="N7" s="53" t="inlineStr">
+      <c r="N7" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -29863,7 +30399,7 @@
           <t>구간별 펌프카 배치도 작성, 타설 시 궤광 고정 잭 지지 계획 승인, 콘크리트 슬럼프 품질 확인</t>
         </is>
       </c>
-      <c r="P7" s="53" t="inlineStr">
+      <c r="P7" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -29946,7 +30482,7 @@
           <t>노반-궤도 간 인터페이스, 신호 루프 센서 및 누설 전류(Stray Current) 부식 방지 디오드 접지선 매설 계획 의결.</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -29957,7 +30493,7 @@
 2) 도로 매설 궤도 표면과 도로 포장 표면 마감 높이 일치성 확정</t>
         </is>
       </c>
-      <c r="N8" s="53" t="inlineStr">
+      <c r="N8" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -29967,7 +30503,7 @@
           <t>신호 센서 매설 위치 철근 간섭 해결, 접지선 용접부 연속성 확인, 부서 합동 서명 날인</t>
         </is>
       </c>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="P8" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -30042,7 +30578,7 @@
           <t>장대레일 운반 트레일러(길이 25m 이상) 도로 회전 반경 R=15m 확보 및 타공종 가설재 간섭 배제.</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -30053,7 +30589,7 @@
 2) 전담 신호수 배치 및 대형 레일 운반 차량 유도</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -30063,7 +30599,7 @@
           <t>트레일러 회전 시뮬레이션 승인, 가설 비계 간섭 범위 해제, 도로 점용 허가 필증 확인</t>
         </is>
       </c>
-      <c r="P9" s="53" t="inlineStr">
+      <c r="P9" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -30138,7 +30674,7 @@
           <t>홈레일, 체결구, 탄성 충전재 등 주요 자재의 해상 운송 및 국내 보관 일정 검토. OMC 품질 시방 확보.</t>
         </is>
       </c>
-      <c r="L10" s="53" t="inlineStr">
+      <c r="L10" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -30149,7 +30685,7 @@
 2) PST 슬래브 공장 생산 강도 및 홈레일 단면 검수</t>
         </is>
       </c>
-      <c r="N10" s="53" t="inlineStr">
+      <c r="N10" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -30159,7 +30695,7 @@
           <t>선적 서류 및 통관 승인서 구비, 국내 야적장 2차 보관 상태 점검, 자재 공급 승인서 확인</t>
         </is>
       </c>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="P10" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -30235,7 +30771,7 @@
           <t>KDS 47 30 00 및 EN 규격 기준 자재 발주서 승인. 공급원 검토 승인 요청서 작성 요령 준수.</t>
         </is>
       </c>
-      <c r="L11" s="53" t="inlineStr">
+      <c r="L11" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -30246,7 +30782,7 @@
 2) 공장 검사(FAT) 조건 및 성적서 첨부 명시</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -30256,7 +30792,7 @@
           <t>자재 발주 수량 설계 대조, 공급원 승인 필증 원본 확인, 발주 공문 승인 요청</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="P11" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -30332,7 +30868,7 @@
           <t>콘크리트도상 시공 절차 및 공정 스케줄 작성. 궤간(+3,-1mm), 캔트(±2mm) 관리계획 수립.</t>
         </is>
       </c>
-      <c r="L12" s="53" t="inlineStr">
+      <c r="L12" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -30343,7 +30879,7 @@
 2) 스핀들 게이지 조정, 테르밋 용접(EN 14730) 및 TCL 콘크리트 타설 수칙 수립</t>
         </is>
       </c>
-      <c r="N12" s="53" t="inlineStr">
+      <c r="N12" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -30353,7 +30889,7 @@
           <t>시공계획서 감리단 최종 승인, 선형 관리 한계선 설정 확인, 품질보증계획서 제출</t>
         </is>
       </c>
-      <c r="P12" s="53" t="inlineStr">
+      <c r="P12" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -30428,7 +30964,7 @@
           <t>반입 자재의 공장 성적서 대조 및 감리 입회 자재 인수 검사 수행. 변형/균열 자재 전량 반출.</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -30439,7 +30975,7 @@
 2) 레일 표면 흠집 및 PST 패널 치수 오차(±2mm) 측정</t>
         </is>
       </c>
-      <c r="N13" s="53" t="inlineStr">
+      <c r="N13" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -30449,7 +30985,7 @@
           <t>인수 검서 보고서 감리 서명, 자재 고유 마킹 대조, 손상 자재 반출 대장 기록</t>
         </is>
       </c>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="P13" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -30525,7 +31061,7 @@
           <t>기초 노반 표면의 지지력 검증. 평판재하시험 K30 ≥ 110 MN/m³ 또는 Ev2 ≥ 120 MPa 확인.</t>
         </is>
       </c>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="L14" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -30536,7 +31072,7 @@
 2) 노반 높이 오차(±10mm 이내) 광학 레벨 측량 검증</t>
         </is>
       </c>
-      <c r="N14" s="53" t="inlineStr">
+      <c r="N14" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -30546,7 +31082,7 @@
           <t>K30 성적서 원본 대조, 노반 마무리면 요철 제거 상태, 횡단 구배 2.0% 만족 확인</t>
         </is>
       </c>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="P14" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -30621,7 +31157,7 @@
           <t>강화노반 상부 기초콘크리트(HBR) 28일 압축강도 ≥ 21 MPa 확보. 고주파 다짐 및 습윤 양생 7일.</t>
         </is>
       </c>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="L15" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -30632,7 +31168,7 @@
 2) 콜드조인트 방지 연속 타설 및 바이브레이터 밀실 다짐</t>
         </is>
       </c>
-      <c r="N15" s="53" t="inlineStr">
+      <c r="N15" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -30642,7 +31178,7 @@
           <t>HBR 강도 시험 성적서, 습윤 부직포 포설 상태, 타설 두께 오차 ±10mm 이내 검속</t>
         </is>
       </c>
-      <c r="P15" s="17" t="inlineStr">
+      <c r="P15" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -30718,7 +31254,7 @@
           <t>PC 슬래브 패널 평탄성 오차 ±3mm 이내 거치. 광학 토탈스테이션 연동 정밀 3D 얼라인먼트.</t>
         </is>
       </c>
-      <c r="L16" s="17" t="inlineStr">
+      <c r="L16" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -30729,7 +31265,7 @@
 2) 점 인양 빔으로 패널 거치 후 스핀들 게이지 정밀 수평 조정</t>
         </is>
       </c>
-      <c r="N16" s="17" t="inlineStr">
+      <c r="N16" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -30739,7 +31275,7 @@
           <t>Screw Jack 레벨 정위치 고정, 3D 광학 실측 좌표 일치, 코너 크랙 육안 검사</t>
         </is>
       </c>
-      <c r="P16" s="53" t="inlineStr">
+      <c r="P16" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -30815,7 +31351,7 @@
           <t>전단앵커 구멍 천공 깊이 및 수직도 확보. 무수축 모르타르 그라우트 압축강도 ≥ 30 MPa 충전.</t>
         </is>
       </c>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="L17" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -30826,7 +31362,7 @@
 2) 음향 탐사로 공기 공동 파악 및 45 MPa 몰드 시험 확인</t>
         </is>
       </c>
-      <c r="N17" s="17" t="inlineStr">
+      <c r="N17" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -30836,7 +31372,7 @@
           <t>천공 깊이 측정 게이지 점검, 앵커 인장 강도 확인, 원웨이 주입 배출구 몰탈 오버플로우 확인</t>
         </is>
       </c>
-      <c r="P17" s="17" t="inlineStr">
+      <c r="P17" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -30911,7 +31447,7 @@
           <t>1,435mm 표준궤 정밀 유지 타이바 설치. 철근 피복 두께 40mm 확보 및 신호 감선 이격 150mm.</t>
         </is>
       </c>
-      <c r="L18" s="17" t="inlineStr">
+      <c r="L18" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -30922,7 +31458,7 @@
 2) 궤간 1,435mm(+3,-1mm) 고정 및 캔트/수평 오차 ±2mm 이내 정밀 정열</t>
         </is>
       </c>
-      <c r="N18" s="53" t="inlineStr">
+      <c r="N18" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -30932,7 +31468,7 @@
           <t>철근 결속선 긴장 상태, 타이바 조임 토크 확인, 신호 루프 케이블 배근 이격 확인</t>
         </is>
       </c>
-      <c r="P18" s="17" t="inlineStr">
+      <c r="P18" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -31007,7 +31543,7 @@
           <t>타설 측압 대비 서포트 앵커 W=1.0m 간격 고정. 거푸집 수평/수직 처짐 변위 ±2mm 이내 통제.</t>
         </is>
       </c>
-      <c r="L19" s="53" t="inlineStr">
+      <c r="L19" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -31018,7 +31554,7 @@
 2) 거푸집 면 이물질 청소 및 환경 친화 박리제 균일 도포</t>
         </is>
       </c>
-      <c r="N19" s="17" t="inlineStr">
+      <c r="N19" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -31028,7 +31564,7 @@
           <t>거푸집 지지대 앵커 조임, 박리제 도포 상태, 이음매 틈새 누수 패킹 확인</t>
         </is>
       </c>
-      <c r="P19" s="53" t="inlineStr">
+      <c r="P19" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -31104,7 +31640,7 @@
           <t>TCL 도상 콘크리트 강도 ≥ 35 MPa. 타설 중 실시간 궤간척(Gauge Bar) 캔트 오차 ±2mm 보정.</t>
         </is>
       </c>
-      <c r="L20" s="17" t="inlineStr">
+      <c r="L20" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -31115,7 +31651,7 @@
 2) 고주파 다짐 실시 및 타설 중 실시간 궤간/캔트 오차 미세 조율</t>
         </is>
       </c>
-      <c r="N20" s="53" t="inlineStr">
+      <c r="N20" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -31125,7 +31661,7 @@
           <t>타설 중 궤간척 실시간 모니터링, 슬럼프 및 공기량 시험, 습윤 양생 부직포 포설 확인</t>
         </is>
       </c>
-      <c r="P20" s="53" t="inlineStr">
+      <c r="P20" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -31201,7 +31737,7 @@
           <t>EN 14587 규격 준수. 레일 단부 가열(1200℃) 후 압송. 용접부 직선도 1m당 ±0.2mm 이내 정밀 연마.</t>
         </is>
       </c>
-      <c r="L21" s="17" t="inlineStr">
+      <c r="L21" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -31212,7 +31748,7 @@
 2) EN 14587 프로그램에 따라 자동 가열 및 버(Burr) 핫 쉐어링 전단</t>
         </is>
       </c>
-      <c r="N21" s="53" t="inlineStr">
+      <c r="N21" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -31222,7 +31758,7 @@
           <t>가스 압접 압력 게이지 확인, 용접부 급랭 방지 덮개 설치, 비파괴 시험(UT) 성적서 결재</t>
         </is>
       </c>
-      <c r="P21" s="53" t="inlineStr">
+      <c r="P21" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -31299,7 +31835,7 @@
           <t>EN 14730 규격 준수. 도가니 반응 후 슬래그 분리. 직선도 오차 ±0.2mm 이내 및 NDT 100% 합격.</t>
         </is>
       </c>
-      <c r="L22" s="17" t="inlineStr">
+      <c r="L22" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -31310,7 +31846,7 @@
 2) 몰드 밀봉 후 테르밋 소모품點火 반응 주입 및 약 5분 후 유압 전단</t>
         </is>
       </c>
-      <c r="N22" s="53" t="inlineStr">
+      <c r="N22" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -31320,7 +31856,7 @@
           <t>테르밋 용제 예열 온도 확인, 도가니 수평 고정, 비파괴 검사(UT/MT) 전수 실시</t>
         </is>
       </c>
-      <c r="P22" s="17" t="inlineStr">
+      <c r="P22" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -31396,7 +31932,7 @@
           <t>레일 마무리면 평탄성 1m 기준 오차 ±0.2mm 이내 밀링. 레일 과열에 의한 열응력 크랙 방지.</t>
         </is>
       </c>
-      <c r="L23" s="53" t="inlineStr">
+      <c r="L23" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -31407,7 +31943,7 @@
 2) 장대레일 구간 연마/밀링 장비 점검 및 표면 단차 사전 조사</t>
         </is>
       </c>
-      <c r="N23" s="17" t="inlineStr">
+      <c r="N23" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -31417,7 +31953,7 @@
           <t>레일 조도/평탄성 측정 성적서, 절삭유 적정 분사 상태, 마이크로미터 선로 실측</t>
         </is>
       </c>
-      <c r="P23" s="17" t="inlineStr">
+      <c r="P23" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -31491,7 +32027,7 @@
           <t>전기/신호/노반 담당자 입회 하에 궤도 회로 절연 저항 ≥ 100MΩ 검속. 준공 도면 일치 서명.</t>
         </is>
       </c>
-      <c r="L24" s="58" t="inlineStr">
+      <c r="L24" s="132" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -31502,7 +32038,7 @@
 2) 구간별 NDT 용접 성과표, 강도 성적서 및 궤도 정열표 대조</t>
         </is>
       </c>
-      <c r="N24" s="55" t="inlineStr">
+      <c r="N24" s="132" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -31512,7 +32048,7 @@
           <t>3자 공동 인수 서명 날인, 절연 저항 테스트 결과표 첨부, CAD 준공 대장 제출</t>
         </is>
       </c>
-      <c r="P24" s="58" t="inlineStr">
+      <c r="P24" s="132" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -31794,7 +32330,7 @@
 2) 설계 적정성 검토 달성을 위한 필수 시공 방법(시공성 검토: 구조물, 마감, 가시설 등 기계설비/전기/통신 등 인터페이스: 개구부/슬리브 반영 유무 및 확...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K2" s="34" t="inlineStr">
+      <c r="K2" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -31805,7 +32341,7 @@
 2) 실무 작업방법 수칙(시공성 검토: 구조물, 마감, 가시설 등 기계설비/전기/통신 등 인터페이스: 개구부/슬리브 반...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M2" s="88" t="inlineStr">
+      <c r="M2" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -31816,7 +32352,7 @@
 2) 미검측 및 정량 시방 미달에 따른 설계 적정성 검토 (WBS 9000-4-1) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 설계변경 예상 List, 회의록 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O2" s="34" t="inlineStr">
+      <c r="O2" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -31890,7 +32426,7 @@
 2) 발주전략 KOM 달성을 위한 필수 시공 방법(가시공 B/P 적정성 검토 현설조건 검토 공법 및 공기 검토 예산 적정성 검토 현장 여건 및 지반상태(기초,...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K3" s="34" t="inlineStr">
+      <c r="K3" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -31901,7 +32437,7 @@
 2) 실무 작업방법 수칙(가시공 B/P 적정성 검토 현설조건 검토 공법 및 공기 검토 예산 적정성 검토 현장 여건 및 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M3" s="88" t="inlineStr">
+      <c r="M3" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -31912,7 +32448,7 @@
 2) 미검측 및 정량 시방 미달에 따른 발주전략 KOM (WBS 9000-4-2) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 KOM 검토결과서, 현설서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O3" s="34" t="inlineStr">
+      <c r="O3" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -31985,7 +32521,7 @@
 2) 착공전 건축 인허가 달성을 위한 필수 시공 방법(건축허가 요청(-&gt;관할 지자체) 착공신고서 제출(-&gt;관할 지자체) 소방시설공사 착공신고서 제출 (-&gt;관할 소...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K4" s="34" t="inlineStr">
+      <c r="K4" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -31996,7 +32532,7 @@
 2) 실무 작업방법 수칙(건축허가 요청(-&gt;관할 지자체) 착공신고서 제출(-&gt;관할 지자체) 소방시설공사 착공신고서 제출...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M4" s="34" t="inlineStr">
+      <c r="M4" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -32007,7 +32543,7 @@
 2) 미검측 및 정량 시방 미달에 따른 착공전 건축 인허가 (WBS 9000-4-3) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 인허가 신고/승인 문서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O4" s="34" t="inlineStr">
+      <c r="O4" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -32080,7 +32616,7 @@
 2) 건축허가 요청 달성을 위한 필수 시공 방법(건축설계사, 현장준비팀 -&gt; 관할지자체 건축법 제11조(건축허가) 서식: 별지 제1호의4서식 관할지자체(시,...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K5" s="34" t="inlineStr">
+      <c r="K5" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -32091,7 +32627,7 @@
 2) 실무 작업방법 수칙(건축설계사, 현장준비팀 -&gt; 관할지자체 건축법 제11조(건축허가) 서식: 별지 제1호의4서식 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M5" s="34" t="inlineStr">
+      <c r="M5" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -32102,7 +32638,7 @@
 2) 미검측 및 정량 시방 미달에 따른 건축허가 요청 (WBS 9000-4-4) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 건축허가 통보 문서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O5" s="34" t="inlineStr">
+      <c r="O5" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -32175,7 +32711,7 @@
 2) 착공신고서 제출 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체 건축법 제21조(착공신고등) 서식: 별지 제13호 서식 제출후 지자체 처리기간 3일 이...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K6" s="34" t="inlineStr">
+      <c r="K6" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -32186,7 +32722,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체 건축법 제21조(착공신고등) 서식: 별지 제13호 서식 제출후 지자체 처...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M6" s="88" t="inlineStr">
+      <c r="M6" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -32197,7 +32733,7 @@
 2) 미검측 및 정량 시방 미달에 따른 착공신고서 제출 (WBS 9000-4-5) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 착공신고서 승인 통보 문서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O6" s="34" t="inlineStr">
+      <c r="O6" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -32269,7 +32805,7 @@
 2) 소방시설공사 착공 신고서 제출 달성을 위한 필수 시공 방법(현장 -&gt; 관할소방서, 소방시설공사업법 제13조(착공신고) 서식: 별지 제14호 서식 제출후 처리기간 2일 ...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K7" s="34" t="inlineStr">
+      <c r="K7" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -32280,7 +32816,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할소방서, 소방시설공사업법 제13조(착공신고) 서식: 별지 제14호 서식 제출후 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M7" s="34" t="inlineStr">
+      <c r="M7" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -32291,7 +32827,7 @@
 2) 미검측 및 정량 시방 미달에 따른 소방시설공사 착공 신고서 제출 (WBS 9000-4-6) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 소방시설공사 착공신고필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O7" s="34" t="inlineStr">
+      <c r="O7" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -32363,7 +32899,7 @@
 2) 정보통신공사 착공전 설계도 확인 (신청서 제출 및 결과 접수) 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체, 정보통신공사업법 시행령 제35조의 2 서식: 별지 제7호 서식 제출후 처리기간 14일...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K8" s="34" t="inlineStr">
+      <c r="K8" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -32374,7 +32910,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체, 정보통신공사업법 시행령 제35조의 2 서식: 별지 제7호 서식 제출후 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M8" s="34" t="inlineStr">
+      <c r="M8" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -32385,7 +32921,7 @@
 2) 미검측 및 정량 시방 미달에 따른 정보통신공사 착공전 설계도 확인 (신청서 제출 및 결과 접수) (WBS 9000-4-7) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 정보통신공사 착공전 설계도 확인결과 통보서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O8" s="34" t="inlineStr">
+      <c r="O8" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -32457,7 +32993,7 @@
 2) 선행공종 인수사항 확인 달성을 위한 필수 시공 방법(부지경계 측량 확인 업체간 현장확인+좌표화 Data 인수 지장물, 지반상태, 진입로, 작업장 현황...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K9" s="34" t="inlineStr">
+      <c r="K9" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -32468,7 +33004,7 @@
 2) 실무 작업방법 수칙(부지경계 측량 확인 업체간 현장확인+좌표화 Data 인수 지장물, 지반상태, 진입로, 작업장 현황)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M9" s="34" t="inlineStr">
+      <c r="M9" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -32479,7 +33015,7 @@
 2) 미검측 및 정량 시방 미달에 따른 선행공종 인수사항 확인 (WBS 9000-4-8) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 회의록, 인수사항 List 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O9" s="34" t="inlineStr">
+      <c r="O9" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -32551,7 +33087,7 @@
 2) 인터페이스 사항 검토 및 지원 달성을 위한 필수 시공 방법(설계도서 검토를 통한 공종간 인터페이스 사항에 대한 사전검토(오픈구 등) 유사공종 경험자 현장 지원 파견검토...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K10" s="34" t="inlineStr">
+      <c r="K10" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -32562,7 +33098,7 @@
 2) 실무 작업방법 수칙(설계도서 검토를 통한 공종간 인터페이스 사항에 대한 사전검토(오픈구 등) 유사공종 경험자 현장...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M10" s="34" t="inlineStr">
+      <c r="M10" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -32573,7 +33109,7 @@
 2) 미검측 및 정량 시방 미달에 따른 인터페이스 사항 검토 및 지원 (WBS 9000-4-9) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 회의록, 시공상세도 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O10" s="34" t="inlineStr">
+      <c r="O10" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -32643,7 +33179,7 @@
 2) 품질/안전 LL 공유 달성을 위한 필수 시공 방법(시공시 발생가능 품질, 안전 하자 최소화...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K11" s="34" t="inlineStr">
+      <c r="K11" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -32654,7 +33190,7 @@
 2) 실무 작업방법 수칙(시공시 발생가능 품질, 안전 하자 최소화)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M11" s="34" t="inlineStr">
+      <c r="M11" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -32665,7 +33201,7 @@
 2) 미검측 및 정량 시방 미달에 따른 품질/안전 LL 공유 (WBS 9000-4-10) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 시공계획수립시 반영 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O11" s="34" t="inlineStr">
+      <c r="O11" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -32737,7 +33273,7 @@
 2) 자재공급원승인 및 자재발주 달성을 위한 필수 시공 방법(자재 규격 및 반입 일정 계획 수립 시공에 필요한 당사 지급자재에 대한 발주 요청 자재공급원 승인 제출 및 ...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K12" s="34" t="inlineStr">
+      <c r="K12" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -32748,7 +33284,7 @@
 2) 실무 작업방법 수칙(자재 규격 및 반입 일정 계획 수립 시공에 필요한 당사 지급자재에 대한 발주 요청 자재공급원 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M12" s="34" t="inlineStr">
+      <c r="M12" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -32759,7 +33295,7 @@
 2) 미검측 및 정량 시방 미달에 따른 자재공급원승인 및 자재발주 (WBS 9000-4-11) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 구매 의뢰 승인, 자재공급원 승인서류 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O12" s="34" t="inlineStr">
+      <c r="O12" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -32838,7 +33374,7 @@
 2) 착수전 Big Room 회의 달성을 위한 필수 시공 방법(본사/현장/협력사 협의체 구축 후 상세검토 건축인허가 사항 체크 (건축허가, 착공계제출, 소방착공신고, 정보...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K13" s="34" t="inlineStr">
+      <c r="K13" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -32849,7 +33385,7 @@
 2) 실무 작업방법 수칙(본사/현장/협력사 협의체 구축 후 상세검토 건축인허가 사항 체크 (건축허가, 착공계제출, 소방...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M13" s="88" t="inlineStr">
+      <c r="M13" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -32860,7 +33396,7 @@
 2) 미검측 및 정량 시방 미달에 따른 착수전 Big Room 회의 (WBS 9000-4-12) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 Big Room 회의록(참석자 전원 서명) 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O13" s="34" t="inlineStr">
+      <c r="O13" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -32933,7 +33469,7 @@
 2) 시공계획 수립/승인 달성을 위한 필수 시공 방법(공사계획: 장비/자재배치, 동선, 인원/장비/자재투입 계획, 공정표, 배수계획 등 안전관리: 위험요인/대책,...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K14" s="34" t="inlineStr">
+      <c r="K14" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -32944,7 +33480,7 @@
 2) 실무 작업방법 수칙(공사계획: 장비/자재배치, 동선, 인원/장비/자재투입 계획, 공정표, 배수계획 등 안전관리: ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M14" s="34" t="inlineStr">
+      <c r="M14" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -32955,7 +33491,7 @@
 2) 미검측 및 정량 시방 미달에 따른 시공계획 수립/승인 (WBS 9000-4-13) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 (승인)관리시공계획서&amp;시공상세도 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O14" s="34" t="inlineStr">
+      <c r="O14" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -33028,7 +33564,7 @@
 2) 측량, 자재/장비 반입, 안전교육 달성을 위한 필수 시공 방법(측량: 측량기준점 설치, 공사위치 마킹 자재는 지정된 야적장에 보관 장비 Spec확인, 장비안전검사 작업원 ...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K15" s="34" t="inlineStr">
+      <c r="K15" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -33039,7 +33575,7 @@
 2) 실무 작업방법 수칙(측량: 측량기준점 설치, 공사위치 마킹 자재는 지정된 야적장에 보관 장비 Spec확인, 장비안...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M15" s="34" t="inlineStr">
+      <c r="M15" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -33050,7 +33586,7 @@
 2) 미검측 및 정량 시방 미달에 따른 측량, 자재/장비 반입, 안전교육 (WBS 9000-4-14) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 측량기록지, 안전교육 결과서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O15" s="34" t="inlineStr">
+      <c r="O15" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -33122,7 +33658,7 @@
 2) 자재 검수 달성을 위한 필수 시공 방법(송장과 실물 확인(규격, 성능, 수량) 시방기준에 따른 품질시험 실시 훼손, 오반입시 반출조치...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K16" s="34" t="inlineStr">
+      <c r="K16" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -33133,7 +33669,7 @@
 2) 실무 작업방법 수칙(송장과 실물 확인(규격, 성능, 수량) 시방기준에 따른 품질시험 실시 훼손, 오반입시 반출조치)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M16" s="34" t="inlineStr">
+      <c r="M16" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -33144,7 +33680,7 @@
 2) 미검측 및 정량 시방 미달에 따른 자재 검수 (WBS 9000-4-15) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 자재검수서, 품질시험 보고서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O16" s="34" t="inlineStr">
+      <c r="O16" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -33214,7 +33750,7 @@
 2) 터파기/지반 정리 달성을 위한 필수 시공 방법(측량을 통한 계획Level, 위치 확인, 바닥 지지력 시험...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K17" s="34" t="inlineStr">
+      <c r="K17" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -33225,7 +33761,7 @@
 2) 실무 작업방법 수칙(측량을 통한 계획Level, 위치 확인, 바닥 지지력 시험)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M17" s="34" t="inlineStr">
+      <c r="M17" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -33236,7 +33772,7 @@
 2) 미검측 및 정량 시방 미달에 따른 터파기/지반 정리 (WBS 9000-4-16) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 측량 성과, 지지력시험성과 보고서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O17" s="34" t="inlineStr">
+      <c r="O17" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -33306,7 +33842,7 @@
 2) 바닥(버림) 콘크리트 타설 달성을 위한 필수 시공 방법(도면에 따라 거푸집 조립, 버림con't타설, 양생, 거푸집 해체/정리...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K18" s="34" t="inlineStr">
+      <c r="K18" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -33317,7 +33853,7 @@
 2) 실무 작업방법 수칙(도면에 따라 거푸집 조립, 버림con't타설, 양생, 거푸집 해체/정리)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M18" s="34" t="inlineStr">
+      <c r="M18" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -33328,7 +33864,7 @@
 2) 미검측 및 정량 시방 미달에 따른 바닥(버림) 콘크리트 타설 (WBS 9000-4-17) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O18" s="34" t="inlineStr">
+      <c r="O18" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -33398,7 +33934,7 @@
 2) 인터페이스 회의(매주) 달성을 위한 필수 시공 방법(시공중 지속적인 인터페이스(기계, 전기, 통신 등) 회의를 통하여 시공전 계획했던 대로 원활한 선후행공정 시...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K19" s="34" t="inlineStr">
+      <c r="K19" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -33409,7 +33945,7 @@
 2) 실무 작업방법 수칙(시공중 지속적인 인터페이스(기계, 전기, 통신 등) 회의를 통하여 시공전 계획했던 대로 원활한...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M19" s="34" t="inlineStr">
+      <c r="M19" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -33420,7 +33956,7 @@
 2) 미검측 및 정량 시방 미달에 따른 인터페이스 회의(매주) (WBS 9000-4-18) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 인터페이스 회의록 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O19" s="34" t="inlineStr">
+      <c r="O19" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -33490,7 +34026,7 @@
 2) 인터페이스 각 공종별 Issue (기계, 전기, 통신분야) 달성을 위한 필수 시공 방법(각 해당공종(건축, 기계, 전기) 도면과 건축도면을 비교 및 현장여건 검토를 통한 시공방법 결정, 각종 필증...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K20" s="34" t="inlineStr">
+      <c r="K20" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -33501,7 +34037,7 @@
 2) 실무 작업방법 수칙(각 해당공종(건축, 기계, 전기) 도면과 건축도면을 비교 및 현장여건 검토를 통한 시공방법 결...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M20" s="34" t="inlineStr">
+      <c r="M20" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -33512,7 +34048,7 @@
 2) 미검측 및 정량 시방 미달에 따른 인터페이스 각 공종별 Issue (기계, 전기, 통신분야) (WBS 9000-4-19) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 인터페이스 회의록 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O20" s="34" t="inlineStr">
+      <c r="O20" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -33582,7 +34118,7 @@
 2) 인터페이스 각 공종별 Issue (토목분야) 달성을 위한 필수 시공 방법(구조물별 외부 배수 설계와 같은 현장 여건을 구성이 되었는지 확인...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K21" s="34" t="inlineStr">
+      <c r="K21" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -33593,7 +34129,7 @@
 2) 실무 작업방법 수칙(구조물별 외부 배수 설계와 같은 현장 여건을 구성이 되었는지 확인)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M21" s="34" t="inlineStr">
+      <c r="M21" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -33604,7 +34140,7 @@
 2) 미검측 및 정량 시방 미달에 따른 인터페이스 각 공종별 Issue (토목분야) (WBS 9000-4-20) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 회의록 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O21" s="34" t="inlineStr">
+      <c r="O21" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -33674,7 +34210,7 @@
 2) 기초~상부슬라브 구조물 시공 달성을 위한 필수 시공 방법(발주 이후 마감공정 연계, 거푸집 해체 이후 균열조사 및 보수조치 시행...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K22" s="34" t="inlineStr">
+      <c r="K22" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -33685,7 +34221,7 @@
 2) 실무 작업방법 수칙(발주 이후 마감공정 연계, 거푸집 해체 이후 균열조사 및 보수조치 시행)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M22" s="34" t="inlineStr">
+      <c r="M22" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -33696,7 +34232,7 @@
 2) 미검측 및 정량 시방 미달에 따른 기초~상부슬라브 구조물 시공 (WBS 9000-4-21) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 해당공종 검측서, 각종 품질시험결과 보고서, 마감공종 인수인계서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O22" s="34" t="inlineStr">
+      <c r="O22" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -33766,7 +34302,7 @@
 2) 철근 가공 달성을 위한 필수 시공 방법(설계도면과 가공상세가 일치하는지 확인 및 보강부분 시공상세도 확인...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K23" s="34" t="inlineStr">
+      <c r="K23" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -33777,7 +34313,7 @@
 2) 실무 작업방법 수칙(설계도면과 가공상세가 일치하는지 확인 및 보강부분 시공상세도 확인)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M23" s="34" t="inlineStr">
+      <c r="M23" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -33788,7 +34324,7 @@
 2) 미검측 및 정량 시방 미달에 따른 철근 가공 (WBS 9000-4-22) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 철근 시공상세도 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O23" s="34" t="inlineStr">
+      <c r="O23" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -33858,7 +34394,7 @@
 2) 작업발판, 비계 및 동바리 설치 달성을 위한 필수 시공 방법(안전난간 및 발판 설치 이후 철근 조립 및 거푸집 설치를 위한 비계 및 동바리 설치...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K24" s="34" t="inlineStr">
+      <c r="K24" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -33869,7 +34405,7 @@
 2) 실무 작업방법 수칙(안전난간 및 발판 설치 이후 철근 조립 및 거푸집 설치를 위한 비계 및 동바리 설치)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M24" s="34" t="inlineStr">
+      <c r="M24" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -33880,7 +34416,7 @@
 2) 미검측 및 정량 시방 미달에 따른 작업발판, 비계 및 동바리 설치 (WBS 9000-4-23) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 비계 및 동바리 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O24" s="34" t="inlineStr">
+      <c r="O24" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -33950,7 +34486,7 @@
 2) 철근 조립 달성을 위한 필수 시공 방법(철근 배근, 철근 조립 및 결속, 철근 이물질 등 검사...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K25" s="34" t="inlineStr">
+      <c r="K25" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -33961,7 +34497,7 @@
 2) 실무 작업방법 수칙(철근 배근, 철근 조립 및 결속, 철근 이물질 등 검사)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M25" s="34" t="inlineStr">
+      <c r="M25" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -33972,7 +34508,7 @@
 2) 미검측 및 정량 시방 미달에 따른 철근 조립 (WBS 9000-4-24) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 철근 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O25" s="34" t="inlineStr">
+      <c r="O25" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34042,7 +34578,7 @@
 2) 거푸집 조립 달성을 위한 필수 시공 방법(합판, 강재등의 자재를 활용하여 설계도면 형상에 맞게 시공...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K26" s="34" t="inlineStr">
+      <c r="K26" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34053,7 +34589,7 @@
 2) 실무 작업방법 수칙(합판, 강재등의 자재를 활용하여 설계도면 형상에 맞게 시공)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M26" s="34" t="inlineStr">
+      <c r="M26" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -34064,7 +34600,7 @@
 2) 미검측 및 정량 시방 미달에 따른 거푸집 조립 (WBS 9000-4-25) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 거푸집 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O26" s="34" t="inlineStr">
+      <c r="O26" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34136,7 +34672,7 @@
 2) 콘크리트 타설 및 다짐 달성을 위한 필수 시공 방법(타설과 동시에 적당한 공법으로 다짐, 양생관리 마감품질 관련하여, 재료, 균열관리방안 상부슬라브 타설시 동바...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K27" s="34" t="inlineStr">
+      <c r="K27" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34147,7 +34683,7 @@
 2) 실무 작업방법 수칙(타설과 동시에 적당한 공법으로 다짐, 양생관리 마감품질 관련하여, 재료, 균열관리방안 상부슬라...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M27" s="34" t="inlineStr">
+      <c r="M27" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -34158,7 +34694,7 @@
 2) 미검측 및 정량 시방 미달에 따른 콘크리트 타설 및 다짐 (WBS 9000-4-26) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 콘크리트 구조물 확보, 타설보고서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O27" s="34" t="inlineStr">
+      <c r="O27" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34228,7 +34764,7 @@
 2) 거푸집 해체 달성을 위한 필수 시공 방법(구조물에 훼손이 없도록 주의하여 안전하게 해체, 부속자재(핀, 타이, 결속선 등) 제거, 상태 Double ...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K28" s="34" t="inlineStr">
+      <c r="K28" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34239,7 +34775,7 @@
 2) 실무 작업방법 수칙(구조물에 훼손이 없도록 주의하여 안전하게 해체, 부속자재(핀, 타이, 결속선 등) 제거, 상태...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M28" s="34" t="inlineStr">
+      <c r="M28" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -34250,7 +34786,7 @@
 2) 미검측 및 정량 시방 미달에 따른 거푸집 해체 (WBS 9000-4-27) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 해체 완료 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O28" s="34" t="inlineStr">
+      <c r="O28" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34320,7 +34856,7 @@
 2) 건축 내부 및 마감공사 달성을 위한 필수 시공 방법(구조물 시공 이후 외벽 방수 진행, 내부 마감공사 연계, 선행공종 균열관리대책 확인...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K29" s="34" t="inlineStr">
+      <c r="K29" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34331,7 +34867,7 @@
 2) 실무 작업방법 수칙(구조물 시공 이후 외벽 방수 진행, 내부 마감공사 연계, 선행공종 균열관리대책 확인)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M29" s="34" t="inlineStr">
+      <c r="M29" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -34342,7 +34878,7 @@
 2) 미검측 및 정량 시방 미달에 따른 건축 내부 및 마감공사 (WBS 9000-4-28) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 해당공종 검측서, 품질시험결과 보고서, 마감공종 인수인계서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O29" s="34" t="inlineStr">
+      <c r="O29" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34412,7 +34948,7 @@
 2) 창호,유리 및 금속지붕공사 달성을 위한 필수 시공 방법(외벽 마감 공사(금속지붕 공사 / 내부 창호 및 유리 시공)...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K30" s="34" t="inlineStr">
+      <c r="K30" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34423,7 +34959,7 @@
 2) 실무 작업방법 수칙(외벽 마감 공사(금속지붕 공사 / 내부 창호 및 유리 시공))에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M30" s="34" t="inlineStr">
+      <c r="M30" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -34434,7 +34970,7 @@
 2) 미검측 및 정량 시방 미달에 따른 창호,유리 및 금속지붕공사 (WBS 9000-4-29) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 시공상세도 및 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O30" s="34" t="inlineStr">
+      <c r="O30" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34504,7 +35040,7 @@
 2) 조적공사 달성을 위한 필수 시공 방법(시멘트 벽돌 및 블록으로 세대 칸막이 형성 일일 최대 쌓는높이 1.2m(내력벽)...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K31" s="34" t="inlineStr">
+      <c r="K31" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34515,7 +35051,7 @@
 2) 실무 작업방법 수칙(시멘트 벽돌 및 블록으로 세대 칸막이 형성 일일 최대 쌓는높이 1.2m(내력벽))에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M31" s="34" t="inlineStr">
+      <c r="M31" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -34526,7 +35062,7 @@
 2) 미검측 및 정량 시방 미달에 따른 조적공사 (WBS 9000-4-30) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 시멘트 벽돌 및 블록 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O31" s="34" t="inlineStr">
+      <c r="O31" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34596,7 +35132,7 @@
 2) 내부 방수공사 달성을 위한 필수 시공 방법(구조물 청소 및 바탕정리후 방수공사 시행(코너부 및 드레인 주위 보강방수 실시)...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K32" s="34" t="inlineStr">
+      <c r="K32" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34607,7 +35143,7 @@
 2) 실무 작업방법 수칙(구조물 청소 및 바탕정리후 방수공사 시행(코너부 및 드레인 주위 보강방수 실시))에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M32" s="34" t="inlineStr">
+      <c r="M32" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -34618,7 +35154,7 @@
 2) 미검측 및 정량 시방 미달에 따른 내부 방수공사 (WBS 9000-4-31) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 방수공사 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O32" s="34" t="inlineStr">
+      <c r="O32" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34688,7 +35224,7 @@
 2) 미장 및 타일공사 달성을 위한 필수 시공 방법(미장공사는 시멘트와 모래(1:3배합)하여 바탕면에 바르는 작업, 타일공사는 벽면 미장후 타일시공...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K33" s="34" t="inlineStr">
+      <c r="K33" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34699,7 +35235,7 @@
 2) 실무 작업방법 수칙(미장공사는 시멘트와 모래(1:3배합)하여 바탕면에 바르는 작업, 타일공사는 벽면 미장후 타일시공)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M33" s="34" t="inlineStr">
+      <c r="M33" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -34710,7 +35246,7 @@
 2) 미검측 및 정량 시방 미달에 따른 미장 및 타일공사 (WBS 9000-4-32) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 미장,타일 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O33" s="34" t="inlineStr">
+      <c r="O33" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34780,7 +35316,7 @@
 2) 수장 및 잡철물공사 달성을 위한 필수 시공 방법(각실의 천정공사(텍스류), 바닥마감공사(비닐계타일),도배공사등을 수행, 잡철물 공사는 각실의 도어, 난간,창...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K34" s="34" t="inlineStr">
+      <c r="K34" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34791,7 +35327,7 @@
 2) 실무 작업방법 수칙(각실의 천정공사(텍스류), 바닥마감공사(비닐계타일),도배공사등을 수행, 잡철물 공사는 각실의 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M34" s="34" t="inlineStr">
+      <c r="M34" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -34802,7 +35338,7 @@
 2) 미검측 및 정량 시방 미달에 따른 수장 및 잡철물공사 (WBS 9000-4-33) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 수장 및 잡철물검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O34" s="34" t="inlineStr">
+      <c r="O34" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34872,7 +35408,7 @@
 2) 도장공사 달성을 위한 필수 시공 방법(도장재 (붓, 롤러등)로 벽면에 시공...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K35" s="34" t="inlineStr">
+      <c r="K35" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34883,7 +35419,7 @@
 2) 실무 작업방법 수칙(도장재 (붓, 롤러등)로 벽면에 시공)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M35" s="34" t="inlineStr">
+      <c r="M35" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -34894,7 +35430,7 @@
 2) 미검측 및 정량 시방 미달에 따른 도장공사 (WBS 9000-4-34) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 도장공사 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O35" s="34" t="inlineStr">
+      <c r="O35" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -34964,7 +35500,7 @@
 2) 인테리어 및 무대공사 달성을 위한 필수 시공 방법(추가로 발생되는 건축공사에 적합한 자재 반입, 검수 및 시공...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K36" s="34" t="inlineStr">
+      <c r="K36" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -34975,7 +35511,7 @@
 2) 실무 작업방법 수칙(추가로 발생되는 건축공사에 적합한 자재 반입, 검수 및 시공)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M36" s="34" t="inlineStr">
+      <c r="M36" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -34986,7 +35522,7 @@
 2) 미검측 및 정량 시방 미달에 따른 인테리어 및 무대공사 (WBS 9000-4-35) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 각 공종 검측서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O36" s="34" t="inlineStr">
+      <c r="O36" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -35056,7 +35592,7 @@
 2) 준공전 건축 인허가 달성을 위한 필수 시공 방법(승강기 설치신고, 저수조 설치신고, 정화조 및 오수처리시설 신고, 전기사용전 검사 신청, 승강기 설치검사 신...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K37" s="34" t="inlineStr">
+      <c r="K37" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -35067,7 +35603,7 @@
 2) 실무 작업방법 수칙(승강기 설치신고, 저수조 설치신고, 정화조 및 오수처리시설 신고, 전기사용전 검사 신청, 승강...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M37" s="34" t="inlineStr">
+      <c r="M37" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -35078,7 +35614,7 @@
 2) 미검측 및 정량 시방 미달에 따른 준공전 건축 인허가 (WBS 9000-4-36) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 인허가 신고 / 승인 문서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O37" s="34" t="inlineStr">
+      <c r="O37" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -35150,7 +35686,7 @@
 2) 소방시설공사 완공검사 달성을 위한 필수 시공 방법(현장 -&gt; 관할소방서 및 지자체 소방시설공사법 제14조 서식: 별지 제17호 서식 제출후 처리기간 3일 이내...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K38" s="34" t="inlineStr">
+      <c r="K38" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -35161,7 +35697,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할소방서 및 지자체 소방시설공사법 제14조 서식: 별지 제17호 서식 제출후 처리...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M38" s="34" t="inlineStr">
+      <c r="M38" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -35172,7 +35708,7 @@
 2) 미검측 및 정량 시방 미달에 따른 소방시설공사 완공검사 (WBS 9000-4-37) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 소방시설 완공검사 증명서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O38" s="34" t="inlineStr">
+      <c r="O38" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -35244,7 +35780,7 @@
 2) 승강기 설치 신고서 제출 달성을 위한 필수 시공 방법(현장 -&gt; 승강기 안전공단, 승강기 안전관리법 제27조 서식: 별지 제22호 서식 제출후 처리기간 7일 이내...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K39" s="34" t="inlineStr">
+      <c r="K39" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -35255,7 +35791,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 승강기 안전공단, 승강기 안전관리법 제27조 서식: 별지 제22호 서식 제출후 처리...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M39" s="34" t="inlineStr">
+      <c r="M39" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -35266,7 +35802,7 @@
 2) 미검측 및 정량 시방 미달에 따른 승강기 설치 신고서 제출 (WBS 9000-4-38) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 승강기 설치 신고필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O39" s="34" t="inlineStr">
+      <c r="O39" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -35337,7 +35873,7 @@
 2) 저수조 설치현황 신고서 제출 달성을 위한 필수 시공 방법(현장 -&gt; 저수조업체 -&gt; 관할지자체, 수도법 제33조(위생상의 조치) 서식: 별지 제12호 서식...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K40" s="34" t="inlineStr">
+      <c r="K40" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -35348,7 +35884,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 저수조업체 -&gt; 관할지자체, 수도법 제33조(위생상의 조치) 서식: 별지 제12호 서식)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M40" s="34" t="inlineStr">
+      <c r="M40" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -35359,7 +35895,7 @@
 2) 미검측 및 정량 시방 미달에 따른 저수조 설치현황 신고서 제출 (WBS 9000-4-39) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 저수조 설치 신고필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O40" s="34" t="inlineStr">
+      <c r="O40" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -35431,7 +35967,7 @@
 2) 오수처리시설 / 정화조 설치 신고서 제출 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체, 하수도법 제34조 서식: 별지 제13호 서식 제출후 처리기간 5일 이내...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K41" s="34" t="inlineStr">
+      <c r="K41" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -35442,7 +35978,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체, 하수도법 제34조 서식: 별지 제13호 서식 제출후 처리기간 5일 이내)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M41" s="34" t="inlineStr">
+      <c r="M41" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -35453,7 +35989,7 @@
 2) 미검측 및 정량 시방 미달에 따른 오수처리시설 / 정화조 설치 신고서 제출 (WBS 9000-4-40) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 오수처리시설/정화조 설치 신고필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O41" s="34" t="inlineStr">
+      <c r="O41" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -35524,7 +36060,7 @@
 2) 전기사용전 검사 달성을 위한 필수 시공 방법(현장 -&gt; 한국전기안전공사, 전기안전관리법 제9조(사용전검사) 서식: 별지 제4호 서식...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K42" s="34" t="inlineStr">
+      <c r="K42" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -35535,7 +36071,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 한국전기안전공사, 전기안전관리법 제9조(사용전검사) 서식: 별지 제4호 서식)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M42" s="34" t="inlineStr">
+      <c r="M42" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -35546,7 +36082,7 @@
 2) 미검측 및 정량 시방 미달에 따른 전기사용전 검사 (WBS 9000-4-41) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 전기사용전 검사 필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O42" s="34" t="inlineStr">
+      <c r="O42" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -35618,7 +36154,7 @@
 2) 승강기 설치검사 달성을 위한 필수 시공 방법(현장 -&gt; 한국승강기안전공단, 승강기 안전관리법 제28조(승강기 설치) 서식: 별지 제23호 서식 제출후 처...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K43" s="34" t="inlineStr">
+      <c r="K43" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -35629,7 +36165,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 한국승강기안전공단, 승강기 안전관리법 제28조(승강기 설치) 서식: 별지 제23호 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M43" s="34" t="inlineStr">
+      <c r="M43" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -35640,7 +36176,7 @@
 2) 미검측 및 정량 시방 미달에 따른 승강기 설치검사 (WBS 9000-4-42) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 승강기 사용필증, 합격증보고서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O43" s="34" t="inlineStr">
+      <c r="O43" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -35710,7 +36246,7 @@
 2) 배수설비 설치 신고서 제출 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체/하수도법 제27조/별지 제7호 서식/제출후 처리기간 7일 이내...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K44" s="34" t="inlineStr">
+      <c r="K44" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -35721,7 +36257,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체/하수도법 제27조/별지 제7호 서식/제출후 처리기간 7일 이내)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M44" s="34" t="inlineStr">
+      <c r="M44" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -35732,7 +36268,7 @@
 2) 미검측 및 정량 시방 미달에 따른 배수설비 설치 신고서 제출 (WBS 9000-4-43) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 배수설비 사용필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O44" s="34" t="inlineStr">
+      <c r="O44" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -35804,7 +36340,7 @@
 2) 정보통신공사 사용전검사 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체, 정보통신공사업 시행령 제36조 서식: 해당 법 별지 제9호 서식 제출후 처리기간 14...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K45" s="34" t="inlineStr">
+      <c r="K45" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -35815,7 +36351,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체, 정보통신공사업 시행령 제36조 서식: 해당 법 별지 제9호 서식 제출후...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M45" s="34" t="inlineStr">
+      <c r="M45" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -35826,7 +36362,7 @@
 2) 미검측 및 정량 시방 미달에 따른 정보통신공사 사용전검사 (WBS 9000-4-44) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 정보통신사용전 검사필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O45" s="34" t="inlineStr">
+      <c r="O45" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -35898,7 +36434,7 @@
 2) 오수처리시설 / 정화조 준공검사 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체, 하수도법 제37조 서식: 해당 법 별지 제15호 서식 제출후 처리기간 5일 이내...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K46" s="34" t="inlineStr">
+      <c r="K46" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -35909,7 +36445,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체, 하수도법 제37조 서식: 해당 법 별지 제15호 서식 제출후 처리기간 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M46" s="34" t="inlineStr">
+      <c r="M46" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -35920,7 +36456,7 @@
 2) 미검측 및 정량 시방 미달에 따른 오수처리시설 / 정화조 준공검사 (WBS 9000-4-45) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 오수처리시설 / 정화조 준공필증 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O46" s="34" t="inlineStr">
+      <c r="O46" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -35991,7 +36527,7 @@
 2) 급수공사 신청서 제출 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체, 수도 조례 시행규칙 서식: 해당 법 별지 제1호 서식...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K47" s="34" t="inlineStr">
+      <c r="K47" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -36002,7 +36538,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체, 수도 조례 시행규칙 서식: 해당 법 별지 제1호 서식)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M47" s="34" t="inlineStr">
+      <c r="M47" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -36013,7 +36549,7 @@
 2) 미검측 및 정량 시방 미달에 따른 급수공사 신청서 제출 (WBS 9000-4-46) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 급수 사용허가 문서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O47" s="34" t="inlineStr">
+      <c r="O47" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -36084,7 +36620,7 @@
 2) 업무대행 건축사 사용승인 검사 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체, 건축법시행령 제20조(현장조사검사 및 확인 업무대행) 서식: 해당 법 별지 제17호 ...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K48" s="34" t="inlineStr">
+      <c r="K48" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -36095,7 +36631,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체, 건축법시행령 제20조(현장조사검사 및 확인 업무대행) 서식: 해당 법 ...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M48" s="34" t="inlineStr">
+      <c r="M48" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -36106,7 +36642,7 @@
 2) 미검측 및 정량 시방 미달에 따른 업무대행 건축사 사용승인 검사 (WBS 9000-4-47) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 건축물 사용승인 알림 [공문] 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O48" s="34" t="inlineStr">
+      <c r="O48" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -36178,7 +36714,7 @@
 2) 건축물 사용승인 신청 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체, 건축법 제22조(건축물의 사용승인) 서식: 해당 법 별지 제17호 서식 제출후 처리기...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K49" s="34" t="inlineStr">
+      <c r="K49" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -36189,7 +36725,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체, 건축법 제22조(건축물의 사용승인) 서식: 해당 법 별지 제17호 서식...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M49" s="34" t="inlineStr">
+      <c r="M49" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -36200,7 +36736,7 @@
 2) 미검측 및 정량 시방 미달에 따른 건축물 사용승인 신청 (WBS 9000-4-48) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 건축물 사용승인 알림 [공문] 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O49" s="34" t="inlineStr">
+      <c r="O49" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -36270,7 +36806,7 @@
 2) 건축물대장 등재 달성을 위한 필수 시공 방법(현장 -&gt; 관할지자체 -&gt; 관할지자체, 건축물대장의 기재 12조, 처리기간 7일 이내...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K50" s="34" t="inlineStr">
+      <c r="K50" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -36281,7 +36817,7 @@
 2) 실무 작업방법 수칙(현장 -&gt; 관할지자체 -&gt; 관할지자체, 건축물대장의 기재 12조, 처리기간 7일 이내)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M50" s="34" t="inlineStr">
+      <c r="M50" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -36292,7 +36828,7 @@
 2) 미검측 및 정량 시방 미달에 따른 건축물대장 등재 (WBS 9000-4-49) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 건축물 대장 등재 확인 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O50" s="34" t="inlineStr">
+      <c r="O50" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -36365,7 +36901,7 @@
 2) 후속 구조물 인계 달성을 위한 필수 시공 방법(건축 인허가 서류 및 준공도서 인계 건축인허가 서류: 승강기 사용필증, 소방시설 완공검사 증명서, 전기사용전...) 및 국가 기술 규격을 엄격히 보장한다. 이에 따라 구조 안전성 100% 입증, 누수/균열 하자 0건 달성 및 책임감리원 최종 결재를 완료하여 지자체 건축물 사용승인(준공) 필증을 획득한다.</t>
         </is>
       </c>
-      <c r="K51" s="34" t="inlineStr">
+      <c r="K51" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -36376,7 +36912,7 @@
 2) 실무 작업방법 수칙(건축 인허가 서류 및 준공도서 인계 건축인허가 서류: 승강기 사용필증, 소방시설 완공검사 증명...)에 따라 철근 이음/피복두께 검측, 거푸집 다짐 양생 및 현장 3대 금기 수칙(피복 미달, 무단 타설)을 완수한다.</t>
         </is>
       </c>
-      <c r="M51" s="34" t="inlineStr">
+      <c r="M51" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -36387,7 +36923,7 @@
 2) 미검측 및 정량 시방 미달에 따른 후속 구조물 인계 (WBS 9000-4-50) 구조 균열/누수 하자 발생, 개구부 누락 재시공 손실 및 최종 유지관리기관 인수인계서, 건축 인허가 서류, 준공도서 승인 반려 리스크를 전면 차단한다.</t>
         </is>
       </c>
-      <c r="O51" s="34" t="inlineStr">
+      <c r="O51" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -36750,7 +37286,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K2" s="17" t="inlineStr">
+      <c r="K2" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -36761,7 +37297,7 @@
 2) 타 공종의 도면 개정(Revision) 여부를 매주 확인하여 구버전 도면 기반의 시공 오류를 차단하십시오.</t>
         </is>
       </c>
-      <c r="M2" s="17" t="inlineStr">
+      <c r="M2" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -36772,7 +37308,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O2" s="17" t="inlineStr">
+      <c r="O2" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -36848,7 +37384,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K3" s="17" t="inlineStr">
+      <c r="K3" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -36859,7 +37395,7 @@
 2) 설계 변경 안건 발생 시 책임감리원의 서면 결재 없이 현장 임의 시공을 절대 진행하지 마십시오.</t>
         </is>
       </c>
-      <c r="M3" s="53" t="inlineStr">
+      <c r="M3" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -36870,7 +37406,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O3" s="17" t="inlineStr">
+      <c r="O3" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -36944,7 +37480,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K4" s="17" t="inlineStr">
+      <c r="K4" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -36955,7 +37491,7 @@
 2) 설계 변경 안건 발생 시 책임감리원의 서면 결재 없이 현장 임의 시공을 절대 진행하지 마십시오.</t>
         </is>
       </c>
-      <c r="M4" s="17" t="inlineStr">
+      <c r="M4" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -36966,7 +37502,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O4" s="17" t="inlineStr">
+      <c r="O4" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37034,7 +37570,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K5" s="17" t="inlineStr">
+      <c r="K5" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -37047,7 +37583,7 @@
 2) 장애 및 인터페이스 회복 및 관리대응</t>
         </is>
       </c>
-      <c r="M5" s="17" t="inlineStr">
+      <c r="M5" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37058,7 +37594,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O5" s="17" t="inlineStr">
+      <c r="O5" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37125,7 +37661,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K6" s="17" t="inlineStr">
+      <c r="K6" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -37137,7 +37673,7 @@
 - 궤도 분기기 통과 요구사항 검토 및 확인</t>
         </is>
       </c>
-      <c r="M6" s="53" t="inlineStr">
+      <c r="M6" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37148,7 +37684,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O6" s="17" t="inlineStr">
+      <c r="O6" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37215,7 +37751,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K7" s="17" t="inlineStr">
+      <c r="K7" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -37227,7 +37763,7 @@
 - 통신선 배선 적합성 및 인터페이스 검토</t>
         </is>
       </c>
-      <c r="M7" s="17" t="inlineStr">
+      <c r="M7" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37238,7 +37774,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O7" s="17" t="inlineStr">
+      <c r="O7" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37306,7 +37842,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K8" s="17" t="inlineStr">
+      <c r="K8" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -37317,7 +37853,7 @@
 2) 설계 변경 안건 발생 시 책임감리원의 서면 결재 없이 현장 임의 시공을 절대 진행하지 마십시오.</t>
         </is>
       </c>
-      <c r="M8" s="17" t="inlineStr">
+      <c r="M8" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37328,7 +37864,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O8" s="17" t="inlineStr">
+      <c r="O8" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37395,7 +37931,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K9" s="17" t="inlineStr">
+      <c r="K9" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -37407,7 +37943,7 @@
 - 신호제어 운영사 실무 조율 및 협의</t>
         </is>
       </c>
-      <c r="M9" s="17" t="inlineStr">
+      <c r="M9" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37418,7 +37954,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O9" s="17" t="inlineStr">
+      <c r="O9" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37484,7 +38020,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K10" s="17" t="inlineStr">
+      <c r="K10" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -37495,7 +38031,7 @@
 2) 설계 변경 안건 발생 시 책임감리원의 서면 결재 없이 현장 임의 시공을 절대 진행하지 마십시오.</t>
         </is>
       </c>
-      <c r="M10" s="17" t="inlineStr">
+      <c r="M10" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37506,7 +38042,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O10" s="17" t="inlineStr">
+      <c r="O10" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37574,7 +38110,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K11" s="17" t="inlineStr">
+      <c r="K11" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -37585,7 +38121,7 @@
 2) [센서 타격 금지]매립 궤도 콘크리트 타설 시 고주파 바이브레이터 다짐기가 축차계수기 듀얼 센서 지지대에 부딪히지 않도록 5cm 이상 이격 다짐을 이행하십시오.</t>
         </is>
       </c>
-      <c r="M11" s="53" t="inlineStr">
+      <c r="M11" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37596,7 +38132,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O11" s="17" t="inlineStr">
+      <c r="O11" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37664,7 +38200,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K12" s="17" t="inlineStr">
+      <c r="K12" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -37675,7 +38211,7 @@
 2) [센서 타격 금지]매립 궤도 콘크리트 타설 시 고주파 바이브레이터 다짐기가 축차계수기 듀얼 센서 지지대에 부딪히지 않도록 5cm 이상 이격 다짐을 이행하십시오.</t>
         </is>
       </c>
-      <c r="M12" s="17" t="inlineStr">
+      <c r="M12" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37686,7 +38222,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O12" s="17" t="inlineStr">
+      <c r="O12" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37757,7 +38293,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K13" s="17" t="inlineStr">
+      <c r="K13" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -37768,7 +38304,7 @@
 2) [센서 타격 금지]매립 궤도 콘크리트 타설 시 고주파 바이브레이터 다짐기가 축차계수기 듀얼 센서 지지대에 부딪히지 않도록 5cm 이상 이격 다짐을 이행하십시오.</t>
         </is>
       </c>
-      <c r="M13" s="17" t="inlineStr">
+      <c r="M13" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37779,7 +38315,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O13" s="17" t="inlineStr">
+      <c r="O13" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37850,7 +38386,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K14" s="17" t="inlineStr">
+      <c r="K14" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -37862,7 +38398,7 @@
 - 지상신호장치 및 관계부서 단위시험 결과서</t>
         </is>
       </c>
-      <c r="M14" s="17" t="inlineStr">
+      <c r="M14" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37873,7 +38409,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O14" s="17" t="inlineStr">
+      <c r="O14" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -37945,7 +38481,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K15" s="17" t="inlineStr">
+      <c r="K15" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -37958,7 +38494,7 @@
 - 지상 및 차량 인터페이스 시 시험 결과표</t>
         </is>
       </c>
-      <c r="M15" s="17" t="inlineStr">
+      <c r="M15" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -37969,7 +38505,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O15" s="17" t="inlineStr">
+      <c r="O15" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -38041,7 +38577,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K16" s="17" t="inlineStr">
+      <c r="K16" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -38054,7 +38590,7 @@
 - 신기술공법/기능성/현장성 단위 시험 결과서</t>
         </is>
       </c>
-      <c r="M16" s="17" t="inlineStr">
+      <c r="M16" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -38065,7 +38601,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O16" s="17" t="inlineStr">
+      <c r="O16" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -38138,7 +38674,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K17" s="17" t="inlineStr">
+      <c r="K17" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -38152,7 +38688,7 @@
 - 수전 및 전압 점검</t>
         </is>
       </c>
-      <c r="M17" s="17" t="inlineStr">
+      <c r="M17" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -38163,7 +38699,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O17" s="17" t="inlineStr">
+      <c r="O17" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -38235,7 +38771,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K18" s="17" t="inlineStr">
+      <c r="K18" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -38248,7 +38784,7 @@
 - 2) 차량, 신호, 통신 시스템간 인터페이스 시험</t>
         </is>
       </c>
-      <c r="M18" s="17" t="inlineStr">
+      <c r="M18" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -38259,7 +38795,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O18" s="17" t="inlineStr">
+      <c r="O18" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -38331,7 +38867,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K19" s="17" t="inlineStr">
+      <c r="K19" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -38344,7 +38880,7 @@
 - 관제센터와의 연계 기계실/차량내 장치(DID 보드 등) 운영 및 테스트</t>
         </is>
       </c>
-      <c r="M19" s="17" t="inlineStr">
+      <c r="M19" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -38355,7 +38891,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O19" s="17" t="inlineStr">
+      <c r="O19" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -38427,7 +38963,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K20" s="17" t="inlineStr">
+      <c r="K20" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -38438,7 +38974,7 @@
 2) 설계 변경 안건 발생 시 책임감리원의 서면 결재 없이 현장 임의 시공을 절대 진행하지 마십시오.</t>
         </is>
       </c>
-      <c r="M20" s="17" t="inlineStr">
+      <c r="M20" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -38449,7 +38985,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O20" s="17" t="inlineStr">
+      <c r="O20" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -38519,7 +39055,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K21" s="17" t="inlineStr">
+      <c r="K21" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -38530,7 +39066,7 @@
 2) - 철도종합시험운행 시행지침상 검사사항 검증</t>
         </is>
       </c>
-      <c r="M21" s="17" t="inlineStr">
+      <c r="M21" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -38541,7 +39077,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O21" s="17" t="inlineStr">
+      <c r="O21" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -38613,7 +39149,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K22" s="17" t="inlineStr">
+      <c r="K22" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -38626,7 +39162,7 @@
 - 철도안전관련계 체계 및 시운전수행 승인 등 관계 기관에 제출</t>
         </is>
       </c>
-      <c r="M22" s="17" t="inlineStr">
+      <c r="M22" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -38637,7 +39173,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O22" s="17" t="inlineStr">
+      <c r="O22" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
@@ -38708,7 +39244,7 @@
 2) IEC 61508/62425 SIL 4 전자연동장치(CBI) 이중화 회로 무결성을 검증하고 신호 시스템 장애율 0%, 비상 사고 대응 연동 무결성 100% 이수로 동탄트램 정식 개통 및 영업 진입 승인을 완수한다.</t>
         </is>
       </c>
-      <c r="K23" s="17" t="inlineStr">
+      <c r="K23" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 표준서 열기 📄</t>
         </is>
@@ -38719,7 +39255,7 @@
 2) [센서 타격 금지]매립 궤도 콘크리트 타설 시 고주파 바이브레이터 다짐기가 축차계수기 듀얼 센서 지지대에 부딪히지 않도록 5cm 이상 이격 다짐을 이행하십시오.</t>
         </is>
       </c>
-      <c r="M23" s="17" t="inlineStr">
+      <c r="M23" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 수행지침 열기 📄</t>
         </is>
@@ -38730,7 +39266,7 @@
 2) 축차계수기 듀얼 센서 레일 체결 토크(45~50 Nm)를 정밀 토크렌치로 검측하였는가?</t>
         </is>
       </c>
-      <c r="O23" s="17" t="inlineStr">
+      <c r="O23" s="125" t="inlineStr">
         <is>
           <t>👉 [더블클릭] 체크리스트 열기 📄</t>
         </is>
